--- a/Datos de azucar y firmeza por melon en general.xlsx
+++ b/Datos de azucar y firmeza por melon en general.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>% &gt; 12 °Brix</t>
+          <t>% ≥ 12 °Brix</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -619,7 +619,7 @@
         <v>7407</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.6985</v>
+        <v>0.8304</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>3509</v>
@@ -663,7 +663,7 @@
         <v>95</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>0.6947</v>
+        <v>0.6943</v>
       </c>
       <c r="K3" s="5" t="n">
         <v>45</v>
@@ -711,7 +711,7 @@
         <v>95</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>0.6947</v>
+        <v>0.6943</v>
       </c>
       <c r="K4" s="8" t="n">
         <v>45</v>
@@ -755,7 +755,7 @@
         <v>165</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>0.3999</v>
+        <v>0.6906</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>80</v>
@@ -851,7 +851,7 @@
         <v>35</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>0.3714</v>
+        <v>0.3999</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>15</v>
@@ -899,7 +899,7 @@
         <v>10</v>
       </c>
       <c r="J8" s="11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K8" s="8" t="n">
         <v>5</v>
@@ -947,7 +947,7 @@
         <v>110</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.4181</v>
+        <v>0.8087</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>55</v>
@@ -991,7 +991,7 @@
         <v>664</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.8488</v>
+        <v>0.8431</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>319</v>
@@ -1183,7 +1183,7 @@
         <v>99</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.9272</v>
+        <v>0.8989</v>
       </c>
       <c r="K14" s="8" t="n">
         <v>54</v>
@@ -1327,7 +1327,7 @@
         <v>142</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.753</v>
       </c>
       <c r="K17" s="8" t="n">
         <v>65</v>
@@ -1423,7 +1423,7 @@
         <v>70</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>0.9428</v>
+        <v>0.9425</v>
       </c>
       <c r="K19" s="8" t="n">
         <v>35</v>
@@ -1471,7 +1471,7 @@
         <v>118</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9486</v>
       </c>
       <c r="K20" s="8" t="n">
         <v>60</v>
@@ -1519,7 +1519,7 @@
         <v>70</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>0.9571</v>
+        <v>0.9567</v>
       </c>
       <c r="K21" s="8" t="n">
         <v>35</v>
@@ -1563,7 +1563,7 @@
         <v>1290</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.5151</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>580</v>
@@ -1611,7 +1611,7 @@
         <v>140</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>0.7357</v>
+        <v>0.7138</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>65</v>
@@ -1659,7 +1659,7 @@
         <v>10</v>
       </c>
       <c r="J24" s="11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K24" s="8" t="n">
         <v>5</v>
@@ -1707,7 +1707,7 @@
         <v>100</v>
       </c>
       <c r="J25" s="11" t="n">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="K25" s="8" t="n">
         <v>45</v>
@@ -1755,7 +1755,7 @@
         <v>90</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.7111</v>
+        <v>0.7108</v>
       </c>
       <c r="K26" s="8" t="n">
         <v>40</v>
@@ -1803,7 +1803,7 @@
         <v>150</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>0.9066</v>
+        <v>0.9462</v>
       </c>
       <c r="K27" s="8" t="n">
         <v>75</v>
@@ -1851,7 +1851,7 @@
         <v>10</v>
       </c>
       <c r="J28" s="11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K28" s="8" t="n">
         <v>5</v>
@@ -1899,7 +1899,7 @@
         <v>20</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" s="8" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
         <v>140</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>0.9</v>
+        <v>0.8995</v>
       </c>
       <c r="K31" s="8" t="n">
         <v>70</v>
@@ -2091,7 +2091,7 @@
         <v>101</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>0.29</v>
+        <v>0.9207</v>
       </c>
       <c r="K33" s="8" t="n">
         <v>50</v>
@@ -2139,7 +2139,7 @@
         <v>10</v>
       </c>
       <c r="J34" s="11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K34" s="8" t="n">
         <v>5</v>
@@ -2187,7 +2187,7 @@
         <v>292</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>0.3071</v>
+        <v>0.6261</v>
       </c>
       <c r="K35" s="8" t="n">
         <v>115</v>
@@ -2235,7 +2235,7 @@
         <v>50</v>
       </c>
       <c r="J36" s="11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="K36" s="8" t="n">
         <v>15</v>
@@ -2283,7 +2283,7 @@
         <v>157</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>0.1375</v>
+        <v>0.643</v>
       </c>
       <c r="K37" s="8" t="n">
         <v>70</v>
@@ -2327,7 +2327,7 @@
         <v>401</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>0.9002</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>194</v>
@@ -2375,7 +2375,7 @@
         <v>180</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>0.9888</v>
+        <v>0.9826</v>
       </c>
       <c r="K39" s="8" t="n">
         <v>90</v>
@@ -2471,7 +2471,7 @@
         <v>211</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>0.8199</v>
+        <v>0.8242</v>
       </c>
       <c r="K41" s="8" t="n">
         <v>100</v>
@@ -2515,7 +2515,7 @@
         <v>543</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>0.9391</v>
+        <v>0.9371</v>
       </c>
       <c r="K42" s="5" t="n">
         <v>264</v>
@@ -2563,7 +2563,7 @@
         <v>112</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="K43" s="8" t="n">
         <v>55</v>
@@ -2611,7 +2611,7 @@
         <v>30</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>0.9</v>
+        <v>0.8999</v>
       </c>
       <c r="K44" s="8" t="n">
         <v>15</v>
@@ -2659,7 +2659,7 @@
         <v>60</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>0.8833</v>
+        <v>0.8831</v>
       </c>
       <c r="K45" s="8" t="n">
         <v>30</v>
@@ -2707,7 +2707,7 @@
         <v>141</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>0.9214</v>
+        <v>0.9142</v>
       </c>
       <c r="K46" s="8" t="n">
         <v>69</v>
@@ -2803,7 +2803,7 @@
         <v>30</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="K48" s="8" t="n">
         <v>15</v>
@@ -2851,7 +2851,7 @@
         <v>30</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>0.8333</v>
+        <v>0.8331</v>
       </c>
       <c r="K49" s="8" t="n">
         <v>10</v>
@@ -2991,7 +2991,7 @@
         <v>452</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>0.6704</v>
+        <v>0.6788</v>
       </c>
       <c r="K52" s="5" t="n">
         <v>214</v>
@@ -3039,7 +3039,7 @@
         <v>40</v>
       </c>
       <c r="J53" s="11" t="n">
-        <v>0.5</v>
+        <v>0.475</v>
       </c>
       <c r="K53" s="8" t="n">
         <v>20</v>
@@ -3087,7 +3087,7 @@
         <v>101</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>0.6</v>
+        <v>0.6039</v>
       </c>
       <c r="K54" s="8" t="n">
         <v>45</v>
@@ -3231,7 +3231,7 @@
         <v>130</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>0.6846</v>
+        <v>0.6993</v>
       </c>
       <c r="K57" s="8" t="n">
         <v>59</v>
@@ -3279,7 +3279,7 @@
         <v>161</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>0.7046</v>
+        <v>0.7201</v>
       </c>
       <c r="K58" s="8" t="n">
         <v>80</v>
@@ -3323,7 +3323,7 @@
         <v>866</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>0.8578</v>
+        <v>0.8793</v>
       </c>
       <c r="K59" s="5" t="n">
         <v>400</v>
@@ -3419,7 +3419,7 @@
         <v>30</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7664</v>
       </c>
       <c r="K61" s="8" t="n">
         <v>15</v>
@@ -3611,7 +3611,7 @@
         <v>137</v>
       </c>
       <c r="J65" s="11" t="n">
-        <v>0.6115</v>
+        <v>0.5976</v>
       </c>
       <c r="K65" s="8" t="n">
         <v>35</v>
@@ -3707,7 +3707,7 @@
         <v>70</v>
       </c>
       <c r="J67" s="11" t="n">
-        <v>0.9428</v>
+        <v>0.9424</v>
       </c>
       <c r="K67" s="8" t="n">
         <v>35</v>
@@ -3755,7 +3755,7 @@
         <v>139</v>
       </c>
       <c r="J68" s="11" t="n">
-        <v>0.9</v>
+        <v>0.9272</v>
       </c>
       <c r="K68" s="8" t="n">
         <v>65</v>
@@ -3803,7 +3803,7 @@
         <v>390</v>
       </c>
       <c r="J69" s="11" t="n">
-        <v>0.9102</v>
+        <v>0.9532</v>
       </c>
       <c r="K69" s="8" t="n">
         <v>195</v>
@@ -3847,7 +3847,7 @@
         <v>1000</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>0.475</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="K70" s="5" t="n">
         <v>460</v>
@@ -3943,7 +3943,7 @@
         <v>189</v>
       </c>
       <c r="J72" s="11" t="n">
-        <v>0.19</v>
+        <v>0.9201</v>
       </c>
       <c r="K72" s="8" t="n">
         <v>95</v>
@@ -3991,7 +3991,7 @@
         <v>30</v>
       </c>
       <c r="J73" s="11" t="n">
-        <v>0.6333</v>
+        <v>0.6331</v>
       </c>
       <c r="K73" s="8" t="n">
         <v>15</v>
@@ -4039,7 +4039,7 @@
         <v>130</v>
       </c>
       <c r="J74" s="11" t="n">
-        <v>0.8307</v>
+        <v>0.8223</v>
       </c>
       <c r="K74" s="8" t="n">
         <v>65</v>
@@ -4327,7 +4327,7 @@
         <v>60</v>
       </c>
       <c r="J80" s="11" t="n">
-        <v>0.3166</v>
+        <v>0.9829</v>
       </c>
       <c r="K80" s="8" t="n">
         <v>25</v>
@@ -4423,7 +4423,7 @@
         <v>10</v>
       </c>
       <c r="J82" s="11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K82" s="8" t="n">
         <v>5</v>
@@ -4519,7 +4519,7 @@
         <v>40</v>
       </c>
       <c r="J84" s="11" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="K84" s="8" t="n">
         <v>20</v>
@@ -4567,7 +4567,7 @@
         <v>71</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>0.1142</v>
+        <v>0.7461</v>
       </c>
       <c r="K85" s="8" t="n">
         <v>35</v>
@@ -4615,7 +4615,7 @@
         <v>130</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>0.0387</v>
+        <v>0.1842</v>
       </c>
       <c r="K86" s="8" t="n">
         <v>30</v>
@@ -4663,7 +4663,7 @@
         <v>50</v>
       </c>
       <c r="J87" s="11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="K87" s="8" t="n">
         <v>25</v>
@@ -4755,7 +4755,7 @@
         <v>1000</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>0.6364</v>
+        <v>0.9386</v>
       </c>
       <c r="K89" s="5" t="n">
         <v>509</v>
@@ -4803,7 +4803,7 @@
         <v>109</v>
       </c>
       <c r="J90" s="11" t="n">
-        <v>0.8909</v>
+        <v>0.8894</v>
       </c>
       <c r="K90" s="8" t="n">
         <v>54</v>
@@ -4851,7 +4851,7 @@
         <v>150</v>
       </c>
       <c r="J91" s="11" t="n">
-        <v>0.3687</v>
+        <v>0.9796</v>
       </c>
       <c r="K91" s="8" t="n">
         <v>75</v>
@@ -4947,7 +4947,7 @@
         <v>299</v>
       </c>
       <c r="J93" s="11" t="n">
-        <v>0.8714</v>
+        <v>0.9425</v>
       </c>
       <c r="K93" s="8" t="n">
         <v>155</v>
@@ -4995,7 +4995,7 @@
         <v>261</v>
       </c>
       <c r="J94" s="11" t="n">
-        <v>0.45</v>
+        <v>0.9804</v>
       </c>
       <c r="K94" s="8" t="n">
         <v>130</v>
@@ -5139,7 +5139,7 @@
         <v>21</v>
       </c>
       <c r="J97" s="11" t="n">
-        <v>0</v>
+        <v>0.8092</v>
       </c>
       <c r="K97" s="8" t="n">
         <v>10</v>
@@ -5187,7 +5187,7 @@
         <v>100</v>
       </c>
       <c r="J98" s="11" t="n">
-        <v>0.57</v>
+        <v>0.91</v>
       </c>
       <c r="K98" s="8" t="n">
         <v>55</v>
@@ -5231,7 +5231,7 @@
         <v>155</v>
       </c>
       <c r="J99" s="7" t="n">
-        <v>0.8129</v>
+        <v>0.8127</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>75</v>
@@ -5279,7 +5279,7 @@
         <v>95</v>
       </c>
       <c r="J100" s="11" t="n">
-        <v>0.7052</v>
+        <v>0.7049</v>
       </c>
       <c r="K100" s="8" t="n">
         <v>45</v>
@@ -5419,7 +5419,7 @@
         <v>281</v>
       </c>
       <c r="J103" s="7" t="n">
-        <v>0.8925</v>
+        <v>0.8929</v>
       </c>
       <c r="K103" s="5" t="n">
         <v>135</v>
@@ -5467,7 +5467,7 @@
         <v>140</v>
       </c>
       <c r="J104" s="11" t="n">
-        <v>0.9357</v>
+        <v>0.9353</v>
       </c>
       <c r="K104" s="8" t="n">
         <v>65</v>
@@ -5515,7 +5515,7 @@
         <v>71</v>
       </c>
       <c r="J105" s="11" t="n">
-        <v>0.8</v>
+        <v>0.8023</v>
       </c>
       <c r="K105" s="8" t="n">
         <v>35</v>
@@ -5611,7 +5611,7 @@
         <v>30</v>
       </c>
       <c r="J107" s="11" t="n">
-        <v>0.9</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="K107" s="8" t="n">
         <v>15</v>
@@ -5655,7 +5655,7 @@
         <v>314</v>
       </c>
       <c r="J108" s="7" t="n">
-        <v>0.8328</v>
+        <v>0.834</v>
       </c>
       <c r="K108" s="5" t="n">
         <v>150</v>
@@ -5703,7 +5703,7 @@
         <v>29</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>0.5</v>
+        <v>0.5171</v>
       </c>
       <c r="K109" s="8" t="n">
         <v>10</v>
@@ -5751,7 +5751,7 @@
         <v>120</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9498</v>
       </c>
       <c r="K110" s="8" t="n">
         <v>60</v>
@@ -5799,7 +5799,7 @@
         <v>145</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>0.7931</v>
+        <v>0.7924</v>
       </c>
       <c r="K111" s="8" t="n">
         <v>70</v>
@@ -5939,7 +5939,7 @@
         <v>30</v>
       </c>
       <c r="J114" s="7" t="n">
-        <v>0.6666</v>
+        <v>0.6663</v>
       </c>
       <c r="K114" s="5" t="n">
         <v>15</v>
@@ -5987,7 +5987,7 @@
         <v>30</v>
       </c>
       <c r="J115" s="11" t="n">
-        <v>0.6666</v>
+        <v>0.6663</v>
       </c>
       <c r="K115" s="8" t="n">
         <v>15</v>
@@ -6159,7 +6159,7 @@
         <v>10</v>
       </c>
       <c r="J119" s="11" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K119" s="8" t="n">
         <v>5</v>
@@ -6207,7 +6207,7 @@
         <v>10</v>
       </c>
       <c r="J120" s="11" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K120" s="8" t="n">
         <v>5</v>
@@ -6435,7 +6435,7 @@
         <v>81</v>
       </c>
       <c r="J125" s="7" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.901</v>
       </c>
       <c r="K125" s="5" t="n">
         <v>34</v>
@@ -6483,7 +6483,7 @@
         <v>60</v>
       </c>
       <c r="J126" s="11" t="n">
-        <v>0.8666</v>
+        <v>0.9498</v>
       </c>
       <c r="K126" s="8" t="n">
         <v>29</v>
@@ -6563,7 +6563,7 @@
         <v>21</v>
       </c>
       <c r="J128" s="11" t="n">
-        <v>0.8</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="K128" s="8" t="n">
         <v>5</v>
@@ -6767,7 +6767,7 @@
         <v>8173</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>0.6345</v>
+        <v>0.8091</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>2374</v>
@@ -6903,7 +6903,7 @@
         <v>323</v>
       </c>
       <c r="J136" s="7" t="n">
-        <v>0.7879</v>
+        <v>0.7894</v>
       </c>
       <c r="K136" s="5" t="n">
         <v>80</v>
@@ -7095,7 +7095,7 @@
         <v>63</v>
       </c>
       <c r="J140" s="11" t="n">
-        <v>0.8333</v>
+        <v>0.841</v>
       </c>
       <c r="K140" s="8" t="n">
         <v>15</v>
@@ -7283,7 +7283,7 @@
         <v>1238</v>
       </c>
       <c r="J144" s="7" t="n">
-        <v>0.8418</v>
+        <v>0.8502</v>
       </c>
       <c r="K144" s="5" t="n">
         <v>305</v>
@@ -7331,7 +7331,7 @@
         <v>60</v>
       </c>
       <c r="J145" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9498</v>
       </c>
       <c r="K145" s="8" t="n">
         <v>15</v>
@@ -7379,7 +7379,7 @@
         <v>208</v>
       </c>
       <c r="J146" s="11" t="n">
-        <v>0.8315</v>
+        <v>0.8314</v>
       </c>
       <c r="K146" s="8" t="n">
         <v>40</v>
@@ -7427,7 +7427,7 @@
         <v>180</v>
       </c>
       <c r="J147" s="11" t="n">
-        <v>0.9277</v>
+        <v>0.9273</v>
       </c>
       <c r="K147" s="8" t="n">
         <v>45</v>
@@ -7523,7 +7523,7 @@
         <v>60</v>
       </c>
       <c r="J149" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9497</v>
       </c>
       <c r="K149" s="8" t="n">
         <v>10</v>
@@ -7667,7 +7667,7 @@
         <v>100</v>
       </c>
       <c r="J152" s="11" t="n">
-        <v>0.8363</v>
+        <v>0.9492</v>
       </c>
       <c r="K152" s="8" t="n">
         <v>55</v>
@@ -7715,7 +7715,7 @@
         <v>190</v>
       </c>
       <c r="J153" s="11" t="n">
-        <v>0.8736</v>
+        <v>0.8733</v>
       </c>
       <c r="K153" s="8" t="n">
         <v>45</v>
@@ -7763,7 +7763,7 @@
         <v>130</v>
       </c>
       <c r="J154" s="11" t="n">
-        <v>0.6589</v>
+        <v>0.6534</v>
       </c>
       <c r="K154" s="8" t="n">
         <v>30</v>
@@ -7807,7 +7807,7 @@
         <v>747</v>
       </c>
       <c r="J155" s="7" t="n">
-        <v>0.7712</v>
+        <v>0.7749</v>
       </c>
       <c r="K155" s="5" t="n">
         <v>170</v>
@@ -7903,7 +7903,7 @@
         <v>160</v>
       </c>
       <c r="J157" s="11" t="n">
-        <v>0.775</v>
+        <v>0.7995</v>
       </c>
       <c r="K157" s="8" t="n">
         <v>40</v>
@@ -7951,7 +7951,7 @@
         <v>60</v>
       </c>
       <c r="J158" s="11" t="n">
-        <v>0.8833</v>
+        <v>0.883</v>
       </c>
       <c r="K158" s="8" t="n">
         <v>15</v>
@@ -7999,7 +7999,7 @@
         <v>30</v>
       </c>
       <c r="J159" s="11" t="n">
-        <v>0.5666</v>
+        <v>0.5664</v>
       </c>
       <c r="K159" s="8" t="n">
         <v>5</v>
@@ -8095,7 +8095,7 @@
         <v>199</v>
       </c>
       <c r="J161" s="11" t="n">
-        <v>0.6888</v>
+        <v>0.6831</v>
       </c>
       <c r="K161" s="8" t="n">
         <v>40</v>
@@ -8191,7 +8191,7 @@
         <v>38</v>
       </c>
       <c r="J163" s="11" t="n">
-        <v>0.975</v>
+        <v>0.9735</v>
       </c>
       <c r="K163" s="8" t="n">
         <v>10</v>
@@ -8235,7 +8235,7 @@
         <v>4126</v>
       </c>
       <c r="J164" s="7" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.7825</v>
       </c>
       <c r="K164" s="5" t="n">
         <v>985</v>
@@ -8283,7 +8283,7 @@
         <v>175</v>
       </c>
       <c r="J165" s="11" t="n">
-        <v>0.8742</v>
+        <v>0.874</v>
       </c>
       <c r="K165" s="8" t="n">
         <v>45</v>
@@ -8379,7 +8379,7 @@
         <v>260</v>
       </c>
       <c r="J167" s="11" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.7842</v>
       </c>
       <c r="K167" s="8" t="n">
         <v>55</v>
@@ -8427,7 +8427,7 @@
         <v>81</v>
       </c>
       <c r="J168" s="11" t="n">
-        <v>0.075</v>
+        <v>0.7279</v>
       </c>
       <c r="K168" s="8" t="n">
         <v>20</v>
@@ -8475,7 +8475,7 @@
         <v>160</v>
       </c>
       <c r="J169" s="11" t="n">
-        <v>0.375</v>
+        <v>0.7936</v>
       </c>
       <c r="K169" s="8" t="n">
         <v>40</v>
@@ -8523,7 +8523,7 @@
         <v>80</v>
       </c>
       <c r="J170" s="11" t="n">
-        <v>0.4375</v>
+        <v>0.4625</v>
       </c>
       <c r="K170" s="8" t="n">
         <v>15</v>
@@ -8571,7 +8571,7 @@
         <v>59</v>
       </c>
       <c r="J171" s="11" t="n">
-        <v>0.7333</v>
+        <v>0.7285</v>
       </c>
       <c r="K171" s="8" t="n">
         <v>15</v>
@@ -8619,7 +8619,7 @@
         <v>280</v>
       </c>
       <c r="J172" s="11" t="n">
-        <v>0.7714</v>
+        <v>0.771</v>
       </c>
       <c r="K172" s="8" t="n">
         <v>65</v>
@@ -8667,7 +8667,7 @@
         <v>160</v>
       </c>
       <c r="J173" s="11" t="n">
-        <v>0.8148</v>
+        <v>0.8434</v>
       </c>
       <c r="K173" s="8" t="n">
         <v>40</v>
@@ -8811,7 +8811,7 @@
         <v>60</v>
       </c>
       <c r="J176" s="11" t="n">
-        <v>0.9</v>
+        <v>0.9163</v>
       </c>
       <c r="K176" s="8" t="n">
         <v>15</v>
@@ -8859,7 +8859,7 @@
         <v>79</v>
       </c>
       <c r="J177" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9489</v>
       </c>
       <c r="K177" s="8" t="n">
         <v>15</v>
@@ -9003,7 +9003,7 @@
         <v>60</v>
       </c>
       <c r="J180" s="11" t="n">
-        <v>0.8833</v>
+        <v>0.8829</v>
       </c>
       <c r="K180" s="8" t="n">
         <v>15</v>
@@ -9051,7 +9051,7 @@
         <v>180</v>
       </c>
       <c r="J181" s="11" t="n">
-        <v>0</v>
+        <v>0.8107</v>
       </c>
       <c r="K181" s="8" t="n">
         <v>40</v>
@@ -9147,7 +9147,7 @@
         <v>200</v>
       </c>
       <c r="J183" s="11" t="n">
-        <v>0.7909</v>
+        <v>0.795</v>
       </c>
       <c r="K183" s="8" t="n">
         <v>50</v>
@@ -9195,7 +9195,7 @@
         <v>198</v>
       </c>
       <c r="J184" s="11" t="n">
-        <v>0.76</v>
+        <v>0.7621</v>
       </c>
       <c r="K184" s="8" t="n">
         <v>50</v>
@@ -9243,7 +9243,7 @@
         <v>99</v>
       </c>
       <c r="J185" s="11" t="n">
-        <v>0.88</v>
+        <v>0.8787</v>
       </c>
       <c r="K185" s="8" t="n">
         <v>20</v>
@@ -9339,7 +9339,7 @@
         <v>41</v>
       </c>
       <c r="J187" s="11" t="n">
-        <v>0.85</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="K187" s="8" t="n">
         <v>10</v>
@@ -9387,7 +9387,7 @@
         <v>59</v>
       </c>
       <c r="J188" s="11" t="n">
-        <v>0.6833</v>
+        <v>0.6604</v>
       </c>
       <c r="K188" s="8" t="n">
         <v>15</v>
@@ -9435,7 +9435,7 @@
         <v>278</v>
       </c>
       <c r="J189" s="11" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7762</v>
       </c>
       <c r="K189" s="8" t="n">
         <v>70</v>
@@ -9483,7 +9483,7 @@
         <v>293</v>
       </c>
       <c r="J190" s="11" t="n">
-        <v>0</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="K190" s="8" t="n">
         <v>70</v>
@@ -9531,7 +9531,7 @@
         <v>416</v>
       </c>
       <c r="J191" s="11" t="n">
-        <v>0.4428</v>
+        <v>0.6343</v>
       </c>
       <c r="K191" s="8" t="n">
         <v>90</v>
@@ -9579,7 +9579,7 @@
         <v>110</v>
       </c>
       <c r="J192" s="11" t="n">
-        <v>0.1</v>
+        <v>0.5907</v>
       </c>
       <c r="K192" s="8" t="n">
         <v>20</v>
@@ -9627,7 +9627,7 @@
         <v>139</v>
       </c>
       <c r="J193" s="11" t="n">
-        <v>0</v>
+        <v>0.7479</v>
       </c>
       <c r="K193" s="8" t="n">
         <v>40</v>
@@ -9675,7 +9675,7 @@
         <v>80</v>
       </c>
       <c r="J194" s="11" t="n">
-        <v>0.73</v>
+        <v>0.875</v>
       </c>
       <c r="K194" s="8" t="n">
         <v>25</v>
@@ -9723,7 +9723,7 @@
         <v>120</v>
       </c>
       <c r="J195" s="11" t="n">
-        <v>0.675</v>
+        <v>0.858</v>
       </c>
       <c r="K195" s="8" t="n">
         <v>30</v>
@@ -9771,7 +9771,7 @@
         <v>99</v>
       </c>
       <c r="J196" s="11" t="n">
-        <v>0.7</v>
+        <v>0.8787</v>
       </c>
       <c r="K196" s="8" t="n">
         <v>25</v>
@@ -9819,7 +9819,7 @@
         <v>140</v>
       </c>
       <c r="J197" s="11" t="n">
-        <v>0.1357</v>
+        <v>0.8354</v>
       </c>
       <c r="K197" s="8" t="n">
         <v>35</v>
@@ -9863,7 +9863,7 @@
         <v>219</v>
       </c>
       <c r="J198" s="7" t="n">
-        <v>0</v>
+        <v>0.9404</v>
       </c>
       <c r="K198" s="5" t="n">
         <v>55</v>
@@ -9911,7 +9911,7 @@
         <v>139</v>
       </c>
       <c r="J199" s="11" t="n">
-        <v>0</v>
+        <v>0.9564</v>
       </c>
       <c r="K199" s="8" t="n">
         <v>35</v>
@@ -9959,7 +9959,7 @@
         <v>80</v>
       </c>
       <c r="J200" s="11" t="n">
-        <v>0</v>
+        <v>0.9125</v>
       </c>
       <c r="K200" s="8" t="n">
         <v>20</v>
@@ -10003,7 +10003,7 @@
         <v>1200</v>
       </c>
       <c r="J201" s="7" t="n">
-        <v>0.7716</v>
+        <v>0.8599</v>
       </c>
       <c r="K201" s="5" t="n">
         <v>435</v>
@@ -10051,7 +10051,7 @@
         <v>119</v>
       </c>
       <c r="J202" s="11" t="n">
-        <v>0.9583</v>
+        <v>0.9577</v>
       </c>
       <c r="K202" s="8" t="n">
         <v>30</v>
@@ -10099,7 +10099,7 @@
         <v>40</v>
       </c>
       <c r="J203" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203" s="8" t="n">
         <v>10</v>
@@ -10147,7 +10147,7 @@
         <v>19</v>
       </c>
       <c r="J204" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="K204" s="8" t="n">
         <v>5</v>
@@ -10291,7 +10291,7 @@
         <v>40</v>
       </c>
       <c r="J207" s="11" t="n">
-        <v>0.8</v>
+        <v>0.825</v>
       </c>
       <c r="K207" s="8" t="n">
         <v>10</v>
@@ -10339,7 +10339,7 @@
         <v>100</v>
       </c>
       <c r="J208" s="11" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="K208" s="8" t="n">
         <v>25</v>
@@ -10387,7 +10387,7 @@
         <v>141</v>
       </c>
       <c r="J209" s="11" t="n">
-        <v>0.8071</v>
+        <v>0.9144</v>
       </c>
       <c r="K209" s="8" t="n">
         <v>35</v>
@@ -10435,7 +10435,7 @@
         <v>100</v>
       </c>
       <c r="J210" s="11" t="n">
-        <v>0.7433999999999999</v>
+        <v>0.7431</v>
       </c>
       <c r="K210" s="8" t="n">
         <v>160</v>
@@ -10483,7 +10483,7 @@
         <v>381</v>
       </c>
       <c r="J211" s="11" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.8313</v>
       </c>
       <c r="K211" s="8" t="n">
         <v>95</v>
@@ -10531,7 +10531,7 @@
         <v>40</v>
       </c>
       <c r="J212" s="11" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K212" s="8" t="n">
         <v>10</v>
@@ -10667,7 +10667,7 @@
         <v>200</v>
       </c>
       <c r="J215" s="7" t="n">
-        <v>0.8197</v>
+        <v>0.8192</v>
       </c>
       <c r="K215" s="5" t="n">
         <v>314</v>
@@ -10715,7 +10715,7 @@
         <v>60</v>
       </c>
       <c r="J216" s="11" t="n">
-        <v>0.8</v>
+        <v>0.7998</v>
       </c>
       <c r="K216" s="8" t="n">
         <v>10</v>
@@ -10763,7 +10763,7 @@
         <v>20</v>
       </c>
       <c r="J217" s="11" t="n">
-        <v>0.925</v>
+        <v>0.85</v>
       </c>
       <c r="K217" s="8" t="n">
         <v>5</v>
@@ -10811,7 +10811,7 @@
         <v>100</v>
       </c>
       <c r="J218" s="11" t="n">
-        <v>0.8044</v>
+        <v>0.8185</v>
       </c>
       <c r="K218" s="8" t="n">
         <v>294</v>
@@ -10907,7 +10907,7 @@
         <v>3382</v>
       </c>
       <c r="J220" s="4" t="n">
-        <v>0.762</v>
+        <v>0.837</v>
       </c>
       <c r="K220" s="2" t="n">
         <v>833</v>
@@ -10951,7 +10951,7 @@
         <v>60</v>
       </c>
       <c r="J221" s="7" t="n">
-        <v>0.7166</v>
+        <v>0.7163</v>
       </c>
       <c r="K221" s="5" t="n">
         <v>15</v>
@@ -10999,7 +10999,7 @@
         <v>60</v>
       </c>
       <c r="J222" s="11" t="n">
-        <v>0.7166</v>
+        <v>0.7163</v>
       </c>
       <c r="K222" s="8" t="n">
         <v>15</v>
@@ -11043,7 +11043,7 @@
         <v>20</v>
       </c>
       <c r="J223" s="7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K223" s="5" t="n">
         <v>5</v>
@@ -11091,7 +11091,7 @@
         <v>20</v>
       </c>
       <c r="J224" s="11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K224" s="8" t="n">
         <v>5</v>
@@ -11135,7 +11135,7 @@
         <v>140</v>
       </c>
       <c r="J225" s="7" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9429</v>
       </c>
       <c r="K225" s="5" t="n">
         <v>35</v>
@@ -11183,7 +11183,7 @@
         <v>100</v>
       </c>
       <c r="J226" s="11" t="n">
-        <v>0.9333</v>
+        <v>0.95</v>
       </c>
       <c r="K226" s="8" t="n">
         <v>25</v>
@@ -11275,7 +11275,7 @@
         <v>522</v>
       </c>
       <c r="J228" s="7" t="n">
-        <v>0.9096</v>
+        <v>0.9076</v>
       </c>
       <c r="K228" s="5" t="n">
         <v>130</v>
@@ -11371,7 +11371,7 @@
         <v>241</v>
       </c>
       <c r="J230" s="11" t="n">
-        <v>0.9458</v>
+        <v>0.9411</v>
       </c>
       <c r="K230" s="8" t="n">
         <v>60</v>
@@ -11419,7 +11419,7 @@
         <v>201</v>
       </c>
       <c r="J231" s="11" t="n">
-        <v>0.86</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="K231" s="8" t="n">
         <v>50</v>
@@ -11463,7 +11463,7 @@
         <v>608</v>
       </c>
       <c r="J232" s="7" t="n">
-        <v>0.7508</v>
+        <v>0.7742</v>
       </c>
       <c r="K232" s="5" t="n">
         <v>135</v>
@@ -11511,7 +11511,7 @@
         <v>45</v>
       </c>
       <c r="J233" s="11" t="n">
-        <v>0.525</v>
+        <v>0.533</v>
       </c>
       <c r="K233" s="8" t="n">
         <v>5</v>
@@ -11655,7 +11655,7 @@
         <v>140</v>
       </c>
       <c r="J236" s="11" t="n">
-        <v>0.3571</v>
+        <v>0.4212</v>
       </c>
       <c r="K236" s="8" t="n">
         <v>25</v>
@@ -11703,7 +11703,7 @@
         <v>209</v>
       </c>
       <c r="J237" s="11" t="n">
-        <v>0.9454</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="K237" s="8" t="n">
         <v>50</v>
@@ -11751,7 +11751,7 @@
         <v>174</v>
       </c>
       <c r="J238" s="11" t="n">
-        <v>0.8351</v>
+        <v>0.8673</v>
       </c>
       <c r="K238" s="8" t="n">
         <v>45</v>
@@ -11795,7 +11795,7 @@
         <v>703</v>
       </c>
       <c r="J239" s="7" t="n">
-        <v>0.8763</v>
+        <v>0.8942</v>
       </c>
       <c r="K239" s="5" t="n">
         <v>160</v>
@@ -11843,7 +11843,7 @@
         <v>241</v>
       </c>
       <c r="J240" s="11" t="n">
-        <v>0.8272</v>
+        <v>0.8376</v>
       </c>
       <c r="K240" s="8" t="n">
         <v>55</v>
@@ -11891,7 +11891,7 @@
         <v>290</v>
       </c>
       <c r="J241" s="11" t="n">
-        <v>0.9517</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="K241" s="8" t="n">
         <v>70</v>
@@ -11981,7 +11981,7 @@
         <v>20</v>
       </c>
       <c r="J243" s="11" t="n">
-        <v>0.55</v>
+        <v>0.95</v>
       </c>
       <c r="K243" s="8" t="n">
         <v>5</v>
@@ -12029,7 +12029,7 @@
         <v>132</v>
       </c>
       <c r="J244" s="11" t="n">
-        <v>0.8384</v>
+        <v>0.8557</v>
       </c>
       <c r="K244" s="8" t="n">
         <v>30</v>
@@ -12073,7 +12073,7 @@
         <v>439</v>
       </c>
       <c r="J245" s="7" t="n">
-        <v>0.2632</v>
+        <v>0.7539</v>
       </c>
       <c r="K245" s="5" t="n">
         <v>134</v>
@@ -12121,7 +12121,7 @@
         <v>60</v>
       </c>
       <c r="J246" s="11" t="n">
-        <v>0</v>
+        <v>0.7166</v>
       </c>
       <c r="K246" s="8" t="n">
         <v>39</v>
@@ -12169,7 +12169,7 @@
         <v>79</v>
       </c>
       <c r="J247" s="11" t="n">
-        <v>0.4375</v>
+        <v>0.7593</v>
       </c>
       <c r="K247" s="8" t="n">
         <v>20</v>
@@ -12217,7 +12217,7 @@
         <v>160</v>
       </c>
       <c r="J248" s="11" t="n">
-        <v>0</v>
+        <v>0.7499</v>
       </c>
       <c r="K248" s="8" t="n">
         <v>40</v>
@@ -12265,7 +12265,7 @@
         <v>40</v>
       </c>
       <c r="J249" s="11" t="n">
-        <v>0</v>
+        <v>0.675</v>
       </c>
       <c r="K249" s="8" t="n">
         <v>10</v>
@@ -12357,7 +12357,7 @@
         <v>460</v>
       </c>
       <c r="J251" s="7" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8451</v>
       </c>
       <c r="K251" s="5" t="n">
         <v>120</v>
@@ -12405,7 +12405,7 @@
         <v>340</v>
       </c>
       <c r="J252" s="11" t="n">
-        <v>0.8411</v>
+        <v>0.8406</v>
       </c>
       <c r="K252" s="8" t="n">
         <v>90</v>
@@ -12453,7 +12453,7 @@
         <v>120</v>
       </c>
       <c r="J253" s="11" t="n">
-        <v>0.8454</v>
+        <v>0.858</v>
       </c>
       <c r="K253" s="8" t="n">
         <v>30</v>
@@ -12497,7 +12497,7 @@
         <v>430</v>
       </c>
       <c r="J254" s="7" t="n">
-        <v>0.7983</v>
+        <v>0.8065</v>
       </c>
       <c r="K254" s="5" t="n">
         <v>99</v>
@@ -12545,7 +12545,7 @@
         <v>330</v>
       </c>
       <c r="J255" s="11" t="n">
-        <v>0.7948</v>
+        <v>0.8055</v>
       </c>
       <c r="K255" s="8" t="n">
         <v>79</v>
@@ -12737,7 +12737,7 @@
         <v>7405</v>
       </c>
       <c r="J259" s="4" t="n">
-        <v>0.7672</v>
+        <v>0.9396</v>
       </c>
       <c r="K259" s="2" t="n">
         <v>3694</v>
@@ -12873,7 +12873,7 @@
         <v>1842</v>
       </c>
       <c r="J262" s="7" t="n">
-        <v>0.8434</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="K262" s="5" t="n">
         <v>914</v>
@@ -12921,7 +12921,7 @@
         <v>80</v>
       </c>
       <c r="J263" s="11" t="n">
-        <v>0.2777</v>
+        <v>0.85</v>
       </c>
       <c r="K263" s="8" t="n">
         <v>35</v>
@@ -12969,7 +12969,7 @@
         <v>40</v>
       </c>
       <c r="J264" s="11" t="n">
-        <v>0.475</v>
+        <v>0.875</v>
       </c>
       <c r="K264" s="8" t="n">
         <v>20</v>
@@ -13017,7 +13017,7 @@
         <v>52</v>
       </c>
       <c r="J265" s="11" t="n">
-        <v>0.98</v>
+        <v>0.9804</v>
       </c>
       <c r="K265" s="8" t="n">
         <v>24</v>
@@ -13065,7 +13065,7 @@
         <v>69</v>
       </c>
       <c r="J266" s="11" t="n">
-        <v>0.9714</v>
+        <v>0.9704</v>
       </c>
       <c r="K266" s="8" t="n">
         <v>35</v>
@@ -13113,7 +13113,7 @@
         <v>120</v>
       </c>
       <c r="J267" s="11" t="n">
-        <v>0.9666</v>
+        <v>0.983</v>
       </c>
       <c r="K267" s="8" t="n">
         <v>60</v>
@@ -13161,7 +13161,7 @@
         <v>70</v>
       </c>
       <c r="J268" s="11" t="n">
-        <v>0.8833</v>
+        <v>0.8851</v>
       </c>
       <c r="K268" s="8" t="n">
         <v>35</v>
@@ -13209,7 +13209,7 @@
         <v>369</v>
       </c>
       <c r="J269" s="11" t="n">
-        <v>0.9621</v>
+        <v>0.9858</v>
       </c>
       <c r="K269" s="8" t="n">
         <v>185</v>
@@ -13257,7 +13257,7 @@
         <v>10</v>
       </c>
       <c r="J270" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K270" s="8" t="n">
         <v>5</v>
@@ -13305,7 +13305,7 @@
         <v>110</v>
       </c>
       <c r="J271" s="11" t="n">
-        <v>0.7181</v>
+        <v>0.9902</v>
       </c>
       <c r="K271" s="8" t="n">
         <v>55</v>
@@ -13353,7 +13353,7 @@
         <v>110</v>
       </c>
       <c r="J272" s="11" t="n">
-        <v>0.9727</v>
+        <v>0.9719</v>
       </c>
       <c r="K272" s="8" t="n">
         <v>55</v>
@@ -13401,7 +13401,7 @@
         <v>90</v>
       </c>
       <c r="J273" s="11" t="n">
-        <v>0.9777</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K273" s="8" t="n">
         <v>50</v>
@@ -13449,7 +13449,7 @@
         <v>60</v>
       </c>
       <c r="J274" s="11" t="n">
-        <v>0.9</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="K274" s="8" t="n">
         <v>30</v>
@@ -13497,7 +13497,7 @@
         <v>121</v>
       </c>
       <c r="J275" s="11" t="n">
-        <v>0.8914</v>
+        <v>0.8921</v>
       </c>
       <c r="K275" s="8" t="n">
         <v>60</v>
@@ -13545,7 +13545,7 @@
         <v>80</v>
       </c>
       <c r="J276" s="11" t="n">
-        <v>0.9428</v>
+        <v>0.95</v>
       </c>
       <c r="K276" s="8" t="n">
         <v>40</v>
@@ -13689,7 +13689,7 @@
         <v>50</v>
       </c>
       <c r="J279" s="11" t="n">
-        <v>0.2</v>
+        <v>0.98</v>
       </c>
       <c r="K279" s="8" t="n">
         <v>25</v>
@@ -13737,7 +13737,7 @@
         <v>10</v>
       </c>
       <c r="J280" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K280" s="8" t="n">
         <v>5</v>
@@ -13785,7 +13785,7 @@
         <v>119</v>
       </c>
       <c r="J281" s="11" t="n">
-        <v>0.9666</v>
+        <v>0.9577</v>
       </c>
       <c r="K281" s="8" t="n">
         <v>55</v>
@@ -13833,7 +13833,7 @@
         <v>70</v>
       </c>
       <c r="J282" s="11" t="n">
-        <v>0.9714</v>
+        <v>0.9709</v>
       </c>
       <c r="K282" s="8" t="n">
         <v>35</v>
@@ -13881,7 +13881,7 @@
         <v>51</v>
       </c>
       <c r="J283" s="11" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="K283" s="8" t="n">
         <v>25</v>
@@ -13929,7 +13929,7 @@
         <v>30</v>
       </c>
       <c r="J284" s="11" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="K284" s="8" t="n">
         <v>15</v>
@@ -14025,7 +14025,7 @@
         <v>61</v>
       </c>
       <c r="J286" s="11" t="n">
-        <v>0.15</v>
+        <v>0.9503</v>
       </c>
       <c r="K286" s="8" t="n">
         <v>30</v>
@@ -14069,7 +14069,7 @@
         <v>660</v>
       </c>
       <c r="J287" s="7" t="n">
-        <v>0.2906</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="K287" s="5" t="n">
         <v>343</v>
@@ -14117,7 +14117,7 @@
         <v>11</v>
       </c>
       <c r="J288" s="11" t="n">
-        <v>0</v>
+        <v>0.909</v>
       </c>
       <c r="K288" s="8" t="n">
         <v>5</v>
@@ -14165,7 +14165,7 @@
         <v>80</v>
       </c>
       <c r="J289" s="11" t="n">
-        <v>0.2625</v>
+        <v>0.65</v>
       </c>
       <c r="K289" s="8" t="n">
         <v>40</v>
@@ -14213,7 +14213,7 @@
         <v>120</v>
       </c>
       <c r="J290" s="11" t="n">
-        <v>0.4153</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K290" s="8" t="n">
         <v>65</v>
@@ -14261,7 +14261,7 @@
         <v>70</v>
       </c>
       <c r="J291" s="11" t="n">
-        <v>0.2857</v>
+        <v>0.9566</v>
       </c>
       <c r="K291" s="8" t="n">
         <v>35</v>
@@ -14309,7 +14309,7 @@
         <v>80</v>
       </c>
       <c r="J292" s="11" t="n">
-        <v>0.125</v>
+        <v>1</v>
       </c>
       <c r="K292" s="8" t="n">
         <v>40</v>
@@ -14357,7 +14357,7 @@
         <v>199</v>
       </c>
       <c r="J293" s="11" t="n">
-        <v>0.1857</v>
+        <v>0.8137</v>
       </c>
       <c r="K293" s="8" t="n">
         <v>108</v>
@@ -14405,7 +14405,7 @@
         <v>100</v>
       </c>
       <c r="J294" s="11" t="n">
-        <v>0.54</v>
+        <v>0.91</v>
       </c>
       <c r="K294" s="8" t="n">
         <v>50</v>
@@ -14449,7 +14449,7 @@
         <v>1409</v>
       </c>
       <c r="J295" s="7" t="n">
-        <v>0.4896</v>
+        <v>0.9081</v>
       </c>
       <c r="K295" s="5" t="n">
         <v>697</v>
@@ -14497,7 +14497,7 @@
         <v>90</v>
       </c>
       <c r="J296" s="11" t="n">
-        <v>0.73</v>
+        <v>0.8774</v>
       </c>
       <c r="K296" s="8" t="n">
         <v>50</v>
@@ -14545,7 +14545,7 @@
         <v>30</v>
       </c>
       <c r="J297" s="11" t="n">
-        <v>0.2666</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="K297" s="8" t="n">
         <v>20</v>
@@ -14593,7 +14593,7 @@
         <v>20</v>
       </c>
       <c r="J298" s="11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K298" s="8" t="n">
         <v>10</v>
@@ -14641,7 +14641,7 @@
         <v>19</v>
       </c>
       <c r="J299" s="11" t="n">
-        <v>0.65</v>
+        <v>0.6314</v>
       </c>
       <c r="K299" s="8" t="n">
         <v>5</v>
@@ -14689,7 +14689,7 @@
         <v>101</v>
       </c>
       <c r="J300" s="11" t="n">
-        <v>0.15</v>
+        <v>0.6435</v>
       </c>
       <c r="K300" s="8" t="n">
         <v>45</v>
@@ -14737,7 +14737,7 @@
         <v>100</v>
       </c>
       <c r="J301" s="11" t="n">
-        <v>0.38</v>
+        <v>0.91</v>
       </c>
       <c r="K301" s="8" t="n">
         <v>50</v>
@@ -14785,7 +14785,7 @@
         <v>130</v>
       </c>
       <c r="J302" s="11" t="n">
-        <v>0.325</v>
+        <v>0.8534</v>
       </c>
       <c r="K302" s="8" t="n">
         <v>65</v>
@@ -14833,7 +14833,7 @@
         <v>20</v>
       </c>
       <c r="J303" s="11" t="n">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="K303" s="8" t="n">
         <v>10</v>
@@ -14881,7 +14881,7 @@
         <v>310</v>
       </c>
       <c r="J304" s="11" t="n">
-        <v>0.5096000000000001</v>
+        <v>0.9802</v>
       </c>
       <c r="K304" s="8" t="n">
         <v>150</v>
@@ -14929,7 +14929,7 @@
         <v>50</v>
       </c>
       <c r="J305" s="11" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="K305" s="8" t="n">
         <v>25</v>
@@ -15025,7 +15025,7 @@
         <v>110</v>
       </c>
       <c r="J307" s="11" t="n">
-        <v>0.7454</v>
+        <v>0.9176</v>
       </c>
       <c r="K307" s="8" t="n">
         <v>60</v>
@@ -15073,7 +15073,7 @@
         <v>210</v>
       </c>
       <c r="J308" s="11" t="n">
-        <v>0.7571</v>
+        <v>0.9757</v>
       </c>
       <c r="K308" s="8" t="n">
         <v>98</v>
@@ -15121,7 +15121,7 @@
         <v>79</v>
       </c>
       <c r="J309" s="11" t="n">
-        <v>0.575</v>
+        <v>0.9488</v>
       </c>
       <c r="K309" s="8" t="n">
         <v>40</v>
@@ -15169,7 +15169,7 @@
         <v>110</v>
       </c>
       <c r="J310" s="11" t="n">
-        <v>0.3363</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="K310" s="8" t="n">
         <v>54</v>
@@ -15217,7 +15217,7 @@
         <v>10</v>
       </c>
       <c r="J311" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K311" s="8" t="n">
         <v>5</v>
@@ -15261,7 +15261,7 @@
         <v>1475</v>
       </c>
       <c r="J312" s="7" t="n">
-        <v>0.9764</v>
+        <v>0.9772</v>
       </c>
       <c r="K312" s="5" t="n">
         <v>735</v>
@@ -15549,7 +15549,7 @@
         <v>81</v>
       </c>
       <c r="J318" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9502</v>
       </c>
       <c r="K318" s="8" t="n">
         <v>40</v>
@@ -15597,7 +15597,7 @@
         <v>141</v>
       </c>
       <c r="J319" s="11" t="n">
-        <v>0.9928</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="K319" s="8" t="n">
         <v>70</v>
@@ -15645,7 +15645,7 @@
         <v>499</v>
       </c>
       <c r="J320" s="11" t="n">
-        <v>0.9714</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="K320" s="8" t="n">
         <v>250</v>
@@ -15741,7 +15741,7 @@
         <v>70</v>
       </c>
       <c r="J322" s="11" t="n">
-        <v>0.9571</v>
+        <v>0.9566</v>
       </c>
       <c r="K322" s="8" t="n">
         <v>35</v>
@@ -15837,7 +15837,7 @@
         <v>30</v>
       </c>
       <c r="J324" s="11" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="K324" s="8" t="n">
         <v>15</v>
@@ -15885,7 +15885,7 @@
         <v>18</v>
       </c>
       <c r="J325" s="11" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="K325" s="8" t="n">
         <v>10</v>
@@ -16077,7 +16077,7 @@
         <v>30</v>
       </c>
       <c r="J329" s="11" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="K329" s="8" t="n">
         <v>15</v>
@@ -16173,7 +16173,7 @@
         <v>30</v>
       </c>
       <c r="J331" s="11" t="n">
-        <v>0.9666</v>
+        <v>0.9664</v>
       </c>
       <c r="K331" s="8" t="n">
         <v>10</v>
@@ -16413,7 +16413,7 @@
         <v>60</v>
       </c>
       <c r="J336" s="11" t="n">
-        <v>0.9929</v>
+        <v>0.983</v>
       </c>
       <c r="K336" s="8" t="n">
         <v>30</v>
@@ -16461,7 +16461,7 @@
         <v>30</v>
       </c>
       <c r="J337" s="11" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="K337" s="8" t="n">
         <v>15</v>
@@ -16509,7 +16509,7 @@
         <v>30</v>
       </c>
       <c r="J338" s="11" t="n">
-        <v>0.9666</v>
+        <v>0.9664</v>
       </c>
       <c r="K338" s="8" t="n">
         <v>15</v>
@@ -16557,7 +16557,7 @@
         <v>50</v>
       </c>
       <c r="J339" s="11" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="K339" s="8" t="n">
         <v>25</v>
@@ -16605,7 +16605,7 @@
         <v>30</v>
       </c>
       <c r="J340" s="11" t="n">
-        <v>1</v>
+        <v>0.9998</v>
       </c>
       <c r="K340" s="8" t="n">
         <v>15</v>
@@ -16649,7 +16649,7 @@
         <v>411</v>
       </c>
       <c r="J341" s="7" t="n">
-        <v>0.6226</v>
+        <v>0.8731</v>
       </c>
       <c r="K341" s="5" t="n">
         <v>205</v>
@@ -16697,7 +16697,7 @@
         <v>161</v>
       </c>
       <c r="J342" s="11" t="n">
-        <v>0.5379</v>
+        <v>0.745</v>
       </c>
       <c r="K342" s="8" t="n">
         <v>80</v>
@@ -16745,7 +16745,7 @@
         <v>10</v>
       </c>
       <c r="J343" s="11" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K343" s="8" t="n">
         <v>5</v>
@@ -16793,7 +16793,7 @@
         <v>60</v>
       </c>
       <c r="J344" s="11" t="n">
-        <v>0.5714</v>
+        <v>0.9663</v>
       </c>
       <c r="K344" s="8" t="n">
         <v>30</v>
@@ -16841,7 +16841,7 @@
         <v>150</v>
       </c>
       <c r="J345" s="11" t="n">
-        <v>0.8333</v>
+        <v>0.9661</v>
       </c>
       <c r="K345" s="8" t="n">
         <v>75</v>
@@ -16889,7 +16889,7 @@
         <v>20</v>
       </c>
       <c r="J346" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K346" s="8" t="n">
         <v>10</v>
@@ -16937,7 +16937,7 @@
         <v>10</v>
       </c>
       <c r="J347" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K347" s="8" t="n">
         <v>5</v>
@@ -16981,7 +16981,7 @@
         <v>1529</v>
       </c>
       <c r="J348" s="7" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.959</v>
       </c>
       <c r="K348" s="5" t="n">
         <v>760</v>
@@ -17125,7 +17125,7 @@
         <v>182</v>
       </c>
       <c r="J351" s="11" t="n">
-        <v>0.9425</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="K351" s="8" t="n">
         <v>85</v>
@@ -17221,7 +17221,7 @@
         <v>387</v>
       </c>
       <c r="J353" s="11" t="n">
-        <v>0.9615</v>
+        <v>0.9606</v>
       </c>
       <c r="K353" s="8" t="n">
         <v>199</v>
@@ -17269,7 +17269,7 @@
         <v>70</v>
       </c>
       <c r="J354" s="11" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="K354" s="8" t="n">
         <v>35</v>
@@ -17365,7 +17365,7 @@
         <v>59</v>
       </c>
       <c r="J356" s="11" t="n">
-        <v>1</v>
+        <v>0.9992</v>
       </c>
       <c r="K356" s="8" t="n">
         <v>30</v>
@@ -17413,7 +17413,7 @@
         <v>81</v>
       </c>
       <c r="J357" s="11" t="n">
-        <v>0.9375</v>
+        <v>0.9377</v>
       </c>
       <c r="K357" s="8" t="n">
         <v>35</v>
@@ -17461,7 +17461,7 @@
         <v>60</v>
       </c>
       <c r="J358" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9497</v>
       </c>
       <c r="K358" s="8" t="n">
         <v>30</v>
@@ -17509,7 +17509,7 @@
         <v>100</v>
       </c>
       <c r="J359" s="11" t="n">
-        <v>0.9666</v>
+        <v>0.97</v>
       </c>
       <c r="K359" s="8" t="n">
         <v>51</v>
@@ -17605,7 +17605,7 @@
         <v>60</v>
       </c>
       <c r="J361" s="11" t="n">
-        <v>0.9</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="K361" s="8" t="n">
         <v>30</v>
@@ -17653,7 +17653,7 @@
         <v>30</v>
       </c>
       <c r="J362" s="11" t="n">
-        <v>0.9666</v>
+        <v>0.9665</v>
       </c>
       <c r="K362" s="8" t="n">
         <v>15</v>
@@ -17797,7 +17797,7 @@
         <v>81</v>
       </c>
       <c r="J365" s="11" t="n">
-        <v>0.9125</v>
+        <v>0.9131</v>
       </c>
       <c r="K365" s="8" t="n">
         <v>40</v>
@@ -17845,7 +17845,7 @@
         <v>59</v>
       </c>
       <c r="J366" s="11" t="n">
-        <v>1</v>
+        <v>0.9993</v>
       </c>
       <c r="K366" s="8" t="n">
         <v>30</v>
@@ -17893,7 +17893,7 @@
         <v>70</v>
       </c>
       <c r="J367" s="11" t="n">
-        <v>0.9857</v>
+        <v>0.9849</v>
       </c>
       <c r="K367" s="8" t="n">
         <v>35</v>
@@ -17937,7 +17937,7 @@
         <v>69</v>
       </c>
       <c r="J368" s="7" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="K368" s="5" t="n">
         <v>35</v>
@@ -17985,7 +17985,7 @@
         <v>69</v>
       </c>
       <c r="J369" s="11" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="K369" s="8" t="n">
         <v>35</v>
@@ -18033,7 +18033,7 @@
         <v>4559</v>
       </c>
       <c r="J370" s="4" t="n">
-        <v>0.6481</v>
+        <v>0.8364</v>
       </c>
       <c r="K370" s="2" t="n">
         <v>2268</v>
@@ -18169,7 +18169,7 @@
         <v>240</v>
       </c>
       <c r="J373" s="7" t="n">
-        <v>0.8833</v>
+        <v>0.9162</v>
       </c>
       <c r="K373" s="5" t="n">
         <v>125</v>
@@ -18265,7 +18265,7 @@
         <v>190</v>
       </c>
       <c r="J375" s="11" t="n">
-        <v>0.8894</v>
+        <v>0.931</v>
       </c>
       <c r="K375" s="8" t="n">
         <v>100</v>
@@ -18309,7 +18309,7 @@
         <v>89</v>
       </c>
       <c r="J376" s="7" t="n">
-        <v>0.9111</v>
+        <v>0.9095</v>
       </c>
       <c r="K376" s="5" t="n">
         <v>45</v>
@@ -18357,7 +18357,7 @@
         <v>89</v>
       </c>
       <c r="J377" s="11" t="n">
-        <v>0.9111</v>
+        <v>0.9095</v>
       </c>
       <c r="K377" s="8" t="n">
         <v>45</v>
@@ -18401,7 +18401,7 @@
         <v>1314</v>
       </c>
       <c r="J378" s="7" t="n">
-        <v>0.7772</v>
+        <v>0.8405</v>
       </c>
       <c r="K378" s="5" t="n">
         <v>645</v>
@@ -18449,7 +18449,7 @@
         <v>99</v>
       </c>
       <c r="J379" s="11" t="n">
-        <v>0.88</v>
+        <v>0.8686</v>
       </c>
       <c r="K379" s="8" t="n">
         <v>50</v>
@@ -18497,7 +18497,7 @@
         <v>30</v>
       </c>
       <c r="J380" s="11" t="n">
-        <v>0</v>
+        <v>0.7998</v>
       </c>
       <c r="K380" s="8" t="n">
         <v>15</v>
@@ -18545,7 +18545,7 @@
         <v>162</v>
       </c>
       <c r="J381" s="11" t="n">
-        <v>0.7937</v>
+        <v>0.839</v>
       </c>
       <c r="K381" s="8" t="n">
         <v>75</v>
@@ -18593,7 +18593,7 @@
         <v>192</v>
       </c>
       <c r="J382" s="11" t="n">
-        <v>0.8134</v>
+        <v>0.8121</v>
       </c>
       <c r="K382" s="8" t="n">
         <v>90</v>
@@ -18641,7 +18641,7 @@
         <v>270</v>
       </c>
       <c r="J383" s="11" t="n">
-        <v>0.8481</v>
+        <v>0.8478</v>
       </c>
       <c r="K383" s="8" t="n">
         <v>135</v>
@@ -18689,7 +18689,7 @@
         <v>364</v>
       </c>
       <c r="J384" s="11" t="n">
-        <v>0.8594000000000001</v>
+        <v>0.8921</v>
       </c>
       <c r="K384" s="8" t="n">
         <v>180</v>
@@ -18737,7 +18737,7 @@
         <v>119</v>
       </c>
       <c r="J385" s="11" t="n">
-        <v>0.6583</v>
+        <v>0.8568</v>
       </c>
       <c r="K385" s="8" t="n">
         <v>65</v>
@@ -18785,7 +18785,7 @@
         <v>78</v>
       </c>
       <c r="J386" s="11" t="n">
-        <v>0.375</v>
+        <v>0.6022999999999999</v>
       </c>
       <c r="K386" s="8" t="n">
         <v>35</v>
@@ -18921,7 +18921,7 @@
         <v>140</v>
       </c>
       <c r="J389" s="7" t="n">
-        <v>0.6214</v>
+        <v>0.8998</v>
       </c>
       <c r="K389" s="5" t="n">
         <v>69</v>
@@ -18969,7 +18969,7 @@
         <v>10</v>
       </c>
       <c r="J390" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K390" s="8" t="n">
         <v>5</v>
@@ -19017,7 +19017,7 @@
         <v>10</v>
       </c>
       <c r="J391" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K391" s="8" t="n">
         <v>5</v>
@@ -19065,7 +19065,7 @@
         <v>40</v>
       </c>
       <c r="J392" s="11" t="n">
-        <v>0.4</v>
+        <v>0.875</v>
       </c>
       <c r="K392" s="8" t="n">
         <v>19</v>
@@ -19161,7 +19161,7 @@
         <v>60</v>
       </c>
       <c r="J394" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9495</v>
       </c>
       <c r="K394" s="8" t="n">
         <v>30</v>
@@ -19205,7 +19205,7 @@
         <v>612</v>
       </c>
       <c r="J395" s="7" t="n">
-        <v>0.4672</v>
+        <v>0.8331</v>
       </c>
       <c r="K395" s="5" t="n">
         <v>305</v>
@@ -19253,7 +19253,7 @@
         <v>50</v>
       </c>
       <c r="J396" s="11" t="n">
-        <v>0.2857</v>
+        <v>0.72</v>
       </c>
       <c r="K396" s="8" t="n">
         <v>25</v>
@@ -19349,7 +19349,7 @@
         <v>152</v>
       </c>
       <c r="J398" s="11" t="n">
-        <v>0.8333</v>
+        <v>0.835</v>
       </c>
       <c r="K398" s="8" t="n">
         <v>80</v>
@@ -19445,7 +19445,7 @@
         <v>10</v>
       </c>
       <c r="J400" s="11" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K400" s="8" t="n">
         <v>5</v>
@@ -19493,7 +19493,7 @@
         <v>10</v>
       </c>
       <c r="J401" s="11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K401" s="8" t="n">
         <v>5</v>
@@ -19541,7 +19541,7 @@
         <v>180</v>
       </c>
       <c r="J402" s="11" t="n">
-        <v>0.1277</v>
+        <v>0.8607</v>
       </c>
       <c r="K402" s="8" t="n">
         <v>90</v>
@@ -19589,7 +19589,7 @@
         <v>100</v>
       </c>
       <c r="J403" s="11" t="n">
-        <v>0.34</v>
+        <v>0.89</v>
       </c>
       <c r="K403" s="8" t="n">
         <v>50</v>
@@ -19681,7 +19681,7 @@
         <v>240</v>
       </c>
       <c r="J405" s="7" t="n">
-        <v>0.4354</v>
+        <v>0.9789</v>
       </c>
       <c r="K405" s="5" t="n">
         <v>120</v>
@@ -19729,7 +19729,7 @@
         <v>11</v>
       </c>
       <c r="J406" s="11" t="n">
-        <v>0</v>
+        <v>0.9999</v>
       </c>
       <c r="K406" s="8" t="n">
         <v>5</v>
@@ -19777,7 +19777,7 @@
         <v>50</v>
       </c>
       <c r="J407" s="11" t="n">
-        <v>0.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K407" s="8" t="n">
         <v>25</v>
@@ -19825,7 +19825,7 @@
         <v>10</v>
       </c>
       <c r="J408" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K408" s="8" t="n">
         <v>5</v>
@@ -19873,7 +19873,7 @@
         <v>30</v>
       </c>
       <c r="J409" s="11" t="n">
-        <v>0.6333</v>
+        <v>0.9663</v>
       </c>
       <c r="K409" s="8" t="n">
         <v>15</v>
@@ -19921,7 +19921,7 @@
         <v>20</v>
       </c>
       <c r="J410" s="11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K410" s="8" t="n">
         <v>10</v>
@@ -19969,7 +19969,7 @@
         <v>59</v>
       </c>
       <c r="J411" s="11" t="n">
-        <v>0.5</v>
+        <v>0.9993</v>
       </c>
       <c r="K411" s="8" t="n">
         <v>30</v>
@@ -20017,7 +20017,7 @@
         <v>60</v>
       </c>
       <c r="J412" s="11" t="n">
-        <v>0.3166</v>
+        <v>0.9831</v>
       </c>
       <c r="K412" s="8" t="n">
         <v>30</v>
@@ -20061,7 +20061,7 @@
         <v>1163</v>
       </c>
       <c r="J413" s="7" t="n">
-        <v>0.4641</v>
+        <v>0.7813</v>
       </c>
       <c r="K413" s="5" t="n">
         <v>598</v>
@@ -20109,7 +20109,7 @@
         <v>49</v>
       </c>
       <c r="J414" s="11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7548</v>
       </c>
       <c r="K414" s="8" t="n">
         <v>25</v>
@@ -20157,7 +20157,7 @@
         <v>60</v>
       </c>
       <c r="J415" s="11" t="n">
-        <v>0.15</v>
+        <v>0.6329</v>
       </c>
       <c r="K415" s="8" t="n">
         <v>25</v>
@@ -20205,7 +20205,7 @@
         <v>20</v>
       </c>
       <c r="J416" s="11" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K416" s="8" t="n">
         <v>10</v>
@@ -20253,7 +20253,7 @@
         <v>20</v>
       </c>
       <c r="J417" s="11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K417" s="8" t="n">
         <v>10</v>
@@ -20301,7 +20301,7 @@
         <v>139</v>
       </c>
       <c r="J418" s="11" t="n">
-        <v>0.6928</v>
+        <v>0.6903</v>
       </c>
       <c r="K418" s="8" t="n">
         <v>65</v>
@@ -20349,7 +20349,7 @@
         <v>120</v>
       </c>
       <c r="J419" s="11" t="n">
-        <v>0.7416</v>
+        <v>0.7329</v>
       </c>
       <c r="K419" s="8" t="n">
         <v>64</v>
@@ -20397,7 +20397,7 @@
         <v>19</v>
       </c>
       <c r="J420" s="11" t="n">
-        <v>0.85</v>
+        <v>0.8945</v>
       </c>
       <c r="K420" s="8" t="n">
         <v>10</v>
@@ -20445,7 +20445,7 @@
         <v>100</v>
       </c>
       <c r="J421" s="11" t="n">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="K421" s="8" t="n">
         <v>55</v>
@@ -20493,7 +20493,7 @@
         <v>50</v>
       </c>
       <c r="J422" s="11" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="K422" s="8" t="n">
         <v>25</v>
@@ -20541,7 +20541,7 @@
         <v>120</v>
       </c>
       <c r="J423" s="11" t="n">
-        <v>0.6333</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="K423" s="8" t="n">
         <v>65</v>
@@ -20589,7 +20589,7 @@
         <v>50</v>
       </c>
       <c r="J424" s="11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K424" s="8" t="n">
         <v>25</v>
@@ -20637,7 +20637,7 @@
         <v>59</v>
       </c>
       <c r="J425" s="11" t="n">
-        <v>0.4166</v>
+        <v>0.6606</v>
       </c>
       <c r="K425" s="8" t="n">
         <v>25</v>
@@ -20685,7 +20685,7 @@
         <v>119</v>
       </c>
       <c r="J426" s="11" t="n">
-        <v>0.6583</v>
+        <v>0.8905</v>
       </c>
       <c r="K426" s="8" t="n">
         <v>60</v>
@@ -20733,7 +20733,7 @@
         <v>30</v>
       </c>
       <c r="J427" s="11" t="n">
-        <v>0.9</v>
+        <v>0.8996</v>
       </c>
       <c r="K427" s="8" t="n">
         <v>20</v>
@@ -20781,7 +20781,7 @@
         <v>91</v>
       </c>
       <c r="J428" s="11" t="n">
-        <v>0.2333</v>
+        <v>0.8238</v>
       </c>
       <c r="K428" s="8" t="n">
         <v>45</v>
@@ -20829,7 +20829,7 @@
         <v>117</v>
       </c>
       <c r="J429" s="11" t="n">
-        <v>0.2285</v>
+        <v>0.8371</v>
       </c>
       <c r="K429" s="8" t="n">
         <v>69</v>
@@ -20873,7 +20873,7 @@
         <v>430</v>
       </c>
       <c r="J430" s="7" t="n">
-        <v>0.8242</v>
+        <v>0.8343</v>
       </c>
       <c r="K430" s="5" t="n">
         <v>201</v>
@@ -20921,7 +20921,7 @@
         <v>190</v>
       </c>
       <c r="J431" s="11" t="n">
-        <v>0.7947</v>
+        <v>0.7995</v>
       </c>
       <c r="K431" s="8" t="n">
         <v>90</v>
@@ -20969,7 +20969,7 @@
         <v>230</v>
       </c>
       <c r="J432" s="11" t="n">
-        <v>0.8583</v>
+        <v>0.8732</v>
       </c>
       <c r="K432" s="8" t="n">
         <v>106</v>
@@ -21061,7 +21061,7 @@
         <v>49</v>
       </c>
       <c r="J434" s="7" t="n">
-        <v>0.9</v>
+        <v>0.8976</v>
       </c>
       <c r="K434" s="5" t="n">
         <v>35</v>
@@ -21109,7 +21109,7 @@
         <v>49</v>
       </c>
       <c r="J435" s="11" t="n">
-        <v>0.9</v>
+        <v>0.8976</v>
       </c>
       <c r="K435" s="8" t="n">
         <v>35</v>
@@ -21153,7 +21153,7 @@
         <v>100</v>
       </c>
       <c r="J436" s="7" t="n">
-        <v>0.7199</v>
+        <v>0.7296</v>
       </c>
       <c r="K436" s="5" t="n">
         <v>50</v>
@@ -21249,7 +21249,7 @@
         <v>90</v>
       </c>
       <c r="J438" s="11" t="n">
-        <v>0.6888</v>
+        <v>0.6996</v>
       </c>
       <c r="K438" s="8" t="n">
         <v>45</v>
@@ -21293,7 +21293,7 @@
         <v>51</v>
       </c>
       <c r="J439" s="7" t="n">
-        <v>0.7598</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="K439" s="5" t="n">
         <v>20</v>
@@ -21389,7 +21389,7 @@
         <v>21</v>
       </c>
       <c r="J441" s="11" t="n">
-        <v>0.75</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="K441" s="8" t="n">
         <v>5</v>
@@ -21545,7 +21545,7 @@
         <v>30</v>
       </c>
       <c r="J445" s="7" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7664</v>
       </c>
       <c r="K445" s="5" t="n">
         <v>10</v>
@@ -21593,7 +21593,7 @@
         <v>30</v>
       </c>
       <c r="J446" s="11" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7664</v>
       </c>
       <c r="K446" s="8" t="n">
         <v>10</v>
@@ -21669,7 +21669,7 @@
         <v>41</v>
       </c>
       <c r="J448" s="7" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="K448" s="5" t="n">
         <v>15</v>
@@ -21717,7 +21717,7 @@
         <v>41</v>
       </c>
       <c r="J449" s="11" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="K449" s="8" t="n">
         <v>15</v>
@@ -21889,7 +21889,7 @@
         <v>958</v>
       </c>
       <c r="J453" s="4" t="n">
-        <v>0.7929</v>
+        <v>0.9516</v>
       </c>
       <c r="K453" s="2" t="n">
         <v>495</v>
@@ -21933,7 +21933,7 @@
         <v>20</v>
       </c>
       <c r="J454" s="7" t="n">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="K454" s="5" t="n">
         <v>10</v>
@@ -21981,7 +21981,7 @@
         <v>10</v>
       </c>
       <c r="J455" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K455" s="8" t="n">
         <v>5</v>
@@ -22073,7 +22073,7 @@
         <v>149</v>
       </c>
       <c r="J457" s="7" t="n">
-        <v>0.8399</v>
+        <v>0.9796</v>
       </c>
       <c r="K457" s="5" t="n">
         <v>85</v>
@@ -22169,7 +22169,7 @@
         <v>10</v>
       </c>
       <c r="J459" s="11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K459" s="8" t="n">
         <v>5</v>
@@ -22265,7 +22265,7 @@
         <v>10</v>
       </c>
       <c r="J461" s="11" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K461" s="8" t="n">
         <v>5</v>
@@ -22361,7 +22361,7 @@
         <v>60</v>
       </c>
       <c r="J463" s="11" t="n">
-        <v>0.9857</v>
+        <v>0.9828</v>
       </c>
       <c r="K463" s="8" t="n">
         <v>35</v>
@@ -22505,7 +22505,7 @@
         <v>10</v>
       </c>
       <c r="J466" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K466" s="8" t="n">
         <v>5</v>
@@ -22553,7 +22553,7 @@
         <v>9</v>
       </c>
       <c r="J467" s="11" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="K467" s="8" t="n">
         <v>5</v>
@@ -22597,7 +22597,7 @@
         <v>439</v>
       </c>
       <c r="J468" s="7" t="n">
-        <v>0.7232</v>
+        <v>0.9678</v>
       </c>
       <c r="K468" s="5" t="n">
         <v>225</v>
@@ -22645,7 +22645,7 @@
         <v>30</v>
       </c>
       <c r="J469" s="11" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="K469" s="8" t="n">
         <v>15</v>
@@ -22693,7 +22693,7 @@
         <v>9</v>
       </c>
       <c r="J470" s="11" t="n">
-        <v>0</v>
+        <v>0.8888</v>
       </c>
       <c r="K470" s="8" t="n">
         <v>5</v>
@@ -22741,7 +22741,7 @@
         <v>40</v>
       </c>
       <c r="J471" s="11" t="n">
-        <v>0.475</v>
+        <v>0.975</v>
       </c>
       <c r="K471" s="8" t="n">
         <v>20</v>
@@ -22789,7 +22789,7 @@
         <v>30</v>
       </c>
       <c r="J472" s="11" t="n">
-        <v>0.6</v>
+        <v>0.9332</v>
       </c>
       <c r="K472" s="8" t="n">
         <v>15</v>
@@ -22837,7 +22837,7 @@
         <v>70</v>
       </c>
       <c r="J473" s="11" t="n">
-        <v>0.9142</v>
+        <v>0.9135</v>
       </c>
       <c r="K473" s="8" t="n">
         <v>35</v>
@@ -22933,7 +22933,7 @@
         <v>10</v>
       </c>
       <c r="J475" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="K475" s="8" t="n">
         <v>5</v>
@@ -23029,7 +23029,7 @@
         <v>90</v>
       </c>
       <c r="J477" s="11" t="n">
-        <v>0.9666</v>
+        <v>0.9661</v>
       </c>
       <c r="K477" s="8" t="n">
         <v>45</v>
@@ -23077,7 +23077,7 @@
         <v>50</v>
       </c>
       <c r="J478" s="11" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="K478" s="8" t="n">
         <v>25</v>
@@ -23125,7 +23125,7 @@
         <v>30</v>
       </c>
       <c r="J479" s="11" t="n">
-        <v>0.6666</v>
+        <v>0.9997</v>
       </c>
       <c r="K479" s="8" t="n">
         <v>15</v>
@@ -23173,7 +23173,7 @@
         <v>30</v>
       </c>
       <c r="J480" s="11" t="n">
-        <v>0.3333</v>
+        <v>0.9998</v>
       </c>
       <c r="K480" s="8" t="n">
         <v>15</v>
@@ -23217,7 +23217,7 @@
         <v>160</v>
       </c>
       <c r="J481" s="7" t="n">
-        <v>0.8187</v>
+        <v>0.9059</v>
       </c>
       <c r="K481" s="5" t="n">
         <v>80</v>
@@ -23265,7 +23265,7 @@
         <v>30</v>
       </c>
       <c r="J482" s="11" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="K482" s="8" t="n">
         <v>15</v>
@@ -23313,7 +23313,7 @@
         <v>130</v>
       </c>
       <c r="J483" s="11" t="n">
-        <v>0.7769</v>
+        <v>0.8842</v>
       </c>
       <c r="K483" s="8" t="n">
         <v>65</v>
@@ -23449,7 +23449,7 @@
         <v>30</v>
       </c>
       <c r="J486" s="7" t="n">
-        <v>0.8333</v>
+        <v>0.833</v>
       </c>
       <c r="K486" s="5" t="n">
         <v>15</v>
@@ -23497,7 +23497,7 @@
         <v>30</v>
       </c>
       <c r="J487" s="11" t="n">
-        <v>0.8333</v>
+        <v>0.833</v>
       </c>
       <c r="K487" s="8" t="n">
         <v>15</v>
@@ -23541,7 +23541,7 @@
         <v>110</v>
       </c>
       <c r="J488" s="7" t="n">
-        <v>0.9545</v>
+        <v>0.9537</v>
       </c>
       <c r="K488" s="5" t="n">
         <v>55</v>
@@ -23589,7 +23589,7 @@
         <v>110</v>
       </c>
       <c r="J489" s="11" t="n">
-        <v>0.9545</v>
+        <v>0.9537</v>
       </c>
       <c r="K489" s="8" t="n">
         <v>55</v>
@@ -23637,7 +23637,7 @@
         <v>473</v>
       </c>
       <c r="J490" s="4" t="n">
-        <v>0.8908</v>
+        <v>0.9532</v>
       </c>
       <c r="K490" s="2" t="n">
         <v>245</v>
@@ -23681,7 +23681,7 @@
         <v>10</v>
       </c>
       <c r="J491" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K491" s="5" t="n">
         <v>5</v>
@@ -23729,7 +23729,7 @@
         <v>10</v>
       </c>
       <c r="J492" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K492" s="8" t="n">
         <v>5</v>
@@ -23865,7 +23865,7 @@
         <v>443</v>
       </c>
       <c r="J495" s="7" t="n">
-        <v>0.9059</v>
+        <v>0.95</v>
       </c>
       <c r="K495" s="5" t="n">
         <v>230</v>
@@ -23961,7 +23961,7 @@
         <v>59</v>
       </c>
       <c r="J497" s="11" t="n">
-        <v>0.5</v>
+        <v>0.847</v>
       </c>
       <c r="K497" s="8" t="n">
         <v>30</v>
@@ -24009,7 +24009,7 @@
         <v>50</v>
       </c>
       <c r="J498" s="11" t="n">
-        <v>0.8367</v>
+        <v>0.82</v>
       </c>
       <c r="K498" s="8" t="n">
         <v>20</v>
@@ -24105,7 +24105,7 @@
         <v>60</v>
       </c>
       <c r="J500" s="11" t="n">
-        <v>0.9833</v>
+        <v>0.983</v>
       </c>
       <c r="K500" s="8" t="n">
         <v>30</v>
@@ -24153,7 +24153,7 @@
         <v>15</v>
       </c>
       <c r="J501" s="11" t="n">
-        <v>1</v>
+        <v>0.9997</v>
       </c>
       <c r="K501" s="8" t="n">
         <v>15</v>
@@ -24249,7 +24249,7 @@
         <v>59</v>
       </c>
       <c r="J503" s="11" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="K503" s="8" t="n">
         <v>30</v>
@@ -24345,7 +24345,7 @@
         <v>70</v>
       </c>
       <c r="J505" s="11" t="n">
-        <v>1</v>
+        <v>0.9993</v>
       </c>
       <c r="K505" s="8" t="n">
         <v>35</v>
@@ -24393,7 +24393,7 @@
         <v>1851</v>
       </c>
       <c r="J506" s="4" t="n">
-        <v>0.6777</v>
+        <v>0.8333</v>
       </c>
       <c r="K506" s="2" t="n">
         <v>903</v>
@@ -24437,7 +24437,7 @@
         <v>75</v>
       </c>
       <c r="J507" s="7" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="K507" s="5" t="n">
         <v>35</v>
@@ -24581,7 +24581,7 @@
         <v>15</v>
       </c>
       <c r="J510" s="11" t="n">
-        <v>0.2307</v>
+        <v>0.3999</v>
       </c>
       <c r="K510" s="8" t="n">
         <v>5</v>
@@ -24629,7 +24629,7 @@
         <v>20</v>
       </c>
       <c r="J511" s="11" t="n">
-        <v>0.525</v>
+        <v>0.95</v>
       </c>
       <c r="K511" s="8" t="n">
         <v>10</v>
@@ -24673,7 +24673,7 @@
         <v>63</v>
       </c>
       <c r="J512" s="7" t="n">
-        <v>0.9166</v>
+        <v>0.9201</v>
       </c>
       <c r="K512" s="5" t="n">
         <v>30</v>
@@ -24721,7 +24721,7 @@
         <v>63</v>
       </c>
       <c r="J513" s="11" t="n">
-        <v>0.9166</v>
+        <v>0.9201</v>
       </c>
       <c r="K513" s="8" t="n">
         <v>30</v>
@@ -24765,7 +24765,7 @@
         <v>528</v>
       </c>
       <c r="J514" s="7" t="n">
-        <v>0.8032</v>
+        <v>0.8576</v>
       </c>
       <c r="K514" s="5" t="n">
         <v>265</v>
@@ -24813,7 +24813,7 @@
         <v>189</v>
       </c>
       <c r="J515" s="11" t="n">
-        <v>0.921</v>
+        <v>0.92</v>
       </c>
       <c r="K515" s="8" t="n">
         <v>100</v>
@@ -24909,7 +24909,7 @@
         <v>49</v>
       </c>
       <c r="J517" s="11" t="n">
-        <v>0.96</v>
+        <v>0.9589</v>
       </c>
       <c r="K517" s="8" t="n">
         <v>25</v>
@@ -24957,7 +24957,7 @@
         <v>150</v>
       </c>
       <c r="J518" s="11" t="n">
-        <v>0.6666</v>
+        <v>0.7331</v>
       </c>
       <c r="K518" s="8" t="n">
         <v>75</v>
@@ -25005,7 +25005,7 @@
         <v>120</v>
       </c>
       <c r="J519" s="11" t="n">
-        <v>0.7083</v>
+        <v>0.8666</v>
       </c>
       <c r="K519" s="8" t="n">
         <v>55</v>
@@ -25081,7 +25081,7 @@
         <v>346</v>
       </c>
       <c r="J521" s="7" t="n">
-        <v>0.3595</v>
+        <v>0.8321</v>
       </c>
       <c r="K521" s="5" t="n">
         <v>170</v>
@@ -25129,7 +25129,7 @@
         <v>50</v>
       </c>
       <c r="J522" s="11" t="n">
-        <v>0.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K522" s="8" t="n">
         <v>25</v>
@@ -25177,7 +25177,7 @@
         <v>10</v>
       </c>
       <c r="J523" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K523" s="8" t="n">
         <v>5</v>
@@ -25225,7 +25225,7 @@
         <v>20</v>
       </c>
       <c r="J524" s="11" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K524" s="8" t="n">
         <v>10</v>
@@ -25273,7 +25273,7 @@
         <v>261</v>
       </c>
       <c r="J525" s="11" t="n">
-        <v>0.4</v>
+        <v>0.8004</v>
       </c>
       <c r="K525" s="8" t="n">
         <v>125</v>
@@ -25321,7 +25321,7 @@
         <v>5</v>
       </c>
       <c r="J526" s="11" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K526" s="8" t="n">
         <v>5</v>
@@ -25365,7 +25365,7 @@
         <v>139</v>
       </c>
       <c r="J527" s="7" t="n">
-        <v>0.8358</v>
+        <v>0.8484</v>
       </c>
       <c r="K527" s="5" t="n">
         <v>70</v>
@@ -25413,7 +25413,7 @@
         <v>70</v>
       </c>
       <c r="J528" s="11" t="n">
-        <v>0.8571</v>
+        <v>0.8567</v>
       </c>
       <c r="K528" s="8" t="n">
         <v>35</v>
@@ -25461,7 +25461,7 @@
         <v>69</v>
       </c>
       <c r="J529" s="11" t="n">
-        <v>0.8142</v>
+        <v>0.84</v>
       </c>
       <c r="K529" s="8" t="n">
         <v>35</v>
@@ -25505,7 +25505,7 @@
         <v>20</v>
       </c>
       <c r="J530" s="7" t="n">
-        <v>0.45</v>
+        <v>0.9</v>
       </c>
       <c r="K530" s="5" t="n">
         <v>10</v>
@@ -25553,7 +25553,7 @@
         <v>20</v>
       </c>
       <c r="J531" s="11" t="n">
-        <v>0.45</v>
+        <v>0.9</v>
       </c>
       <c r="K531" s="8" t="n">
         <v>10</v>
@@ -25677,7 +25677,7 @@
         <v>80</v>
       </c>
       <c r="J534" s="7" t="n">
-        <v>0.8375</v>
+        <v>0.8373</v>
       </c>
       <c r="K534" s="5" t="n">
         <v>38</v>
@@ -25725,7 +25725,7 @@
         <v>60</v>
       </c>
       <c r="J535" s="11" t="n">
-        <v>0.8833</v>
+        <v>0.8831</v>
       </c>
       <c r="K535" s="8" t="n">
         <v>28</v>
@@ -25817,7 +25817,7 @@
         <v>410</v>
       </c>
       <c r="J537" s="7" t="n">
-        <v>0.8683</v>
+        <v>0.8754</v>
       </c>
       <c r="K537" s="5" t="n">
         <v>200</v>
@@ -25865,7 +25865,7 @@
         <v>90</v>
       </c>
       <c r="J538" s="11" t="n">
-        <v>0.8333</v>
+        <v>0.8331</v>
       </c>
       <c r="K538" s="8" t="n">
         <v>40</v>
@@ -25913,7 +25913,7 @@
         <v>51</v>
       </c>
       <c r="J539" s="11" t="n">
-        <v>0.82</v>
+        <v>0.8233</v>
       </c>
       <c r="K539" s="8" t="n">
         <v>25</v>
@@ -25961,7 +25961,7 @@
         <v>49</v>
       </c>
       <c r="J540" s="11" t="n">
-        <v>0.8</v>
+        <v>0.9996</v>
       </c>
       <c r="K540" s="8" t="n">
         <v>25</v>
@@ -26009,7 +26009,7 @@
         <v>30</v>
       </c>
       <c r="J541" s="11" t="n">
-        <v>1</v>
+        <v>0.9999</v>
       </c>
       <c r="K541" s="8" t="n">
         <v>15</v>
@@ -26105,7 +26105,7 @@
         <v>90</v>
       </c>
       <c r="J543" s="11" t="n">
-        <v>0.9444</v>
+        <v>0.9442</v>
       </c>
       <c r="K543" s="8" t="n">
         <v>45</v>
@@ -26249,7 +26249,7 @@
         <v>10</v>
       </c>
       <c r="J546" s="11" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K546" s="8" t="n">
         <v>5</v>
@@ -26293,7 +26293,7 @@
         <v>180</v>
       </c>
       <c r="J547" s="7" t="n">
-        <v>0.2222</v>
+        <v>0.6166</v>
       </c>
       <c r="K547" s="5" t="n">
         <v>85</v>
@@ -26341,7 +26341,7 @@
         <v>10</v>
       </c>
       <c r="J548" s="11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K548" s="8" t="n">
         <v>5</v>
@@ -26389,7 +26389,7 @@
         <v>70</v>
       </c>
       <c r="J549" s="11" t="n">
-        <v>0.2142</v>
+        <v>0.4713</v>
       </c>
       <c r="K549" s="8" t="n">
         <v>30</v>
@@ -26437,7 +26437,7 @@
         <v>100</v>
       </c>
       <c r="J550" s="11" t="n">
-        <v>0.23</v>
+        <v>0.75</v>
       </c>
       <c r="K550" s="8" t="n">
         <v>50</v>
@@ -26485,7 +26485,7 @@
         <v>3175</v>
       </c>
       <c r="J551" s="4" t="n">
-        <v>0.4828</v>
+        <v>0.9066</v>
       </c>
       <c r="K551" s="2" t="n">
         <v>929</v>
@@ -26529,7 +26529,7 @@
         <v>917</v>
       </c>
       <c r="J552" s="7" t="n">
-        <v>0.1352</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="K552" s="5" t="n">
         <v>225</v>
@@ -26577,7 +26577,7 @@
         <v>60</v>
       </c>
       <c r="J553" s="11" t="n">
-        <v>0</v>
+        <v>0.983</v>
       </c>
       <c r="K553" s="8" t="n">
         <v>15</v>
@@ -26721,7 +26721,7 @@
         <v>60</v>
       </c>
       <c r="J556" s="11" t="n">
-        <v>1</v>
+        <v>0.9664</v>
       </c>
       <c r="K556" s="8" t="n">
         <v>15</v>
@@ -26769,7 +26769,7 @@
         <v>80</v>
       </c>
       <c r="J557" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K557" s="8" t="n">
         <v>20</v>
@@ -26817,7 +26817,7 @@
         <v>260</v>
       </c>
       <c r="J558" s="11" t="n">
-        <v>0</v>
+        <v>0.9532</v>
       </c>
       <c r="K558" s="8" t="n">
         <v>65</v>
@@ -26865,7 +26865,7 @@
         <v>200</v>
       </c>
       <c r="J559" s="11" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K559" s="8" t="n">
         <v>50</v>
@@ -26913,7 +26913,7 @@
         <v>20</v>
       </c>
       <c r="J560" s="11" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="K560" s="8" t="n">
         <v>0</v>
@@ -26955,7 +26955,7 @@
         <v>59</v>
       </c>
       <c r="J561" s="11" t="n">
-        <v>0</v>
+        <v>0.9488</v>
       </c>
       <c r="K561" s="8" t="n">
         <v>15</v>
@@ -27003,7 +27003,7 @@
         <v>98</v>
       </c>
       <c r="J562" s="11" t="n">
-        <v>0</v>
+        <v>0.8671</v>
       </c>
       <c r="K562" s="8" t="n">
         <v>25</v>
@@ -27047,7 +27047,7 @@
         <v>79</v>
       </c>
       <c r="J563" s="7" t="n">
-        <v>0.9</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="K563" s="5" t="n">
         <v>20</v>
@@ -27095,7 +27095,7 @@
         <v>79</v>
       </c>
       <c r="J564" s="11" t="n">
-        <v>0.9</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="K564" s="8" t="n">
         <v>20</v>
@@ -27139,7 +27139,7 @@
         <v>2179</v>
       </c>
       <c r="J565" s="7" t="n">
-        <v>0.6139</v>
+        <v>0.8998</v>
       </c>
       <c r="K565" s="5" t="n">
         <v>684</v>
@@ -27187,7 +27187,7 @@
         <v>180</v>
       </c>
       <c r="J566" s="11" t="n">
-        <v>0</v>
+        <v>0.905</v>
       </c>
       <c r="K566" s="8" t="n">
         <v>45</v>
@@ -27235,7 +27235,7 @@
         <v>160</v>
       </c>
       <c r="J567" s="11" t="n">
-        <v>0</v>
+        <v>0.9247</v>
       </c>
       <c r="K567" s="8" t="n">
         <v>40</v>
@@ -27331,7 +27331,7 @@
         <v>179</v>
       </c>
       <c r="J569" s="11" t="n">
-        <v>0.8944</v>
+        <v>0.8931</v>
       </c>
       <c r="K569" s="8" t="n">
         <v>45</v>
@@ -27379,7 +27379,7 @@
         <v>120</v>
       </c>
       <c r="J570" s="11" t="n">
-        <v>0.9333</v>
+        <v>0.9331</v>
       </c>
       <c r="K570" s="8" t="n">
         <v>30</v>
@@ -27427,7 +27427,7 @@
         <v>120</v>
       </c>
       <c r="J571" s="11" t="n">
-        <v>0.7083</v>
+        <v>0.8164</v>
       </c>
       <c r="K571" s="8" t="n">
         <v>30</v>
@@ -27475,7 +27475,7 @@
         <v>141</v>
       </c>
       <c r="J572" s="11" t="n">
-        <v>0.9214</v>
+        <v>0.9213</v>
       </c>
       <c r="K572" s="8" t="n">
         <v>35</v>
@@ -27609,7 +27609,7 @@
         <v>40</v>
       </c>
       <c r="J575" s="11" t="n">
-        <v>0</v>
+        <v>0.775</v>
       </c>
       <c r="K575" s="8" t="n">
         <v>20</v>
@@ -27657,7 +27657,7 @@
         <v>100</v>
       </c>
       <c r="J576" s="11" t="n">
-        <v>0</v>
+        <v>0.7938</v>
       </c>
       <c r="K576" s="8" t="n">
         <v>144</v>
@@ -27705,7 +27705,7 @@
         <v>140</v>
       </c>
       <c r="J577" s="11" t="n">
-        <v>0</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="K577" s="8" t="n">
         <v>30</v>
@@ -27753,7 +27753,7 @@
         <v>99</v>
       </c>
       <c r="J578" s="11" t="n">
-        <v>0.9416</v>
+        <v>0.9393</v>
       </c>
       <c r="K578" s="8" t="n">
         <v>30</v>
@@ -27801,7 +27801,7 @@
         <v>180</v>
       </c>
       <c r="J579" s="11" t="n">
-        <v>0.8555</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="K579" s="8" t="n">
         <v>45</v>
@@ -27849,7 +27849,7 @@
         <v>120</v>
       </c>
       <c r="J580" s="11" t="n">
-        <v>0.925</v>
+        <v>0.9247</v>
       </c>
       <c r="K580" s="8" t="n">
         <v>30</v>
@@ -27897,7 +27897,7 @@
         <v>100</v>
       </c>
       <c r="J581" s="11" t="n">
-        <v>0.9555</v>
+        <v>0.96</v>
       </c>
       <c r="K581" s="8" t="n">
         <v>25</v>
@@ -27945,7 +27945,7 @@
         <v>220</v>
       </c>
       <c r="J582" s="11" t="n">
-        <v>0.9666</v>
+        <v>0.9675</v>
       </c>
       <c r="K582" s="8" t="n">
         <v>55</v>
@@ -27993,7 +27993,7 @@
         <v>20</v>
       </c>
       <c r="J583" s="11" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K583" s="8" t="n">
         <v>5</v>
@@ -28041,7 +28041,7 @@
         <v>200</v>
       </c>
       <c r="J584" s="11" t="n">
-        <v>0.6712</v>
+        <v>0.885</v>
       </c>
       <c r="K584" s="8" t="n">
         <v>55</v>
@@ -28129,7 +28129,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>% &gt; 12 °Brix</t>
+          <t>% ≥ 12 °Brix</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -28181,7 +28181,7 @@
         <v>95</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>0.6947</v>
+        <v>0.6943</v>
       </c>
       <c r="J2" s="8" t="n">
         <v>45</v>
@@ -28224,7 +28224,7 @@
         <v>165</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>0.3999</v>
+        <v>0.6906</v>
       </c>
       <c r="J3" s="12" t="n">
         <v>80</v>
@@ -28267,7 +28267,7 @@
         <v>664</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>0.8488</v>
+        <v>0.8431</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>319</v>
@@ -28310,7 +28310,7 @@
         <v>1290</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.5151</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>580</v>
@@ -28353,7 +28353,7 @@
         <v>401</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>0.9002</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>194</v>
@@ -28396,7 +28396,7 @@
         <v>543</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>0.9391</v>
+        <v>0.9371</v>
       </c>
       <c r="J7" s="12" t="n">
         <v>264</v>
@@ -28439,7 +28439,7 @@
         <v>452</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6704</v>
+        <v>0.6788</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>214</v>
@@ -28482,7 +28482,7 @@
         <v>866</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>0.8578</v>
+        <v>0.8793</v>
       </c>
       <c r="J9" s="12" t="n">
         <v>400</v>
@@ -28525,7 +28525,7 @@
         <v>1000</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.475</v>
+        <v>0.7796999999999999</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>460</v>
@@ -28568,7 +28568,7 @@
         <v>1000</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>0.6364</v>
+        <v>0.9386</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>509</v>
@@ -28611,7 +28611,7 @@
         <v>155</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.8129</v>
+        <v>0.8127</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>75</v>
@@ -28654,7 +28654,7 @@
         <v>281</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>0.8925</v>
+        <v>0.8929</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>135</v>
@@ -28697,7 +28697,7 @@
         <v>314</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.8328</v>
+        <v>0.834</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>150</v>
@@ -28740,7 +28740,7 @@
         <v>30</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>0.6666</v>
+        <v>0.6663</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>15</v>
@@ -28912,7 +28912,7 @@
         <v>81</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>0.8493000000000001</v>
+        <v>0.901</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>34</v>
@@ -29041,7 +29041,7 @@
         <v>323</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.7879</v>
+        <v>0.7894</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>80</v>
@@ -29084,7 +29084,7 @@
         <v>1238</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>0.8418</v>
+        <v>0.8502</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>305</v>
@@ -29127,7 +29127,7 @@
         <v>747</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.7712</v>
+        <v>0.7749</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>170</v>
@@ -29170,7 +29170,7 @@
         <v>4126</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.7825</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>985</v>
@@ -29213,7 +29213,7 @@
         <v>219</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0</v>
+        <v>0.9404</v>
       </c>
       <c r="J26" s="8" t="n">
         <v>55</v>
@@ -29256,7 +29256,7 @@
         <v>1200</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>0.7716</v>
+        <v>0.8599</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>435</v>
@@ -29342,7 +29342,7 @@
         <v>200</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0.8197</v>
+        <v>0.8192</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>314</v>
@@ -29385,7 +29385,7 @@
         <v>60</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>0.7166</v>
+        <v>0.7163</v>
       </c>
       <c r="J30" s="8" t="n">
         <v>15</v>
@@ -29428,7 +29428,7 @@
         <v>20</v>
       </c>
       <c r="I31" s="14" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>5</v>
@@ -29471,7 +29471,7 @@
         <v>140</v>
       </c>
       <c r="I32" s="11" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9429</v>
       </c>
       <c r="J32" s="8" t="n">
         <v>35</v>
@@ -29514,7 +29514,7 @@
         <v>522</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>0.9096</v>
+        <v>0.9076</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>130</v>
@@ -29557,7 +29557,7 @@
         <v>608</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>0.7508</v>
+        <v>0.7742</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>135</v>
@@ -29600,7 +29600,7 @@
         <v>703</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0.8763</v>
+        <v>0.8942</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>160</v>
@@ -29643,7 +29643,7 @@
         <v>439</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>0.2632</v>
+        <v>0.7539</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>134</v>
@@ -29686,7 +29686,7 @@
         <v>460</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8451</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>120</v>
@@ -29729,7 +29729,7 @@
         <v>430</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>0.7983</v>
+        <v>0.8065</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>99</v>
@@ -29815,7 +29815,7 @@
         <v>1842</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>0.8434</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>914</v>
@@ -29858,7 +29858,7 @@
         <v>660</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>0.2906</v>
+        <v>0.8695000000000001</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>343</v>
@@ -29901,7 +29901,7 @@
         <v>1409</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>0.4896</v>
+        <v>0.9081</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>697</v>
@@ -29944,7 +29944,7 @@
         <v>1475</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>0.9764</v>
+        <v>0.9772</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>735</v>
@@ -29987,7 +29987,7 @@
         <v>411</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>0.6226</v>
+        <v>0.8731</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>205</v>
@@ -30030,7 +30030,7 @@
         <v>1529</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.959</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>760</v>
@@ -30073,7 +30073,7 @@
         <v>69</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>1</v>
+        <v>0.9994</v>
       </c>
       <c r="J46" s="8" t="n">
         <v>35</v>
@@ -30159,7 +30159,7 @@
         <v>240</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>0.8833</v>
+        <v>0.9162</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>125</v>
@@ -30202,7 +30202,7 @@
         <v>89</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>0.9111</v>
+        <v>0.9095</v>
       </c>
       <c r="J49" s="12" t="n">
         <v>45</v>
@@ -30245,7 +30245,7 @@
         <v>1314</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>0.7772</v>
+        <v>0.8405</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>645</v>
@@ -30331,7 +30331,7 @@
         <v>140</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>0.6214</v>
+        <v>0.8998</v>
       </c>
       <c r="J52" s="8" t="n">
         <v>69</v>
@@ -30374,7 +30374,7 @@
         <v>612</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>0.4672</v>
+        <v>0.8331</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>305</v>
@@ -30417,7 +30417,7 @@
         <v>240</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>0.4354</v>
+        <v>0.9789</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>120</v>
@@ -30460,7 +30460,7 @@
         <v>1163</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>0.4641</v>
+        <v>0.7813</v>
       </c>
       <c r="J55" s="12" t="n">
         <v>598</v>
@@ -30503,7 +30503,7 @@
         <v>430</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>0.8242</v>
+        <v>0.8343</v>
       </c>
       <c r="J56" s="8" t="n">
         <v>201</v>
@@ -30546,7 +30546,7 @@
         <v>49</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>0.9</v>
+        <v>0.8976</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>35</v>
@@ -30589,7 +30589,7 @@
         <v>100</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>0.7199</v>
+        <v>0.7296</v>
       </c>
       <c r="J58" s="8" t="n">
         <v>50</v>
@@ -30632,7 +30632,7 @@
         <v>51</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>0.7598</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>20</v>
@@ -30675,7 +30675,7 @@
         <v>30</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.7664</v>
       </c>
       <c r="J60" s="8" t="n">
         <v>10</v>
@@ -30718,7 +30718,7 @@
         <v>41</v>
       </c>
       <c r="I61" s="14" t="n">
-        <v>1</v>
+        <v>0.9996</v>
       </c>
       <c r="J61" s="12" t="n">
         <v>15</v>
@@ -30804,7 +30804,7 @@
         <v>20</v>
       </c>
       <c r="I63" s="14" t="n">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="J63" s="12" t="n">
         <v>10</v>
@@ -30847,7 +30847,7 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>0.8399</v>
+        <v>0.9796</v>
       </c>
       <c r="J64" s="8" t="n">
         <v>85</v>
@@ -30890,7 +30890,7 @@
         <v>439</v>
       </c>
       <c r="I65" s="14" t="n">
-        <v>0.7232</v>
+        <v>0.9678</v>
       </c>
       <c r="J65" s="12" t="n">
         <v>225</v>
@@ -30933,7 +30933,7 @@
         <v>160</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>0.8187</v>
+        <v>0.9059</v>
       </c>
       <c r="J66" s="8" t="n">
         <v>80</v>
@@ -31019,7 +31019,7 @@
         <v>30</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>0.8333</v>
+        <v>0.833</v>
       </c>
       <c r="J68" s="8" t="n">
         <v>15</v>
@@ -31062,7 +31062,7 @@
         <v>110</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>0.9545</v>
+        <v>0.9537</v>
       </c>
       <c r="J69" s="12" t="n">
         <v>55</v>
@@ -31105,7 +31105,7 @@
         <v>10</v>
       </c>
       <c r="I70" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" s="8" t="n">
         <v>5</v>
@@ -31191,7 +31191,7 @@
         <v>443</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>0.9059</v>
+        <v>0.95</v>
       </c>
       <c r="J72" s="8" t="n">
         <v>230</v>
@@ -31234,7 +31234,7 @@
         <v>75</v>
       </c>
       <c r="I73" s="14" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.8532999999999999</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>35</v>
@@ -31277,7 +31277,7 @@
         <v>63</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>0.9166</v>
+        <v>0.9201</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>30</v>
@@ -31320,7 +31320,7 @@
         <v>528</v>
       </c>
       <c r="I75" s="14" t="n">
-        <v>0.8032</v>
+        <v>0.8576</v>
       </c>
       <c r="J75" s="12" t="n">
         <v>265</v>
@@ -31363,7 +31363,7 @@
         <v>346</v>
       </c>
       <c r="I76" s="11" t="n">
-        <v>0.3595</v>
+        <v>0.8321</v>
       </c>
       <c r="J76" s="8" t="n">
         <v>170</v>
@@ -31406,7 +31406,7 @@
         <v>139</v>
       </c>
       <c r="I77" s="14" t="n">
-        <v>0.8358</v>
+        <v>0.8484</v>
       </c>
       <c r="J77" s="12" t="n">
         <v>70</v>
@@ -31449,7 +31449,7 @@
         <v>20</v>
       </c>
       <c r="I78" s="11" t="n">
-        <v>0.45</v>
+        <v>0.9</v>
       </c>
       <c r="J78" s="8" t="n">
         <v>10</v>
@@ -31529,7 +31529,7 @@
         <v>80</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>0.8375</v>
+        <v>0.8373</v>
       </c>
       <c r="J80" s="8" t="n">
         <v>38</v>
@@ -31572,7 +31572,7 @@
         <v>410</v>
       </c>
       <c r="I81" s="14" t="n">
-        <v>0.8683</v>
+        <v>0.8754</v>
       </c>
       <c r="J81" s="12" t="n">
         <v>200</v>
@@ -31615,7 +31615,7 @@
         <v>180</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>0.2222</v>
+        <v>0.6166</v>
       </c>
       <c r="J82" s="8" t="n">
         <v>85</v>
@@ -31658,7 +31658,7 @@
         <v>917</v>
       </c>
       <c r="I83" s="14" t="n">
-        <v>0.1352</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="J83" s="12" t="n">
         <v>225</v>
@@ -31701,7 +31701,7 @@
         <v>79</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>0.9</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="J84" s="8" t="n">
         <v>20</v>
@@ -31744,7 +31744,7 @@
         <v>2179</v>
       </c>
       <c r="I85" s="14" t="n">
-        <v>0.6139</v>
+        <v>0.8998</v>
       </c>
       <c r="J85" s="12" t="n">
         <v>684</v>
@@ -32538,7 +32538,7 @@
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t>% &gt; 12 °Brix = sección 'VALORES DE AZUCAR' (rango MAYORES DE 12).</t>
+          <t>% ≥ 12 °Brix = % de muestras con 12 °Brix o más (equivale al rango MAYORES DE 12 del ERP).</t>
         </is>
       </c>
     </row>

--- a/Datos de azucar y firmeza por melon en general.xlsx
+++ b/Datos de azucar y firmeza por melon en general.xlsx
@@ -645,7 +645,11 @@
           <t>A-25-09</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr"/>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>PEKIN</t>
+        </is>
+      </c>
       <c r="D3" s="5" t="inlineStr"/>
       <c r="E3" s="5" t="n">
         <v>1</v>
@@ -689,7 +693,11 @@
           <t>A-25-09</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>PEKIN</t>
+        </is>
+      </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
           <t>URCIMAR SCL COPE 21/2026 PEKI (260.003.231)</t>
@@ -737,7 +745,11 @@
           <t>A-26-02</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>MAILLOT</t>
+        </is>
+      </c>
       <c r="D5" s="5" t="inlineStr"/>
       <c r="E5" s="5" t="n">
         <v>4</v>
@@ -781,7 +793,11 @@
           <t>A-26-02</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>MAILLOT</t>
+        </is>
+      </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
           <t>LUCAS TORRES INIESTA J ANTONIO (260.003.497)</t>
@@ -829,7 +845,11 @@
           <t>A-26-02</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>MAILLOT</t>
+        </is>
+      </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
           <t>LUCAS TORRES INIESTA J ANTONIO (260.003.496)</t>
@@ -877,7 +897,11 @@
           <t>A-26-02</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>MAILLOT</t>
+        </is>
+      </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
           <t>LUCERON LUCAS TORRES JESUS CAM (260.003.498)</t>
@@ -925,7 +949,11 @@
           <t>A-26-02</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>MAILLOT</t>
+        </is>
+      </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
           <t>SAT 9861 AGROPEC EL ROSARIO AL (260.003.494)</t>
@@ -973,7 +1001,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n">
         <v>11</v>
@@ -1017,7 +1049,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
           <t>AGRO LA GUIA SL LA GUIA-PITERO (260.003.524)</t>
@@ -1065,7 +1101,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
           <t>AGROFRUT 2019 SL LA PALMA 23/ (260.003.357)</t>
@@ -1113,7 +1153,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr"/>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
           <t>ALJORRA (2.026.345.220)</t>
@@ -1161,7 +1205,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
           <t>ALJORRA (2.026.345.200)</t>
@@ -1209,7 +1257,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr"/>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
           <t>ALJORRA (2.026.345.100)</t>
@@ -1257,7 +1309,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
           <t>ALJORRA (2.026.345.210)</t>
@@ -1305,7 +1361,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr"/>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.002.945)</t>
@@ -1353,7 +1413,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.092)</t>
@@ -1401,7 +1465,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr"/>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.091)</t>
@@ -1449,7 +1517,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.760)</t>
@@ -1497,7 +1569,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr"/>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.220)</t>
@@ -1545,7 +1621,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n">
         <v>15</v>
@@ -1589,7 +1669,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr"/>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.208)</t>
@@ -1637,7 +1721,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr"/>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
           <t>ANGULO MANZANEQUE IGNACIO AREN (260.003.304)</t>
@@ -1685,7 +1773,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr"/>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
           <t>CAÑAS MERINO VICTOR FRANCISCO (260.003.305)</t>
@@ -1733,7 +1825,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.003.068)</t>
@@ -1781,7 +1877,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr"/>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
           <t>EXPLOTACIONES CHINCHILLA SL BA (260.003.306)</t>
@@ -1829,7 +1929,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
           <t>EXPLOTACIONES CHINCHILLA SL CA (260.003.536)</t>
@@ -1877,7 +1981,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C29" s="8" t="inlineStr"/>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
           <t>EXPLOTACIONES CHINCHILLA SL TO (260.003.495)</t>
@@ -1925,7 +2033,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr"/>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
           <t>FRUVEG SDAD COOP EL JERINGAL (260.003.523)</t>
@@ -1973,7 +2085,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr"/>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.123)</t>
@@ -2021,7 +2137,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr"/>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.203)</t>
@@ -2069,7 +2189,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr"/>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
           <t>GUTIERREZ JIMENEZ MANUEL CAMPO (260.003.535)</t>
@@ -2117,7 +2241,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr"/>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
           <t>LUCERON LUCAS TORRES JESUS CAM (260.003.511)</t>
@@ -2165,7 +2293,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr"/>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
           <t>MERINO VIOLERO LUIS CAMPO DE C (260.003.545)</t>
@@ -2213,7 +2345,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr"/>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
           <t>SEÑORIO DE AGROGIGANTES SL CAM (260.003.557)</t>
@@ -2261,7 +2397,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr"/>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
           <t>VELA BASTANTE RUBEN CAMPO DE C (260.003.518)</t>
@@ -2309,7 +2449,11 @@
           <t>A-26-12</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>PIEL DE SOL</t>
+        </is>
+      </c>
       <c r="D38" s="5" t="inlineStr"/>
       <c r="E38" s="5" t="n">
         <v>3</v>
@@ -2353,7 +2497,11 @@
           <t>A-26-12</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr"/>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>PIEL DE SOL</t>
+        </is>
+      </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.081)</t>
@@ -2401,7 +2549,11 @@
           <t>A-26-12</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr"/>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>PIEL DE SOL</t>
+        </is>
+      </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.208)</t>
@@ -2449,7 +2601,11 @@
           <t>A-26-12</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr"/>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>PIEL DE SOL</t>
+        </is>
+      </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.003.038)</t>
@@ -2497,7 +2653,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr"/>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D42" s="5" t="inlineStr"/>
       <c r="E42" s="5" t="n">
         <v>9</v>
@@ -2541,7 +2701,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr"/>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
           <t>ALJORRA (2.026.345.100)</t>
@@ -2589,7 +2753,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr"/>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
           <t>ALJORRA (2.026.345.230)</t>
@@ -2637,7 +2805,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr"/>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
           <t>JUAN GARRE HERNANDEZ LUGAR NUE (260.003.094)</t>
@@ -2685,7 +2857,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr"/>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
           <t>MULATA (2.026.382.351)</t>
@@ -2733,7 +2909,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr"/>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
           <t>MULATA (2.026.382.361)</t>
@@ -2781,7 +2961,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr"/>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
           <t>NIETOS (2.026.356.550)</t>
@@ -2829,7 +3013,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr"/>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
           <t>NIETOS (2.026.356.510)</t>
@@ -2877,7 +3065,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr"/>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
           <t>NIETOS (2.026.356.530)</t>
@@ -2925,7 +3117,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr"/>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
           <t>NIETOS (2.026.356.570)</t>
@@ -2973,7 +3169,11 @@
           <t>A-26-14</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr"/>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>NIVAL (34-379)</t>
+        </is>
+      </c>
       <c r="D52" s="5" t="inlineStr"/>
       <c r="E52" s="5" t="n">
         <v>6</v>
@@ -3017,7 +3217,11 @@
           <t>A-26-14</t>
         </is>
       </c>
-      <c r="C53" s="8" t="inlineStr"/>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>NIVAL (34-379)</t>
+        </is>
+      </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
           <t>CARLINA LO FERRO SL LA ALJORRA (260.003.330)</t>
@@ -3065,7 +3269,11 @@
           <t>A-26-14</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr"/>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>NIVAL (34-379)</t>
+        </is>
+      </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.002.946)</t>
@@ -3113,7 +3321,11 @@
           <t>A-26-14</t>
         </is>
       </c>
-      <c r="C55" s="8" t="inlineStr"/>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>NIVAL (34-379)</t>
+        </is>
+      </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.002.944)</t>
@@ -3161,7 +3373,11 @@
           <t>A-26-14</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr"/>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>NIVAL (34-379)</t>
+        </is>
+      </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.122)</t>
@@ -3209,7 +3425,11 @@
           <t>A-26-14</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr"/>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>NIVAL (34-379)</t>
+        </is>
+      </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.033)</t>
@@ -3257,7 +3477,11 @@
           <t>A-26-14</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr"/>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>NIVAL (34-379)</t>
+        </is>
+      </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.003.037)</t>
@@ -3305,7 +3529,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr"/>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D59" s="5" t="inlineStr"/>
       <c r="E59" s="5" t="n">
         <v>10</v>
@@ -3349,7 +3577,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr"/>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
           <t>AGRICOLA ARROYO Y MARIN SL FUE (260.003.559)</t>
@@ -3397,7 +3629,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C61" s="8" t="inlineStr"/>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
           <t>AGROFRUT 2019 SL LAS PALAS 28 (260.003.582)</t>
@@ -3445,7 +3681,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr"/>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
           <t>AGROFRUT 2019 SL LAS PALAS 30 (260.003.617)</t>
@@ -3493,7 +3733,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr"/>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
           <t>AGROFRUT 2019 SL TOTANA-HORFRU (260.003.583)</t>
@@ -3541,7 +3785,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr"/>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.003.047)</t>
@@ -3589,7 +3837,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr"/>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.003.056)</t>
@@ -3637,7 +3889,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr"/>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.122)</t>
@@ -3685,7 +3941,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr"/>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.113)</t>
@@ -3733,7 +3993,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr"/>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA CAS (260.003.138)</t>
@@ -3781,7 +4045,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr"/>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA JUM (260.003.194)</t>
@@ -3829,7 +4097,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr"/>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D70" s="5" t="inlineStr"/>
       <c r="E70" s="5" t="n">
         <v>18</v>
@@ -3873,7 +4145,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C71" s="8" t="inlineStr"/>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
           <t>ANTONIO JOSE MANZANARES CEGARR (260.003.233)</t>
@@ -3921,7 +4197,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr"/>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
           <t>CAÑAS PINTOR FRANCISCO CAMPO D (260.003.513)</t>
@@ -3969,7 +4249,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C73" s="8" t="inlineStr"/>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.003.068)</t>
@@ -4017,7 +4301,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr"/>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.003.047)</t>
@@ -4065,7 +4353,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr"/>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
           <t>FRUTAS J.D. 2015 SLU CINCO CAS (260.003.615)</t>
@@ -4113,7 +4405,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr"/>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.203)</t>
@@ -4161,7 +4457,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr"/>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.091)</t>
@@ -4209,7 +4509,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr"/>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.123)</t>
@@ -4257,7 +4561,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr"/>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
           <t>GREGAL SOCIEDAD COOPERATIVA TO (260.003.631)</t>
@@ -4305,7 +4613,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr"/>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
           <t>GUTIERREZ JIMENEZ MANUEL CAMPO (260.003.551)</t>
@@ -4353,7 +4665,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr"/>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
           <t>LUCAS TORRES DE LA GUIA TERESA (260.003.510)</t>
@@ -4401,7 +4717,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr"/>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
           <t>LUCAS TORRES INIESTA J ANTONIO (260.003.512)</t>
@@ -4449,7 +4769,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr"/>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
           <t>LUCERON LUCAS TORRES JESUS CAM (260.003.498)</t>
@@ -4497,7 +4821,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr"/>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
           <t>LUCERON LUCAS TORRES JESUS CAM (260.003.511)</t>
@@ -4545,7 +4873,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr"/>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
           <t>MERINO VIOLERO LUIS CAMPO DE C (260.003.546)</t>
@@ -4593,7 +4925,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr"/>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
           <t>SEÑORIO DE AGROGIGANTES SL CAM (260.003.556)</t>
@@ -4641,7 +4977,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr"/>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.120)</t>
@@ -4689,7 +5029,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr"/>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.101)</t>
@@ -4737,7 +5081,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr"/>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D89" s="5" t="inlineStr"/>
       <c r="E89" s="5" t="n">
         <v>9</v>
@@ -4781,7 +5129,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr"/>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.003.048)</t>
@@ -4829,7 +5181,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr"/>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
           <t>EXPLOTACIONES CHINCHILLA SL TO (260.003.495)</t>
@@ -4877,7 +5233,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr"/>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.091)</t>
@@ -4925,7 +5285,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr"/>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA AGR (260.003.243)</t>
@@ -4973,7 +5337,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C94" s="8" t="inlineStr"/>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA PIL (260.003.437)</t>
@@ -5021,7 +5389,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C95" s="8" t="inlineStr"/>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
           <t>LUCAS TORRES INIESTA J ANTONIO (260.003.497)</t>
@@ -5069,7 +5441,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C96" s="8" t="inlineStr"/>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
           <t>LUCAS TORRES INIESTA J ANTONIO (260.003.496)</t>
@@ -5117,7 +5493,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C97" s="8" t="inlineStr"/>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
           <t>LUCERON LUCAS TORRES JESUS CAM (260.003.499)</t>
@@ -5165,7 +5545,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr"/>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
           <t>MERINO VIOLERO LUIS CAMPO DE C (260.003.423)</t>
@@ -5213,7 +5597,11 @@
           <t>A-26-25</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr"/>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>MS12MA058</t>
+        </is>
+      </c>
       <c r="D99" s="5" t="inlineStr"/>
       <c r="E99" s="5" t="n">
         <v>3</v>
@@ -5257,7 +5645,11 @@
           <t>A-26-25</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr"/>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>MS12MA058</t>
+        </is>
+      </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.002.943)</t>
@@ -5305,7 +5697,11 @@
           <t>A-26-25</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr"/>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>MS12MA058</t>
+        </is>
+      </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.002.945)</t>
@@ -5353,7 +5749,11 @@
           <t>A-26-25</t>
         </is>
       </c>
-      <c r="C102" s="8" t="inlineStr"/>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>MS12MA058</t>
+        </is>
+      </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.003.065)</t>
@@ -5401,7 +5801,11 @@
           <t>A-26-26</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr"/>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>TEQUILA</t>
+        </is>
+      </c>
       <c r="D103" s="5" t="inlineStr"/>
       <c r="E103" s="5" t="n">
         <v>4</v>
@@ -5445,7 +5849,11 @@
           <t>A-26-26</t>
         </is>
       </c>
-      <c r="C104" s="8" t="inlineStr"/>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>TEQUILA</t>
+        </is>
+      </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.002.942)</t>
@@ -5493,7 +5901,11 @@
           <t>A-26-26</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr"/>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>TEQUILA</t>
+        </is>
+      </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.092)</t>
@@ -5541,7 +5953,11 @@
           <t>A-26-26</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr"/>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>TEQUILA</t>
+        </is>
+      </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
           <t>JUAN GARRE HERNANDEZ LUGAR NUE (260.003.079)</t>
@@ -5589,7 +6005,11 @@
           <t>A-26-26</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr"/>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>TEQUILA</t>
+        </is>
+      </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA CAS (260.003.139)</t>
@@ -5637,7 +6057,11 @@
           <t>A-26-27</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr"/>
+      <c r="C108" s="5" t="inlineStr">
+        <is>
+          <t>HAWAI</t>
+        </is>
+      </c>
       <c r="D108" s="5" t="inlineStr"/>
       <c r="E108" s="5" t="n">
         <v>5</v>
@@ -5681,7 +6105,11 @@
           <t>A-26-27</t>
         </is>
       </c>
-      <c r="C109" s="8" t="inlineStr"/>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>HAWAI</t>
+        </is>
+      </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.208)</t>
@@ -5729,7 +6157,11 @@
           <t>A-26-27</t>
         </is>
       </c>
-      <c r="C110" s="8" t="inlineStr"/>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>HAWAI</t>
+        </is>
+      </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.002.944)</t>
@@ -5777,7 +6209,11 @@
           <t>A-26-27</t>
         </is>
       </c>
-      <c r="C111" s="8" t="inlineStr"/>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>HAWAI</t>
+        </is>
+      </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.067)</t>
@@ -5825,7 +6261,11 @@
           <t>A-26-27</t>
         </is>
       </c>
-      <c r="C112" s="8" t="inlineStr"/>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>HAWAI</t>
+        </is>
+      </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.093)</t>
@@ -5873,7 +6313,11 @@
           <t>A-26-27</t>
         </is>
       </c>
-      <c r="C113" s="8" t="inlineStr"/>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>HAWAI</t>
+        </is>
+      </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA CAS (260.003.140)</t>
@@ -5921,7 +6365,11 @@
           <t>A-ATILA</t>
         </is>
       </c>
-      <c r="C114" s="5" t="inlineStr"/>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>ATILA</t>
+        </is>
+      </c>
       <c r="D114" s="5" t="inlineStr"/>
       <c r="E114" s="5" t="n">
         <v>1</v>
@@ -5965,7 +6413,11 @@
           <t>A-ATILA</t>
         </is>
       </c>
-      <c r="C115" s="8" t="inlineStr"/>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>ATILA</t>
+        </is>
+      </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
           <t>AGROFRUT 2019 SL LA PALMA 23/ (260.003.357)</t>
@@ -6013,7 +6465,11 @@
           <t>A-ROCHESTE</t>
         </is>
       </c>
-      <c r="C116" s="5" t="inlineStr"/>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>ROCHESTE</t>
+        </is>
+      </c>
       <c r="D116" s="5" t="inlineStr"/>
       <c r="E116" s="5" t="n">
         <v>2</v>
@@ -6057,7 +6513,11 @@
           <t>A-ROCHESTE</t>
         </is>
       </c>
-      <c r="C117" s="8" t="inlineStr"/>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>ROCHESTE</t>
+        </is>
+      </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
           <t>LOPEZ VAZQUEZ FRANCISCO MANUEL (260.003.213)</t>
@@ -6105,7 +6565,11 @@
           <t>A-ROCHESTE</t>
         </is>
       </c>
-      <c r="C118" s="8" t="inlineStr"/>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>ROCHESTE</t>
+        </is>
+      </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
           <t>LOPEZ VAZQUEZ FRANCISCO MANUEL (260.003.213) [C2]</t>
@@ -6137,7 +6601,11 @@
           <t>A-ROCHESTE</t>
         </is>
       </c>
-      <c r="C119" s="8" t="inlineStr"/>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>ROCHESTE</t>
+        </is>
+      </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
           <t>LOPEZ VAZQUEZ JUAN ANTONIO EL (260.003.212)</t>
@@ -6185,7 +6653,11 @@
           <t>A-ROCHESTE</t>
         </is>
       </c>
-      <c r="C120" s="8" t="inlineStr"/>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>ROCHESTE</t>
+        </is>
+      </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
           <t>LOPEZ VAZQUEZ JUAN ANTONIO EL (260.003.212) [C2]</t>
@@ -6233,7 +6705,11 @@
           <t>A-SUERTE</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr"/>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>SUERTE</t>
+        </is>
+      </c>
       <c r="D121" s="5" t="inlineStr"/>
       <c r="E121" s="5" t="n">
         <v>1</v>
@@ -6277,7 +6753,11 @@
           <t>A-SUERTE</t>
         </is>
       </c>
-      <c r="C122" s="8" t="inlineStr"/>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>SUERTE</t>
+        </is>
+      </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
           <t>FRUVEG SDAD COOP LOS MEDICOS (260.003.589)</t>
@@ -6325,7 +6805,11 @@
           <t>A-ZENITH</t>
         </is>
       </c>
-      <c r="C123" s="5" t="inlineStr"/>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>ZENITH</t>
+        </is>
+      </c>
       <c r="D123" s="5" t="inlineStr"/>
       <c r="E123" s="5" t="n">
         <v>1</v>
@@ -6369,7 +6853,11 @@
           <t>A-ZENITH</t>
         </is>
       </c>
-      <c r="C124" s="8" t="inlineStr"/>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>ZENITH</t>
+        </is>
+      </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
           <t>ALJORRA (2.026.345.100)</t>
@@ -6417,7 +6905,11 @@
           <t>INDURAIN</t>
         </is>
       </c>
-      <c r="C125" s="5" t="inlineStr"/>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>INDURAIN</t>
+        </is>
+      </c>
       <c r="D125" s="5" t="inlineStr"/>
       <c r="E125" s="5" t="n">
         <v>2</v>
@@ -6461,7 +6953,11 @@
           <t>INDURAIN</t>
         </is>
       </c>
-      <c r="C126" s="8" t="inlineStr"/>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>INDURAIN</t>
+        </is>
+      </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
           <t>BARRANCO VARGAS FRANCISCO ADRA (260.003.144)</t>
@@ -6509,7 +7005,11 @@
           <t>INDURAIN</t>
         </is>
       </c>
-      <c r="C127" s="8" t="inlineStr"/>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>INDURAIN</t>
+        </is>
+      </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
           <t>BARRANCO VARGAS FRANCISCO ADRA (260.003.144) [C2]</t>
@@ -6541,7 +7041,11 @@
           <t>INDURAIN</t>
         </is>
       </c>
-      <c r="C128" s="8" t="inlineStr"/>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>INDURAIN</t>
+        </is>
+      </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
           <t>RODRIGUEZ RUIZ RAUL NIJAR 14/ (260.003.148)</t>
@@ -6589,7 +7093,11 @@
           <t>INDURAIN</t>
         </is>
       </c>
-      <c r="C129" s="8" t="inlineStr"/>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>INDURAIN</t>
+        </is>
+      </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
           <t>RODRIGUEZ RUIZ RAUL NIJAR 14/ (260.003.148) [C2]</t>
@@ -6621,7 +7129,11 @@
           <t>MIELON</t>
         </is>
       </c>
-      <c r="C130" s="5" t="inlineStr"/>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>MIELON</t>
+        </is>
+      </c>
       <c r="D130" s="5" t="inlineStr"/>
       <c r="E130" s="5" t="n">
         <v>1</v>
@@ -6665,7 +7177,11 @@
           <t>MIELON</t>
         </is>
       </c>
-      <c r="C131" s="8" t="inlineStr"/>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>MIELON</t>
+        </is>
+      </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
           <t>MARTIN RODRIGUEZ JUAN MANUEL E (260.003.247)</t>
@@ -6713,7 +7229,11 @@
           <t>MIELON</t>
         </is>
       </c>
-      <c r="C132" s="8" t="inlineStr"/>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>MIELON</t>
+        </is>
+      </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
           <t>MARTIN RODRIGUEZ JUAN MANUEL E (260.003.247) [C2]</t>
@@ -6793,7 +7313,11 @@
           <t>C-19-11</t>
         </is>
       </c>
-      <c r="C134" s="5" t="inlineStr"/>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>N.12788</t>
+        </is>
+      </c>
       <c r="D134" s="5" t="inlineStr"/>
       <c r="E134" s="5" t="n">
         <v>1</v>
@@ -6837,7 +7361,11 @@
           <t>C-19-11</t>
         </is>
       </c>
-      <c r="C135" s="8" t="inlineStr"/>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>N.12788</t>
+        </is>
+      </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.111)</t>
@@ -6885,7 +7413,11 @@
           <t>C-24-21</t>
         </is>
       </c>
-      <c r="C136" s="5" t="inlineStr"/>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>MAGVERIK</t>
+        </is>
+      </c>
       <c r="D136" s="5" t="inlineStr"/>
       <c r="E136" s="5" t="n">
         <v>5</v>
@@ -6929,7 +7461,11 @@
           <t>C-24-21</t>
         </is>
       </c>
-      <c r="C137" s="8" t="inlineStr"/>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>MAGVERIK</t>
+        </is>
+      </c>
       <c r="D137" s="9" t="inlineStr">
         <is>
           <t>AGRICOLA MALOPEZ SL ADRA 18/2 (260.003.293)</t>
@@ -6977,7 +7513,11 @@
           <t>C-24-21</t>
         </is>
       </c>
-      <c r="C138" s="8" t="inlineStr"/>
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t>MAGVERIK</t>
+        </is>
+      </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
           <t>MOLINA SOLER FRANCISCO JAVIER (260.003.150)</t>
@@ -7025,7 +7565,11 @@
           <t>C-24-21</t>
         </is>
       </c>
-      <c r="C139" s="8" t="inlineStr"/>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>MAGVERIK</t>
+        </is>
+      </c>
       <c r="D139" s="9" t="inlineStr">
         <is>
           <t>MOLINA SOLER FRANCISCO JAVIER (260.003.150) [C2]</t>
@@ -7073,7 +7617,11 @@
           <t>C-24-21</t>
         </is>
       </c>
-      <c r="C140" s="8" t="inlineStr"/>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>MAGVERIK</t>
+        </is>
+      </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
           <t>SOLER SUAREZ JUAN JOSE ADRA (260.003.155)</t>
@@ -7121,7 +7669,11 @@
           <t>C-24-21</t>
         </is>
       </c>
-      <c r="C141" s="8" t="inlineStr"/>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>MAGVERIK</t>
+        </is>
+      </c>
       <c r="D141" s="9" t="inlineStr">
         <is>
           <t>SOLER SUAREZ JUAN JOSE EL EJID (260.003.154)</t>
@@ -7169,7 +7721,11 @@
           <t>C-24-21</t>
         </is>
       </c>
-      <c r="C142" s="8" t="inlineStr"/>
+      <c r="C142" s="8" t="inlineStr">
+        <is>
+          <t>MAGVERIK</t>
+        </is>
+      </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
           <t>SOLER SUAREZ MANUEL ADRA 18/2 (260.003.153)</t>
@@ -7217,7 +7773,11 @@
           <t>C-24-21</t>
         </is>
       </c>
-      <c r="C143" s="8" t="inlineStr"/>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>MAGVERIK</t>
+        </is>
+      </c>
       <c r="D143" s="9" t="inlineStr">
         <is>
           <t>SOLER SUAREZ MANUEL ADRA 18/2 (260.003.153) [C2]</t>
@@ -7265,7 +7825,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C144" s="5" t="inlineStr"/>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D144" s="5" t="inlineStr"/>
       <c r="E144" s="5" t="n">
         <v>10</v>
@@ -7309,7 +7873,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C145" s="8" t="inlineStr"/>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D145" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.272)</t>
@@ -7357,7 +7925,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C146" s="8" t="inlineStr"/>
+      <c r="C146" s="8" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.233)</t>
@@ -7405,7 +7977,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C147" s="8" t="inlineStr"/>
+      <c r="C147" s="8" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D147" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.282)</t>
@@ -7453,7 +8029,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C148" s="8" t="inlineStr"/>
+      <c r="C148" s="8" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
           <t>JUAN GARRE HERNANDEZ LUGAR NUE (260.002.978)</t>
@@ -7501,7 +8081,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C149" s="8" t="inlineStr"/>
+      <c r="C149" s="8" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D149" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.120)</t>
@@ -7549,7 +8133,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C150" s="8" t="inlineStr"/>
+      <c r="C150" s="8" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.130)</t>
@@ -7597,7 +8185,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C151" s="8" t="inlineStr"/>
+      <c r="C151" s="8" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D151" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.512)</t>
@@ -7645,7 +8237,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C152" s="8" t="inlineStr"/>
+      <c r="C152" s="8" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.110)</t>
@@ -7693,7 +8289,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C153" s="8" t="inlineStr"/>
+      <c r="C153" s="8" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D153" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.071)</t>
@@ -7741,7 +8341,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C154" s="8" t="inlineStr"/>
+      <c r="C154" s="8" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.003.084)</t>
@@ -7789,7 +8393,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="C155" s="5" t="inlineStr"/>
+      <c r="C155" s="5" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
       <c r="D155" s="5" t="inlineStr"/>
       <c r="E155" s="5" t="n">
         <v>8</v>
@@ -7833,7 +8441,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="C156" s="8" t="inlineStr"/>
+      <c r="C156" s="8" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
           <t>ANTONIO JOSE MANZANARES CEGARR (260.002.987)</t>
@@ -7881,7 +8493,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="C157" s="8" t="inlineStr"/>
+      <c r="C157" s="8" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
       <c r="D157" s="9" t="inlineStr">
         <is>
           <t>ANTONIO JOSE MANZANARES CEGARR (260.002.985)</t>
@@ -7929,7 +8545,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="C158" s="8" t="inlineStr"/>
+      <c r="C158" s="8" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
           <t>JUAN GARRE HERNANDEZ LUGAR NUE (260.003.002)</t>
@@ -7977,7 +8597,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="C159" s="8" t="inlineStr"/>
+      <c r="C159" s="8" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
       <c r="D159" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.101)</t>
@@ -8025,7 +8649,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="C160" s="8" t="inlineStr"/>
+      <c r="C160" s="8" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.090)</t>
@@ -8073,7 +8701,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="C161" s="8" t="inlineStr"/>
+      <c r="C161" s="8" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
       <c r="D161" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.221)</t>
@@ -8121,7 +8753,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="C162" s="8" t="inlineStr"/>
+      <c r="C162" s="8" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.082)</t>
@@ -8169,7 +8805,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="C163" s="8" t="inlineStr"/>
+      <c r="C163" s="8" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
       <c r="D163" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.071)</t>
@@ -8217,7 +8857,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C164" s="5" t="inlineStr"/>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D164" s="5" t="inlineStr"/>
       <c r="E164" s="5" t="n">
         <v>33</v>
@@ -8261,7 +8905,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C165" s="8" t="inlineStr"/>
+      <c r="C165" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D165" s="9" t="inlineStr">
         <is>
           <t>ABAD LOPEZ MARIA CAMPO DE CRIP (260.003.308)</t>
@@ -8309,7 +8957,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C166" s="8" t="inlineStr"/>
+      <c r="C166" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
           <t>AGRO MORENO VERA SL AEROPUERTO (260.002.948)</t>
@@ -8357,7 +9009,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C167" s="8" t="inlineStr"/>
+      <c r="C167" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D167" s="9" t="inlineStr">
         <is>
           <t>AGRO RUIZ CINCO CASAS SL ALCAZ (260.003.507)</t>
@@ -8405,7 +9061,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C168" s="8" t="inlineStr"/>
+      <c r="C168" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D168" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE ARENALES (260.003.529)</t>
@@ -8453,7 +9113,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C169" s="8" t="inlineStr"/>
+      <c r="C169" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D169" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE CAMPO DE (260.003.309)</t>
@@ -8501,7 +9165,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C170" s="8" t="inlineStr"/>
+      <c r="C170" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D170" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.071)</t>
@@ -8549,7 +9217,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C171" s="8" t="inlineStr"/>
+      <c r="C171" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D171" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.082)</t>
@@ -8597,7 +9269,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C172" s="8" t="inlineStr"/>
+      <c r="C172" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D172" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.121)</t>
@@ -8645,7 +9321,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C173" s="8" t="inlineStr"/>
+      <c r="C173" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D173" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.933)</t>
@@ -8693,7 +9373,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C174" s="8" t="inlineStr"/>
+      <c r="C174" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D174" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.950)</t>
@@ -8741,7 +9425,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C175" s="8" t="inlineStr"/>
+      <c r="C175" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D175" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.920)</t>
@@ -8789,7 +9477,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C176" s="8" t="inlineStr"/>
+      <c r="C176" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D176" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.913)</t>
@@ -8837,7 +9529,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C177" s="8" t="inlineStr"/>
+      <c r="C177" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D177" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.980)</t>
@@ -8885,7 +9581,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C178" s="8" t="inlineStr"/>
+      <c r="C178" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D178" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.960)</t>
@@ -8933,7 +9633,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C179" s="8" t="inlineStr"/>
+      <c r="C179" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D179" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.943)</t>
@@ -8981,7 +9685,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C180" s="8" t="inlineStr"/>
+      <c r="C180" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D180" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.051)</t>
@@ -9029,7 +9737,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C181" s="8" t="inlineStr"/>
+      <c r="C181" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D181" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ ARENAL (260.003.534)</t>
@@ -9077,7 +9789,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C182" s="8" t="inlineStr"/>
+      <c r="C182" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D182" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.171)</t>
@@ -9125,7 +9841,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C183" s="8" t="inlineStr"/>
+      <c r="C183" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D183" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.122)</t>
@@ -9173,7 +9893,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C184" s="8" t="inlineStr"/>
+      <c r="C184" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D184" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.110)</t>
@@ -9221,7 +9945,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C185" s="8" t="inlineStr"/>
+      <c r="C185" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D185" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.310)</t>
@@ -9269,7 +9997,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C186" s="8" t="inlineStr"/>
+      <c r="C186" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D186" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.340)</t>
@@ -9317,7 +10049,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C187" s="8" t="inlineStr"/>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D187" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.320)</t>
@@ -9365,7 +10101,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C188" s="8" t="inlineStr"/>
+      <c r="C188" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D188" s="9" t="inlineStr">
         <is>
           <t>SANTIAGO (2.026.381.020)</t>
@@ -9413,7 +10153,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C189" s="8" t="inlineStr"/>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D189" s="9" t="inlineStr">
         <is>
           <t>SANTIAGO (2.026.381.010)</t>
@@ -9461,7 +10205,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C190" s="8" t="inlineStr"/>
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D190" s="9" t="inlineStr">
         <is>
           <t>SAT 9861 AGROPEC EL ROSARIO AL (260.003.520)</t>
@@ -9509,7 +10257,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C191" s="8" t="inlineStr"/>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D191" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.111)</t>
@@ -9557,7 +10309,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C192" s="8" t="inlineStr"/>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D192" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.052)</t>
@@ -9605,7 +10361,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C193" s="8" t="inlineStr"/>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D193" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.061)</t>
@@ -9653,7 +10413,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C194" s="8" t="inlineStr"/>
+      <c r="C194" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D194" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.131)</t>
@@ -9701,7 +10465,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C195" s="8" t="inlineStr"/>
+      <c r="C195" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D195" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.071)</t>
@@ -9749,7 +10517,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C196" s="8" t="inlineStr"/>
+      <c r="C196" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D196" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.091)</t>
@@ -9797,7 +10569,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C197" s="8" t="inlineStr"/>
+      <c r="C197" s="8" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D197" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.103)</t>
@@ -9845,7 +10621,11 @@
           <t>C-26-26</t>
         </is>
       </c>
-      <c r="C198" s="5" t="inlineStr"/>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>URKAN</t>
+        </is>
+      </c>
       <c r="D198" s="5" t="inlineStr"/>
       <c r="E198" s="5" t="n">
         <v>2</v>
@@ -9889,7 +10669,11 @@
           <t>C-26-26</t>
         </is>
       </c>
-      <c r="C199" s="8" t="inlineStr"/>
+      <c r="C199" s="8" t="inlineStr">
+        <is>
+          <t>URKAN</t>
+        </is>
+      </c>
       <c r="D199" s="9" t="inlineStr">
         <is>
           <t>CAÑAS ESCRIBANO DANIEL CAMPO D (260.003.490)</t>
@@ -9937,7 +10721,11 @@
           <t>C-26-26</t>
         </is>
       </c>
-      <c r="C200" s="8" t="inlineStr"/>
+      <c r="C200" s="8" t="inlineStr">
+        <is>
+          <t>URKAN</t>
+        </is>
+      </c>
       <c r="D200" s="9" t="inlineStr">
         <is>
           <t>PRADILLO MANZANERO PATRICIO CA (260.003.484)</t>
@@ -9985,7 +10773,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C201" s="5" t="inlineStr"/>
+      <c r="C201" s="5" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D201" s="5" t="inlineStr"/>
       <c r="E201" s="5" t="n">
         <v>11</v>
@@ -10029,7 +10821,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C202" s="8" t="inlineStr"/>
+      <c r="C202" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D202" s="9" t="inlineStr">
         <is>
           <t>AGRO MORENO VERA SL AEROPUERTO (260.002.986)</t>
@@ -10077,7 +10873,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C203" s="8" t="inlineStr"/>
+      <c r="C203" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D203" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE ARENALES (260.003.558)</t>
@@ -10125,7 +10925,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C204" s="8" t="inlineStr"/>
+      <c r="C204" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D204" s="9" t="inlineStr">
         <is>
           <t>ANTONIO JOSE MANZANARES CEGARR (260.002.987)</t>
@@ -10173,7 +10977,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C205" s="8" t="inlineStr"/>
+      <c r="C205" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D205" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.243)</t>
@@ -10221,7 +11029,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C206" s="8" t="inlineStr"/>
+      <c r="C206" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D206" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.251)</t>
@@ -10269,7 +11081,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C207" s="8" t="inlineStr"/>
+      <c r="C207" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D207" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.023)</t>
@@ -10317,7 +11133,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C208" s="8" t="inlineStr"/>
+      <c r="C208" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D208" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.031)</t>
@@ -10365,7 +11185,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C209" s="8" t="inlineStr"/>
+      <c r="C209" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D209" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.003.090)</t>
@@ -10413,7 +11237,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C210" s="8" t="inlineStr"/>
+      <c r="C210" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D210" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA JUM (260.003.141)</t>
@@ -10461,7 +11289,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C211" s="8" t="inlineStr"/>
+      <c r="C211" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D211" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA LO (260.003.107)</t>
@@ -10509,7 +11341,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C212" s="8" t="inlineStr"/>
+      <c r="C212" s="8" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D212" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ ARENAL (260.003.560)</t>
@@ -10557,7 +11393,11 @@
           <t>C-26-31</t>
         </is>
       </c>
-      <c r="C213" s="5" t="inlineStr"/>
+      <c r="C213" s="5" t="inlineStr">
+        <is>
+          <t>ORANGELUP</t>
+        </is>
+      </c>
       <c r="D213" s="5" t="inlineStr"/>
       <c r="E213" s="5" t="n">
         <v>1</v>
@@ -10601,7 +11441,11 @@
           <t>C-26-31</t>
         </is>
       </c>
-      <c r="C214" s="8" t="inlineStr"/>
+      <c r="C214" s="8" t="inlineStr">
+        <is>
+          <t>ORANGELUP</t>
+        </is>
+      </c>
       <c r="D214" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA JUM (260.003.290)</t>
@@ -10649,7 +11493,11 @@
           <t>C-26-32</t>
         </is>
       </c>
-      <c r="C215" s="5" t="inlineStr"/>
+      <c r="C215" s="5" t="inlineStr">
+        <is>
+          <t>DELPHES</t>
+        </is>
+      </c>
       <c r="D215" s="5" t="inlineStr"/>
       <c r="E215" s="5" t="n">
         <v>4</v>
@@ -10693,7 +11541,11 @@
           <t>C-26-32</t>
         </is>
       </c>
-      <c r="C216" s="8" t="inlineStr"/>
+      <c r="C216" s="8" t="inlineStr">
+        <is>
+          <t>DELPHES</t>
+        </is>
+      </c>
       <c r="D216" s="9" t="inlineStr">
         <is>
           <t>AGRO MORENO VERA SL AEROPUERTO (260.002.948)</t>
@@ -10741,7 +11593,11 @@
           <t>C-26-32</t>
         </is>
       </c>
-      <c r="C217" s="8" t="inlineStr"/>
+      <c r="C217" s="8" t="inlineStr">
+        <is>
+          <t>DELPHES</t>
+        </is>
+      </c>
       <c r="D217" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.003.090)</t>
@@ -10789,7 +11645,11 @@
           <t>C-26-32</t>
         </is>
       </c>
-      <c r="C218" s="8" t="inlineStr"/>
+      <c r="C218" s="8" t="inlineStr">
+        <is>
+          <t>DELPHES</t>
+        </is>
+      </c>
       <c r="D218" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.002.999)</t>
@@ -10837,7 +11697,11 @@
           <t>C-26-32</t>
         </is>
       </c>
-      <c r="C219" s="8" t="inlineStr"/>
+      <c r="C219" s="8" t="inlineStr">
+        <is>
+          <t>DELPHES</t>
+        </is>
+      </c>
       <c r="D219" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.003.084)</t>
@@ -10933,7 +11797,11 @@
           <t>SEM-14012</t>
         </is>
       </c>
-      <c r="C221" s="5" t="inlineStr"/>
+      <c r="C221" s="5" t="inlineStr">
+        <is>
+          <t>N.14012</t>
+        </is>
+      </c>
       <c r="D221" s="5" t="inlineStr"/>
       <c r="E221" s="5" t="n">
         <v>1</v>
@@ -10977,7 +11845,11 @@
           <t>SEM-14012</t>
         </is>
       </c>
-      <c r="C222" s="8" t="inlineStr"/>
+      <c r="C222" s="8" t="inlineStr">
+        <is>
+          <t>N.14012</t>
+        </is>
+      </c>
       <c r="D222" s="9" t="inlineStr">
         <is>
           <t>HIDROPONICO (2.026.610.020)</t>
@@ -11025,7 +11897,11 @@
           <t>SEM-20-03</t>
         </is>
       </c>
-      <c r="C223" s="5" t="inlineStr"/>
+      <c r="C223" s="5" t="inlineStr">
+        <is>
+          <t>TORUM</t>
+        </is>
+      </c>
       <c r="D223" s="5" t="inlineStr"/>
       <c r="E223" s="5" t="n">
         <v>1</v>
@@ -11069,7 +11945,11 @@
           <t>SEM-20-03</t>
         </is>
       </c>
-      <c r="C224" s="8" t="inlineStr"/>
+      <c r="C224" s="8" t="inlineStr">
+        <is>
+          <t>TORUM</t>
+        </is>
+      </c>
       <c r="D224" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.081)</t>
@@ -11117,7 +11997,11 @@
           <t>SEM-26-03</t>
         </is>
       </c>
-      <c r="C225" s="5" t="inlineStr"/>
+      <c r="C225" s="5" t="inlineStr">
+        <is>
+          <t>TORUM</t>
+        </is>
+      </c>
       <c r="D225" s="5" t="inlineStr"/>
       <c r="E225" s="5" t="n">
         <v>2</v>
@@ -11161,7 +12045,11 @@
           <t>SEM-26-03</t>
         </is>
       </c>
-      <c r="C226" s="8" t="inlineStr"/>
+      <c r="C226" s="8" t="inlineStr">
+        <is>
+          <t>TORUM</t>
+        </is>
+      </c>
       <c r="D226" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.242)</t>
@@ -11209,7 +12097,11 @@
           <t>SEM-26-03</t>
         </is>
       </c>
-      <c r="C227" s="8" t="inlineStr"/>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>TORUM</t>
+        </is>
+      </c>
       <c r="D227" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.511)</t>
@@ -11257,7 +12149,11 @@
           <t>SEM-26-04</t>
         </is>
       </c>
-      <c r="C228" s="5" t="inlineStr"/>
+      <c r="C228" s="5" t="inlineStr">
+        <is>
+          <t>SAINZ</t>
+        </is>
+      </c>
       <c r="D228" s="5" t="inlineStr"/>
       <c r="E228" s="5" t="n">
         <v>3</v>
@@ -11301,7 +12197,11 @@
           <t>SEM-26-04</t>
         </is>
       </c>
-      <c r="C229" s="8" t="inlineStr"/>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>SAINZ</t>
+        </is>
+      </c>
       <c r="D229" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.271)</t>
@@ -11349,7 +12249,11 @@
           <t>SEM-26-04</t>
         </is>
       </c>
-      <c r="C230" s="8" t="inlineStr"/>
+      <c r="C230" s="8" t="inlineStr">
+        <is>
+          <t>SAINZ</t>
+        </is>
+      </c>
       <c r="D230" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.260)</t>
@@ -11397,7 +12301,11 @@
           <t>SEM-26-04</t>
         </is>
       </c>
-      <c r="C231" s="8" t="inlineStr"/>
+      <c r="C231" s="8" t="inlineStr">
+        <is>
+          <t>SAINZ</t>
+        </is>
+      </c>
       <c r="D231" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.081)</t>
@@ -11445,7 +12353,11 @@
           <t>SEM-26-21</t>
         </is>
       </c>
-      <c r="C232" s="5" t="inlineStr"/>
+      <c r="C232" s="5" t="inlineStr">
+        <is>
+          <t>ARAGORN (N.14511)</t>
+        </is>
+      </c>
       <c r="D232" s="5" t="inlineStr"/>
       <c r="E232" s="5" t="n">
         <v>6</v>
@@ -11489,7 +12401,11 @@
           <t>SEM-26-21</t>
         </is>
       </c>
-      <c r="C233" s="8" t="inlineStr"/>
+      <c r="C233" s="8" t="inlineStr">
+        <is>
+          <t>ARAGORN (N.14511)</t>
+        </is>
+      </c>
       <c r="D233" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.260)</t>
@@ -11537,7 +12453,11 @@
           <t>SEM-26-21</t>
         </is>
       </c>
-      <c r="C234" s="8" t="inlineStr"/>
+      <c r="C234" s="8" t="inlineStr">
+        <is>
+          <t>ARAGORN (N.14511)</t>
+        </is>
+      </c>
       <c r="D234" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.240)</t>
@@ -11585,7 +12505,11 @@
           <t>SEM-26-21</t>
         </is>
       </c>
-      <c r="C235" s="8" t="inlineStr"/>
+      <c r="C235" s="8" t="inlineStr">
+        <is>
+          <t>ARAGORN (N.14511)</t>
+        </is>
+      </c>
       <c r="D235" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.250)</t>
@@ -11633,7 +12557,11 @@
           <t>SEM-26-21</t>
         </is>
       </c>
-      <c r="C236" s="8" t="inlineStr"/>
+      <c r="C236" s="8" t="inlineStr">
+        <is>
+          <t>ARAGORN (N.14511)</t>
+        </is>
+      </c>
       <c r="D236" s="9" t="inlineStr">
         <is>
           <t>HIDROPONICO (2.026.610.020)</t>
@@ -11681,7 +12609,11 @@
           <t>SEM-26-21</t>
         </is>
       </c>
-      <c r="C237" s="8" t="inlineStr"/>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>ARAGORN (N.14511)</t>
+        </is>
+      </c>
       <c r="D237" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.180)</t>
@@ -11729,7 +12661,11 @@
           <t>SEM-26-21</t>
         </is>
       </c>
-      <c r="C238" s="8" t="inlineStr"/>
+      <c r="C238" s="8" t="inlineStr">
+        <is>
+          <t>ARAGORN (N.14511)</t>
+        </is>
+      </c>
       <c r="D238" s="9" t="inlineStr">
         <is>
           <t>MEROÑO MARTINEZ EUGENIO LOS IN (260.002.949)</t>
@@ -11777,7 +12713,11 @@
           <t>SEM-26-22</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr"/>
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>DELAROSA</t>
+        </is>
+      </c>
       <c r="D239" s="5" t="inlineStr"/>
       <c r="E239" s="5" t="n">
         <v>5</v>
@@ -11821,7 +12761,11 @@
           <t>SEM-26-22</t>
         </is>
       </c>
-      <c r="C240" s="8" t="inlineStr"/>
+      <c r="C240" s="8" t="inlineStr">
+        <is>
+          <t>DELAROSA</t>
+        </is>
+      </c>
       <c r="D240" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.250)</t>
@@ -11869,7 +12813,11 @@
           <t>SEM-26-22</t>
         </is>
       </c>
-      <c r="C241" s="8" t="inlineStr"/>
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>DELAROSA</t>
+        </is>
+      </c>
       <c r="D241" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.240)</t>
@@ -11917,7 +12865,11 @@
           <t>SEM-26-22</t>
         </is>
       </c>
-      <c r="C242" s="8" t="inlineStr"/>
+      <c r="C242" s="8" t="inlineStr">
+        <is>
+          <t>DELAROSA</t>
+        </is>
+      </c>
       <c r="D242" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.271)</t>
@@ -11959,7 +12911,11 @@
           <t>SEM-26-22</t>
         </is>
       </c>
-      <c r="C243" s="8" t="inlineStr"/>
+      <c r="C243" s="8" t="inlineStr">
+        <is>
+          <t>DELAROSA</t>
+        </is>
+      </c>
       <c r="D243" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.180)</t>
@@ -12007,7 +12963,11 @@
           <t>SEM-26-22</t>
         </is>
       </c>
-      <c r="C244" s="8" t="inlineStr"/>
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>DELAROSA</t>
+        </is>
+      </c>
       <c r="D244" s="9" t="inlineStr">
         <is>
           <t>MEROÑO MARTINEZ EUGENIO LOS IN (260.002.950)</t>
@@ -12055,7 +13015,11 @@
           <t>SEM-26-24</t>
         </is>
       </c>
-      <c r="C245" s="5" t="inlineStr"/>
+      <c r="C245" s="5" t="inlineStr">
+        <is>
+          <t>SEANETO</t>
+        </is>
+      </c>
       <c r="D245" s="5" t="inlineStr"/>
       <c r="E245" s="5" t="n">
         <v>5</v>
@@ -12099,7 +13063,11 @@
           <t>SEM-26-24</t>
         </is>
       </c>
-      <c r="C246" s="8" t="inlineStr"/>
+      <c r="C246" s="8" t="inlineStr">
+        <is>
+          <t>SEANETO</t>
+        </is>
+      </c>
       <c r="D246" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.392)</t>
@@ -12147,7 +13115,11 @@
           <t>SEM-26-24</t>
         </is>
       </c>
-      <c r="C247" s="8" t="inlineStr"/>
+      <c r="C247" s="8" t="inlineStr">
+        <is>
+          <t>SEANETO</t>
+        </is>
+      </c>
       <c r="D247" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.072)</t>
@@ -12195,7 +13167,11 @@
           <t>SEM-26-24</t>
         </is>
       </c>
-      <c r="C248" s="8" t="inlineStr"/>
+      <c r="C248" s="8" t="inlineStr">
+        <is>
+          <t>SEANETO</t>
+        </is>
+      </c>
       <c r="D248" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.062)</t>
@@ -12243,7 +13219,11 @@
           <t>SEM-26-24</t>
         </is>
       </c>
-      <c r="C249" s="8" t="inlineStr"/>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>SEANETO</t>
+        </is>
+      </c>
       <c r="D249" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.104)</t>
@@ -12291,7 +13271,11 @@
           <t>SEM-26-24</t>
         </is>
       </c>
-      <c r="C250" s="8" t="inlineStr"/>
+      <c r="C250" s="8" t="inlineStr">
+        <is>
+          <t>SEANETO</t>
+        </is>
+      </c>
       <c r="D250" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.113)</t>
@@ -12339,7 +13323,11 @@
           <t>SEM-26-28</t>
         </is>
       </c>
-      <c r="C251" s="5" t="inlineStr"/>
+      <c r="C251" s="5" t="inlineStr">
+        <is>
+          <t>SVMC0019 (ACAPELLA)</t>
+        </is>
+      </c>
       <c r="D251" s="5" t="inlineStr"/>
       <c r="E251" s="5" t="n">
         <v>2</v>
@@ -12383,7 +13371,11 @@
           <t>SEM-26-28</t>
         </is>
       </c>
-      <c r="C252" s="8" t="inlineStr"/>
+      <c r="C252" s="8" t="inlineStr">
+        <is>
+          <t>SVMC0019 (ACAPELLA)</t>
+        </is>
+      </c>
       <c r="D252" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.281)</t>
@@ -12431,7 +13423,11 @@
           <t>SEM-26-28</t>
         </is>
       </c>
-      <c r="C253" s="8" t="inlineStr"/>
+      <c r="C253" s="8" t="inlineStr">
+        <is>
+          <t>SVMC0019 (ACAPELLA)</t>
+        </is>
+      </c>
       <c r="D253" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.232)</t>
@@ -12479,7 +13475,11 @@
           <t>SEM-26-30</t>
         </is>
       </c>
-      <c r="C254" s="5" t="inlineStr"/>
+      <c r="C254" s="5" t="inlineStr">
+        <is>
+          <t>BONOBO</t>
+        </is>
+      </c>
       <c r="D254" s="5" t="inlineStr"/>
       <c r="E254" s="5" t="n">
         <v>4</v>
@@ -12523,7 +13523,11 @@
           <t>SEM-26-30</t>
         </is>
       </c>
-      <c r="C255" s="8" t="inlineStr"/>
+      <c r="C255" s="8" t="inlineStr">
+        <is>
+          <t>BONOBO</t>
+        </is>
+      </c>
       <c r="D255" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.091)</t>
@@ -12571,7 +13575,11 @@
           <t>SEM-26-30</t>
         </is>
       </c>
-      <c r="C256" s="8" t="inlineStr"/>
+      <c r="C256" s="8" t="inlineStr">
+        <is>
+          <t>BONOBO</t>
+        </is>
+      </c>
       <c r="D256" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.912)</t>
@@ -12619,7 +13627,11 @@
           <t>SEM-26-30</t>
         </is>
       </c>
-      <c r="C257" s="8" t="inlineStr"/>
+      <c r="C257" s="8" t="inlineStr">
+        <is>
+          <t>BONOBO</t>
+        </is>
+      </c>
       <c r="D257" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.942)</t>
@@ -12667,7 +13679,11 @@
           <t>SEM-26-30</t>
         </is>
       </c>
-      <c r="C258" s="8" t="inlineStr"/>
+      <c r="C258" s="8" t="inlineStr">
+        <is>
+          <t>BONOBO</t>
+        </is>
+      </c>
       <c r="D258" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.132)</t>
@@ -12763,7 +13779,11 @@
           <t>G-20-02</t>
         </is>
       </c>
-      <c r="C260" s="5" t="inlineStr"/>
+      <c r="C260" s="5" t="inlineStr">
+        <is>
+          <t>KINDER (G 37526)</t>
+        </is>
+      </c>
       <c r="D260" s="5" t="inlineStr"/>
       <c r="E260" s="5" t="n">
         <v>1</v>
@@ -12807,7 +13827,11 @@
           <t>G-20-02</t>
         </is>
       </c>
-      <c r="C261" s="8" t="inlineStr"/>
+      <c r="C261" s="8" t="inlineStr">
+        <is>
+          <t>KINDER (G 37526)</t>
+        </is>
+      </c>
       <c r="D261" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.030)</t>
@@ -12855,7 +13879,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C262" s="5" t="inlineStr"/>
+      <c r="C262" s="5" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D262" s="5" t="inlineStr"/>
       <c r="E262" s="5" t="n">
         <v>24</v>
@@ -12899,7 +13927,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C263" s="8" t="inlineStr"/>
+      <c r="C263" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D263" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.372)</t>
@@ -12947,7 +13979,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C264" s="8" t="inlineStr"/>
+      <c r="C264" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
           <t>CAMPOS DE CASTILLA SL CAMPO DE (260.003.553)</t>
@@ -12995,7 +14031,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C265" s="8" t="inlineStr"/>
+      <c r="C265" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D265" s="9" t="inlineStr">
         <is>
           <t>EL ALJIBE (2.026.394.050)</t>
@@ -13043,7 +14083,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C266" s="8" t="inlineStr"/>
+      <c r="C266" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D266" s="9" t="inlineStr">
         <is>
           <t>EL ALJIBE (2.026.394.060)</t>
@@ -13091,7 +14135,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C267" s="8" t="inlineStr"/>
+      <c r="C267" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.112)</t>
@@ -13139,7 +14187,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C268" s="8" t="inlineStr"/>
+      <c r="C268" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D268" s="9" t="inlineStr">
         <is>
           <t>JUAN GARRE HERNANDEZ LUGAR NUE (260.003.134)</t>
@@ -13187,7 +14239,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C269" s="8" t="inlineStr"/>
+      <c r="C269" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D269" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA LOS (260.003.044)</t>
@@ -13235,7 +14291,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C270" s="8" t="inlineStr"/>
+      <c r="C270" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D270" s="9" t="inlineStr">
         <is>
           <t>LOPEZ ESCRIBANO MIGUEL ANGEL A (260.003.519)</t>
@@ -13283,7 +14343,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C271" s="8" t="inlineStr"/>
+      <c r="C271" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D271" s="9" t="inlineStr">
         <is>
           <t>LUCERON LUCAS TORRES JESUS CAM (260.003.303)</t>
@@ -13331,7 +14395,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C272" s="8" t="inlineStr"/>
+      <c r="C272" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D272" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.121)</t>
@@ -13379,7 +14447,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C273" s="8" t="inlineStr"/>
+      <c r="C273" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D273" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.140)</t>
@@ -13427,7 +14499,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C274" s="8" t="inlineStr"/>
+      <c r="C274" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D274" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.180)</t>
@@ -13475,7 +14551,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C275" s="8" t="inlineStr"/>
+      <c r="C275" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D275" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.151)</t>
@@ -13523,7 +14603,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C276" s="8" t="inlineStr"/>
+      <c r="C276" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D276" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.130)</t>
@@ -13571,7 +14655,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C277" s="8" t="inlineStr"/>
+      <c r="C277" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D277" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.040)</t>
@@ -13619,7 +14707,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C278" s="8" t="inlineStr"/>
+      <c r="C278" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D278" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.130)</t>
@@ -13667,7 +14759,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C279" s="8" t="inlineStr"/>
+      <c r="C279" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D279" s="9" t="inlineStr">
         <is>
           <t>RAMOS CRUZ ANGEL ALCAZAR DE SA (260.003.541)</t>
@@ -13715,7 +14811,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C280" s="8" t="inlineStr"/>
+      <c r="C280" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D280" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.060)</t>
@@ -13763,7 +14863,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C281" s="8" t="inlineStr"/>
+      <c r="C281" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D281" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.100)</t>
@@ -13811,7 +14915,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C282" s="8" t="inlineStr"/>
+      <c r="C282" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D282" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.091)</t>
@@ -13859,7 +14967,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C283" s="8" t="inlineStr"/>
+      <c r="C283" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D283" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.070)</t>
@@ -13907,7 +15019,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C284" s="8" t="inlineStr"/>
+      <c r="C284" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D284" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.081)</t>
@@ -13955,7 +15071,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C285" s="8" t="inlineStr"/>
+      <c r="C285" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D285" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.110)</t>
@@ -14003,7 +15123,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C286" s="8" t="inlineStr"/>
+      <c r="C286" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D286" s="9" t="inlineStr">
         <is>
           <t>VELA LOPEZ DE LA RICA Mª PAZ A (260.003.550)</t>
@@ -14051,7 +15175,11 @@
           <t>G-26-04</t>
         </is>
       </c>
-      <c r="C287" s="5" t="inlineStr"/>
+      <c r="C287" s="5" t="inlineStr">
+        <is>
+          <t>KINETIC</t>
+        </is>
+      </c>
       <c r="D287" s="5" t="inlineStr"/>
       <c r="E287" s="5" t="n">
         <v>7</v>
@@ -14095,7 +15223,11 @@
           <t>G-26-04</t>
         </is>
       </c>
-      <c r="C288" s="8" t="inlineStr"/>
+      <c r="C288" s="8" t="inlineStr">
+        <is>
+          <t>KINETIC</t>
+        </is>
+      </c>
       <c r="D288" s="9" t="inlineStr">
         <is>
           <t>AGROMAJANAR CONSULTING SL CAMP (260.003.503)</t>
@@ -14143,7 +15275,11 @@
           <t>G-26-04</t>
         </is>
       </c>
-      <c r="C289" s="8" t="inlineStr"/>
+      <c r="C289" s="8" t="inlineStr">
+        <is>
+          <t>KINETIC</t>
+        </is>
+      </c>
       <c r="D289" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.470)</t>
@@ -14191,7 +15327,11 @@
           <t>G-26-04</t>
         </is>
       </c>
-      <c r="C290" s="8" t="inlineStr"/>
+      <c r="C290" s="8" t="inlineStr">
+        <is>
+          <t>KINETIC</t>
+        </is>
+      </c>
       <c r="D290" s="9" t="inlineStr">
         <is>
           <t>ESCRIBANO MINGUEZ EUGENIO AREN (260.003.521)</t>
@@ -14239,7 +15379,11 @@
           <t>G-26-04</t>
         </is>
       </c>
-      <c r="C291" s="8" t="inlineStr"/>
+      <c r="C291" s="8" t="inlineStr">
+        <is>
+          <t>KINETIC</t>
+        </is>
+      </c>
       <c r="D291" s="9" t="inlineStr">
         <is>
           <t>ESCRIBANO MINGUEZ EUGENIO CAMP (260.003.504)</t>
@@ -14287,7 +15431,11 @@
           <t>G-26-04</t>
         </is>
       </c>
-      <c r="C292" s="8" t="inlineStr"/>
+      <c r="C292" s="8" t="inlineStr">
+        <is>
+          <t>KINETIC</t>
+        </is>
+      </c>
       <c r="D292" s="9" t="inlineStr">
         <is>
           <t>LARA ANGULO JUSTO ARENALES DE (260.003.517)</t>
@@ -14335,7 +15483,11 @@
           <t>G-26-04</t>
         </is>
       </c>
-      <c r="C293" s="8" t="inlineStr"/>
+      <c r="C293" s="8" t="inlineStr">
+        <is>
+          <t>KINETIC</t>
+        </is>
+      </c>
       <c r="D293" s="9" t="inlineStr">
         <is>
           <t>LOPEZ ESCRIBANO MIGUEL ANGEL A (260.003.508)</t>
@@ -14383,7 +15535,11 @@
           <t>G-26-04</t>
         </is>
       </c>
-      <c r="C294" s="8" t="inlineStr"/>
+      <c r="C294" s="8" t="inlineStr">
+        <is>
+          <t>KINETIC</t>
+        </is>
+      </c>
       <c r="D294" s="9" t="inlineStr">
         <is>
           <t>RAMOS CRUZ ANGEL ALCAZAR DE SA (260.003.540)</t>
@@ -14431,7 +15587,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C295" s="5" t="inlineStr"/>
+      <c r="C295" s="5" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D295" s="5" t="inlineStr"/>
       <c r="E295" s="5" t="n">
         <v>16</v>
@@ -14475,7 +15635,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C296" s="8" t="inlineStr"/>
+      <c r="C296" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D296" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE CAMPO DE (260.003.316)</t>
@@ -14523,7 +15687,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C297" s="8" t="inlineStr"/>
+      <c r="C297" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D297" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.460)</t>
@@ -14571,7 +15739,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C298" s="8" t="inlineStr"/>
+      <c r="C298" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D298" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.430)</t>
@@ -14619,7 +15791,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C299" s="8" t="inlineStr"/>
+      <c r="C299" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D299" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.410)</t>
@@ -14667,7 +15843,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C300" s="8" t="inlineStr"/>
+      <c r="C300" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D300" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.420)</t>
@@ -14715,7 +15895,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C301" s="8" t="inlineStr"/>
+      <c r="C301" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D301" s="9" t="inlineStr">
         <is>
           <t>CAÑAS ESCRIBANO DANIEL CAMPO D (260.003.425)</t>
@@ -14763,7 +15947,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C302" s="8" t="inlineStr"/>
+      <c r="C302" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D302" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA RIN (260.003.045)</t>
@@ -14811,7 +15999,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C303" s="8" t="inlineStr"/>
+      <c r="C303" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D303" s="9" t="inlineStr">
         <is>
           <t>LOPEZ DE LA RICA VELA MARIO AL (260.003.506)</t>
@@ -14859,7 +16051,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C304" s="8" t="inlineStr"/>
+      <c r="C304" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D304" s="9" t="inlineStr">
         <is>
           <t>LOPEZ DE LA RICA VELA MARIO AL (260.003.307)</t>
@@ -14907,7 +16103,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C305" s="8" t="inlineStr"/>
+      <c r="C305" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D305" s="9" t="inlineStr">
         <is>
           <t>LOPEZ ESCRIBANO MIGUEL ANGEL A (260.003.509)</t>
@@ -14955,7 +16155,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C306" s="8" t="inlineStr"/>
+      <c r="C306" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D306" s="9" t="inlineStr">
         <is>
           <t>LOPEZ ESCRIBANO MIGUEL ANGEL A (260.003.508)</t>
@@ -15003,7 +16207,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C307" s="8" t="inlineStr"/>
+      <c r="C307" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D307" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ CAMPO (260.003.319)</t>
@@ -15051,7 +16259,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C308" s="8" t="inlineStr"/>
+      <c r="C308" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D308" s="9" t="inlineStr">
         <is>
           <t>MERINO FERNANDEZ ALVARO ALCAZA (260.003.320)</t>
@@ -15099,7 +16311,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C309" s="8" t="inlineStr"/>
+      <c r="C309" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D309" s="9" t="inlineStr">
         <is>
           <t>PRADILLO MANZANERO PATRICIO CA (260.003.424)</t>
@@ -15147,7 +16363,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C310" s="8" t="inlineStr"/>
+      <c r="C310" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D310" s="9" t="inlineStr">
         <is>
           <t>VELA BASTANTE RUBEN CAMPO DE C (260.003.502)</t>
@@ -15195,7 +16415,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C311" s="8" t="inlineStr"/>
+      <c r="C311" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D311" s="9" t="inlineStr">
         <is>
           <t>VELA LOPEZ DE LA RICA Mª PAZ A (260.003.550)</t>
@@ -15243,7 +16467,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C312" s="5" t="inlineStr"/>
+      <c r="C312" s="5" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D312" s="5" t="inlineStr"/>
       <c r="E312" s="5" t="n">
         <v>28</v>
@@ -15287,7 +16515,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C313" s="8" t="inlineStr"/>
+      <c r="C313" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D313" s="9" t="inlineStr">
         <is>
           <t>ARICOS (2.026.377.020)</t>
@@ -15335,7 +16567,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C314" s="8" t="inlineStr"/>
+      <c r="C314" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D314" s="9" t="inlineStr">
         <is>
           <t>ARICOS (2.026.377.010)</t>
@@ -15383,7 +16619,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C315" s="8" t="inlineStr"/>
+      <c r="C315" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D315" s="9" t="inlineStr">
         <is>
           <t>ARICOS (2.026.377.040)</t>
@@ -15431,7 +16671,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C316" s="8" t="inlineStr"/>
+      <c r="C316" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D316" s="9" t="inlineStr">
         <is>
           <t>ARICOS (2.026.377.030)</t>
@@ -15479,7 +16723,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C317" s="8" t="inlineStr"/>
+      <c r="C317" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D317" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.290)</t>
@@ -15527,7 +16775,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C318" s="8" t="inlineStr"/>
+      <c r="C318" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D318" s="9" t="inlineStr">
         <is>
           <t>COPE (2.026.340.300)</t>
@@ -15575,7 +16827,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C319" s="8" t="inlineStr"/>
+      <c r="C319" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D319" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.034)</t>
@@ -15623,7 +16879,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C320" s="8" t="inlineStr"/>
+      <c r="C320" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D320" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.002.941)</t>
@@ -15671,7 +16931,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C321" s="8" t="inlineStr"/>
+      <c r="C321" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D321" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA RIN (260.003.045)</t>
@@ -15719,7 +16983,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C322" s="8" t="inlineStr"/>
+      <c r="C322" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D322" s="9" t="inlineStr">
         <is>
           <t>LOS CANOVAS (2.026.332.010)</t>
@@ -15767,7 +17035,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C323" s="8" t="inlineStr"/>
+      <c r="C323" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D323" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.050)</t>
@@ -15815,7 +17087,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C324" s="8" t="inlineStr"/>
+      <c r="C324" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D324" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.030)</t>
@@ -15863,7 +17139,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C325" s="8" t="inlineStr"/>
+      <c r="C325" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D325" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.070)</t>
@@ -15911,7 +17191,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C326" s="8" t="inlineStr"/>
+      <c r="C326" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D326" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.090)</t>
@@ -15959,7 +17243,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C327" s="8" t="inlineStr"/>
+      <c r="C327" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D327" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.120)</t>
@@ -16007,7 +17295,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C328" s="8" t="inlineStr"/>
+      <c r="C328" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D328" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.080)</t>
@@ -16055,7 +17347,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C329" s="8" t="inlineStr"/>
+      <c r="C329" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D329" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.060)</t>
@@ -16103,7 +17399,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C330" s="8" t="inlineStr"/>
+      <c r="C330" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D330" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.130)</t>
@@ -16151,7 +17451,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C331" s="8" t="inlineStr"/>
+      <c r="C331" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D331" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.020)</t>
@@ -16199,7 +17503,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C332" s="8" t="inlineStr"/>
+      <c r="C332" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D332" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.100)</t>
@@ -16247,7 +17555,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C333" s="8" t="inlineStr"/>
+      <c r="C333" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D333" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.110)</t>
@@ -16295,7 +17607,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C334" s="8" t="inlineStr"/>
+      <c r="C334" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D334" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.040)</t>
@@ -16343,7 +17659,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C335" s="8" t="inlineStr"/>
+      <c r="C335" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D335" s="9" t="inlineStr">
         <is>
           <t>MANZANARES (2.026.315.010)</t>
@@ -16391,7 +17711,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C336" s="8" t="inlineStr"/>
+      <c r="C336" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D336" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.100)</t>
@@ -16439,7 +17763,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C337" s="8" t="inlineStr"/>
+      <c r="C337" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D337" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.060)</t>
@@ -16487,7 +17815,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C338" s="8" t="inlineStr"/>
+      <c r="C338" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.020)</t>
@@ -16535,7 +17867,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C339" s="8" t="inlineStr"/>
+      <c r="C339" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D339" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.030)</t>
@@ -16583,7 +17919,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C340" s="8" t="inlineStr"/>
+      <c r="C340" s="8" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D340" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.040)</t>
@@ -16631,7 +17971,11 @@
           <t>G-26-14</t>
         </is>
       </c>
-      <c r="C341" s="5" t="inlineStr"/>
+      <c r="C341" s="5" t="inlineStr">
+        <is>
+          <t>KIONNA</t>
+        </is>
+      </c>
       <c r="D341" s="5" t="inlineStr"/>
       <c r="E341" s="5" t="n">
         <v>6</v>
@@ -16675,7 +18019,11 @@
           <t>G-26-14</t>
         </is>
       </c>
-      <c r="C342" s="8" t="inlineStr"/>
+      <c r="C342" s="8" t="inlineStr">
+        <is>
+          <t>KIONNA</t>
+        </is>
+      </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.410)</t>
@@ -16723,7 +18071,11 @@
           <t>G-26-14</t>
         </is>
       </c>
-      <c r="C343" s="8" t="inlineStr"/>
+      <c r="C343" s="8" t="inlineStr">
+        <is>
+          <t>KIONNA</t>
+        </is>
+      </c>
       <c r="D343" s="9" t="inlineStr">
         <is>
           <t>CAÑAS ESCRIBANO DANIEL CAMPO D (260.003.489)</t>
@@ -16771,7 +18123,11 @@
           <t>G-26-14</t>
         </is>
       </c>
-      <c r="C344" s="8" t="inlineStr"/>
+      <c r="C344" s="8" t="inlineStr">
+        <is>
+          <t>KIONNA</t>
+        </is>
+      </c>
       <c r="D344" s="9" t="inlineStr">
         <is>
           <t>CAÑAS PINTOR FRANCISCO ARENALE (260.003.420)</t>
@@ -16819,7 +18175,11 @@
           <t>G-26-14</t>
         </is>
       </c>
-      <c r="C345" s="8" t="inlineStr"/>
+      <c r="C345" s="8" t="inlineStr">
+        <is>
+          <t>KIONNA</t>
+        </is>
+      </c>
       <c r="D345" s="9" t="inlineStr">
         <is>
           <t>PINTOR LOPEZ DE LA RICA PEDRO (260.003.419)</t>
@@ -16867,7 +18227,11 @@
           <t>G-26-14</t>
         </is>
       </c>
-      <c r="C346" s="8" t="inlineStr"/>
+      <c r="C346" s="8" t="inlineStr">
+        <is>
+          <t>KIONNA</t>
+        </is>
+      </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
           <t>PRADILLO MANZANERO PATRICIO CA (260.003.488)</t>
@@ -16915,7 +18279,11 @@
           <t>G-26-14</t>
         </is>
       </c>
-      <c r="C347" s="8" t="inlineStr"/>
+      <c r="C347" s="8" t="inlineStr">
+        <is>
+          <t>KIONNA</t>
+        </is>
+      </c>
       <c r="D347" s="9" t="inlineStr">
         <is>
           <t>PRADILLO MANZANERO PATRICIO CA (260.003.424)</t>
@@ -16963,7 +18331,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C348" s="5" t="inlineStr"/>
+      <c r="C348" s="5" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D348" s="5" t="inlineStr"/>
       <c r="E348" s="5" t="n">
         <v>19</v>
@@ -17007,7 +18379,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C349" s="8" t="inlineStr"/>
+      <c r="C349" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D349" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.046)</t>
@@ -17055,7 +18431,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C350" s="8" t="inlineStr"/>
+      <c r="C350" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.112)</t>
@@ -17103,7 +18483,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C351" s="8" t="inlineStr"/>
+      <c r="C351" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D351" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.108)</t>
@@ -17151,7 +18535,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C352" s="8" t="inlineStr"/>
+      <c r="C352" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.034)</t>
@@ -17199,7 +18587,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C353" s="8" t="inlineStr"/>
+      <c r="C353" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D353" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA CAS (260.002.992)</t>
@@ -17247,7 +18639,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C354" s="8" t="inlineStr"/>
+      <c r="C354" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
           <t>LOS CANOVAS (2.026.332.050)</t>
@@ -17295,7 +18691,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C355" s="8" t="inlineStr"/>
+      <c r="C355" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D355" s="9" t="inlineStr">
         <is>
           <t>LOS CANOVAS (2.026.332.060)</t>
@@ -17343,7 +18743,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C356" s="8" t="inlineStr"/>
+      <c r="C356" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
           <t>LOS CANOVAS (2.026.332.040)</t>
@@ -17391,7 +18795,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C357" s="8" t="inlineStr"/>
+      <c r="C357" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D357" s="9" t="inlineStr">
         <is>
           <t>LOS CANOVAS (2.026.332.070)</t>
@@ -17439,7 +18847,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C358" s="8" t="inlineStr"/>
+      <c r="C358" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
           <t>LOS CANOVAS (2.026.332.020)</t>
@@ -17487,7 +18899,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C359" s="8" t="inlineStr"/>
+      <c r="C359" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D359" s="9" t="inlineStr">
         <is>
           <t>LOS CANOVAS (2.026.332.080)</t>
@@ -17535,7 +18951,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C360" s="8" t="inlineStr"/>
+      <c r="C360" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
           <t>LOS CANOVAS (2.026.332.030)</t>
@@ -17583,7 +19003,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C361" s="8" t="inlineStr"/>
+      <c r="C361" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D361" s="9" t="inlineStr">
         <is>
           <t>MURPLACA SL EL PERETON 18/202 (260.003.136)</t>
@@ -17631,7 +19055,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C362" s="8" t="inlineStr"/>
+      <c r="C362" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.060)</t>
@@ -17679,7 +19107,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C363" s="8" t="inlineStr"/>
+      <c r="C363" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D363" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.050)</t>
@@ -17727,7 +19159,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C364" s="8" t="inlineStr"/>
+      <c r="C364" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D364" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.020)</t>
@@ -17775,7 +19211,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C365" s="8" t="inlineStr"/>
+      <c r="C365" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D365" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.030)</t>
@@ -17823,7 +19263,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C366" s="8" t="inlineStr"/>
+      <c r="C366" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D366" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.010)</t>
@@ -17871,7 +19315,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C367" s="8" t="inlineStr"/>
+      <c r="C367" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D367" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.040)</t>
@@ -17919,7 +19367,11 @@
           <t>G-67054</t>
         </is>
       </c>
-      <c r="C368" s="5" t="inlineStr"/>
+      <c r="C368" s="5" t="inlineStr">
+        <is>
+          <t>N.67054</t>
+        </is>
+      </c>
       <c r="D368" s="5" t="inlineStr"/>
       <c r="E368" s="5" t="n">
         <v>1</v>
@@ -17963,7 +19415,11 @@
           <t>G-67054</t>
         </is>
       </c>
-      <c r="C369" s="8" t="inlineStr"/>
+      <c r="C369" s="8" t="inlineStr">
+        <is>
+          <t>N.67054</t>
+        </is>
+      </c>
       <c r="D369" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.010)</t>
@@ -18059,7 +19515,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C371" s="5" t="inlineStr"/>
+      <c r="C371" s="5" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D371" s="5" t="inlineStr"/>
       <c r="E371" s="5" t="n">
         <v>1</v>
@@ -18103,7 +19563,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C372" s="8" t="inlineStr"/>
+      <c r="C372" s="8" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D372" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.002.998)</t>
@@ -18151,7 +19615,11 @@
           <t>GLV-26-02</t>
         </is>
       </c>
-      <c r="C373" s="5" t="inlineStr"/>
+      <c r="C373" s="5" t="inlineStr">
+        <is>
+          <t>SV5133MG</t>
+        </is>
+      </c>
       <c r="D373" s="5" t="inlineStr"/>
       <c r="E373" s="5" t="n">
         <v>2</v>
@@ -18195,7 +19663,11 @@
           <t>GLV-26-02</t>
         </is>
       </c>
-      <c r="C374" s="8" t="inlineStr"/>
+      <c r="C374" s="8" t="inlineStr">
+        <is>
+          <t>SV5133MG</t>
+        </is>
+      </c>
       <c r="D374" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE CAMPO DE (260.003.313)</t>
@@ -18243,7 +19715,11 @@
           <t>GLV-26-02</t>
         </is>
       </c>
-      <c r="C375" s="8" t="inlineStr"/>
+      <c r="C375" s="8" t="inlineStr">
+        <is>
+          <t>SV5133MG</t>
+        </is>
+      </c>
       <c r="D375" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ CAMPO (260.003.302)</t>
@@ -18291,7 +19767,11 @@
           <t>GLV-26-04</t>
         </is>
       </c>
-      <c r="C376" s="5" t="inlineStr"/>
+      <c r="C376" s="5" t="inlineStr">
+        <is>
+          <t>PACHANGA (HMC463936)</t>
+        </is>
+      </c>
       <c r="D376" s="5" t="inlineStr"/>
       <c r="E376" s="5" t="n">
         <v>1</v>
@@ -18335,7 +19815,11 @@
           <t>GLV-26-04</t>
         </is>
       </c>
-      <c r="C377" s="8" t="inlineStr"/>
+      <c r="C377" s="8" t="inlineStr">
+        <is>
+          <t>PACHANGA (HMC463936)</t>
+        </is>
+      </c>
       <c r="D377" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.002.998)</t>
@@ -18383,7 +19867,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="C378" s="5" t="inlineStr"/>
+      <c r="C378" s="5" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
       <c r="D378" s="5" t="inlineStr"/>
       <c r="E378" s="5" t="n">
         <v>8</v>
@@ -18427,7 +19915,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="C379" s="8" t="inlineStr"/>
+      <c r="C379" s="8" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
       <c r="D379" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.193)</t>
@@ -18475,7 +19967,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="C380" s="8" t="inlineStr"/>
+      <c r="C380" s="8" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
       <c r="D380" s="9" t="inlineStr">
         <is>
           <t>CAMPOS DE CASTILLA SL CAMPO DE (260.003.555)</t>
@@ -18523,7 +20019,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="C381" s="8" t="inlineStr"/>
+      <c r="C381" s="8" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
       <c r="D381" s="9" t="inlineStr">
         <is>
           <t>COSTA SIMON ANTONIO JOSE FLOTA (260.003.143)</t>
@@ -18571,7 +20071,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="C382" s="8" t="inlineStr"/>
+      <c r="C382" s="8" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
       <c r="D382" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.002.947)</t>
@@ -18619,7 +20123,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="C383" s="8" t="inlineStr"/>
+      <c r="C383" s="8" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
       <c r="D383" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA CAS (260.003.133)</t>
@@ -18667,7 +20175,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="C384" s="8" t="inlineStr"/>
+      <c r="C384" s="8" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
       <c r="D384" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA LOS (260.003.241)</t>
@@ -18715,7 +20227,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="C385" s="8" t="inlineStr"/>
+      <c r="C385" s="8" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
       <c r="D385" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA PIL (260.003.439)</t>
@@ -18763,7 +20279,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="C386" s="8" t="inlineStr"/>
+      <c r="C386" s="8" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
       <c r="D386" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA RIN (260.003.590)</t>
@@ -18811,7 +20331,11 @@
           <t>GLV-26-22</t>
         </is>
       </c>
-      <c r="C387" s="5" t="inlineStr"/>
+      <c r="C387" s="5" t="inlineStr">
+        <is>
+          <t>ANGLIRU (34-GE0337)</t>
+        </is>
+      </c>
       <c r="D387" s="5" t="inlineStr"/>
       <c r="E387" s="5" t="n">
         <v>1</v>
@@ -18855,7 +20379,11 @@
           <t>GLV-26-22</t>
         </is>
       </c>
-      <c r="C388" s="8" t="inlineStr"/>
+      <c r="C388" s="8" t="inlineStr">
+        <is>
+          <t>ANGLIRU (34-GE0337)</t>
+        </is>
+      </c>
       <c r="D388" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.003.036)</t>
@@ -18903,7 +20431,11 @@
           <t>GLV-26-27</t>
         </is>
       </c>
-      <c r="C389" s="5" t="inlineStr"/>
+      <c r="C389" s="5" t="inlineStr">
+        <is>
+          <t>GALUNA LITHIUM (34-GL0401)</t>
+        </is>
+      </c>
       <c r="D389" s="5" t="inlineStr"/>
       <c r="E389" s="5" t="n">
         <v>5</v>
@@ -18947,7 +20479,11 @@
           <t>GLV-26-27</t>
         </is>
       </c>
-      <c r="C390" s="8" t="inlineStr"/>
+      <c r="C390" s="8" t="inlineStr">
+        <is>
+          <t>GALUNA LITHIUM (34-GL0401)</t>
+        </is>
+      </c>
       <c r="D390" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE ARENALES (260.003.525)</t>
@@ -18995,7 +20531,11 @@
           <t>GLV-26-27</t>
         </is>
       </c>
-      <c r="C391" s="8" t="inlineStr"/>
+      <c r="C391" s="8" t="inlineStr">
+        <is>
+          <t>GALUNA LITHIUM (34-GL0401)</t>
+        </is>
+      </c>
       <c r="D391" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ ARENAL (260.003.531)</t>
@@ -19043,7 +20583,11 @@
           <t>GLV-26-27</t>
         </is>
       </c>
-      <c r="C392" s="8" t="inlineStr"/>
+      <c r="C392" s="8" t="inlineStr">
+        <is>
+          <t>GALUNA LITHIUM (34-GL0401)</t>
+        </is>
+      </c>
       <c r="D392" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ ARENAL (260.003.530)</t>
@@ -19091,7 +20635,11 @@
           <t>GLV-26-27</t>
         </is>
       </c>
-      <c r="C393" s="8" t="inlineStr"/>
+      <c r="C393" s="8" t="inlineStr">
+        <is>
+          <t>GALUNA LITHIUM (34-GL0401)</t>
+        </is>
+      </c>
       <c r="D393" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.092)</t>
@@ -19139,7 +20687,11 @@
           <t>GLV-26-27</t>
         </is>
       </c>
-      <c r="C394" s="8" t="inlineStr"/>
+      <c r="C394" s="8" t="inlineStr">
+        <is>
+          <t>GALUNA LITHIUM (34-GL0401)</t>
+        </is>
+      </c>
       <c r="D394" s="9" t="inlineStr">
         <is>
           <t>TIO MORENO (2.026.368.082)</t>
@@ -19187,7 +20739,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C395" s="5" t="inlineStr"/>
+      <c r="C395" s="5" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D395" s="5" t="inlineStr"/>
       <c r="E395" s="5" t="n">
         <v>9</v>
@@ -19231,7 +20787,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C396" s="8" t="inlineStr"/>
+      <c r="C396" s="8" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D396" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE CAMPO DE (260.003.315)</t>
@@ -19279,7 +20839,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C397" s="8" t="inlineStr"/>
+      <c r="C397" s="8" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D397" s="9" t="inlineStr">
         <is>
           <t>CAMPOS DE CASTILLA SL CAMPO DE (260.003.554)</t>
@@ -19327,7 +20891,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C398" s="8" t="inlineStr"/>
+      <c r="C398" s="8" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D398" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.002.991)</t>
@@ -19375,7 +20943,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C399" s="8" t="inlineStr"/>
+      <c r="C399" s="8" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D399" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA LOS (260.003.242)</t>
@@ -19423,7 +20995,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C400" s="8" t="inlineStr"/>
+      <c r="C400" s="8" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D400" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA RIN (260.003.482)</t>
@@ -19471,7 +21047,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C401" s="8" t="inlineStr"/>
+      <c r="C401" s="8" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D401" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA RIN (260.003.590)</t>
@@ -19519,7 +21099,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C402" s="8" t="inlineStr"/>
+      <c r="C402" s="8" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D402" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA RIN (260.003.481)</t>
@@ -19567,7 +21151,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C403" s="8" t="inlineStr"/>
+      <c r="C403" s="8" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D403" s="9" t="inlineStr">
         <is>
           <t>LOPEZ ESCRIBANO MIGUEL ANGEL A (260.003.552)</t>
@@ -19615,7 +21203,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C404" s="8" t="inlineStr"/>
+      <c r="C404" s="8" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D404" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ CAMPO (260.003.318)</t>
@@ -19663,7 +21255,11 @@
           <t>GLV-26-30</t>
         </is>
       </c>
-      <c r="C405" s="5" t="inlineStr"/>
+      <c r="C405" s="5" t="inlineStr">
+        <is>
+          <t>DURERO</t>
+        </is>
+      </c>
       <c r="D405" s="5" t="inlineStr"/>
       <c r="E405" s="5" t="n">
         <v>7</v>
@@ -19707,7 +21303,11 @@
           <t>GLV-26-30</t>
         </is>
       </c>
-      <c r="C406" s="8" t="inlineStr"/>
+      <c r="C406" s="8" t="inlineStr">
+        <is>
+          <t>DURERO</t>
+        </is>
+      </c>
       <c r="D406" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE ARENALES (260.003.525)</t>
@@ -19755,7 +21355,11 @@
           <t>GLV-26-30</t>
         </is>
       </c>
-      <c r="C407" s="8" t="inlineStr"/>
+      <c r="C407" s="8" t="inlineStr">
+        <is>
+          <t>DURERO</t>
+        </is>
+      </c>
       <c r="D407" s="9" t="inlineStr">
         <is>
           <t>FERNANDEZ RUIZ JAIME ARENALES (260.003.563)</t>
@@ -19803,7 +21407,11 @@
           <t>GLV-26-30</t>
         </is>
       </c>
-      <c r="C408" s="8" t="inlineStr"/>
+      <c r="C408" s="8" t="inlineStr">
+        <is>
+          <t>DURERO</t>
+        </is>
+      </c>
       <c r="D408" s="9" t="inlineStr">
         <is>
           <t>LARA JIMENEZ MARTA ARENALES DE (260.003.500)</t>
@@ -19851,7 +21459,11 @@
           <t>GLV-26-30</t>
         </is>
       </c>
-      <c r="C409" s="8" t="inlineStr"/>
+      <c r="C409" s="8" t="inlineStr">
+        <is>
+          <t>DURERO</t>
+        </is>
+      </c>
       <c r="D409" s="9" t="inlineStr">
         <is>
           <t>LOPEZ DE LA RICA VELA MARIO AL (260.003.544)</t>
@@ -19899,7 +21511,11 @@
           <t>GLV-26-30</t>
         </is>
       </c>
-      <c r="C410" s="8" t="inlineStr"/>
+      <c r="C410" s="8" t="inlineStr">
+        <is>
+          <t>DURERO</t>
+        </is>
+      </c>
       <c r="D410" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ ARENAL (260.003.531)</t>
@@ -19947,7 +21563,11 @@
           <t>GLV-26-30</t>
         </is>
       </c>
-      <c r="C411" s="8" t="inlineStr"/>
+      <c r="C411" s="8" t="inlineStr">
+        <is>
+          <t>DURERO</t>
+        </is>
+      </c>
       <c r="D411" s="9" t="inlineStr">
         <is>
           <t>MERINO MUÑOZ FLORENCIO ARENALE (260.003.501)</t>
@@ -19995,7 +21615,11 @@
           <t>GLV-26-30</t>
         </is>
       </c>
-      <c r="C412" s="8" t="inlineStr"/>
+      <c r="C412" s="8" t="inlineStr">
+        <is>
+          <t>DURERO</t>
+        </is>
+      </c>
       <c r="D412" s="9" t="inlineStr">
         <is>
           <t>VELA LOPEZ DE LA RICA Mª PAZ A (260.003.542)</t>
@@ -20043,7 +21667,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C413" s="5" t="inlineStr"/>
+      <c r="C413" s="5" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D413" s="5" t="inlineStr"/>
       <c r="E413" s="5" t="n">
         <v>16</v>
@@ -20087,7 +21715,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C414" s="8" t="inlineStr"/>
+      <c r="C414" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D414" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE CAMPO DE (260.003.314)</t>
@@ -20135,7 +21767,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C415" s="8" t="inlineStr"/>
+      <c r="C415" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D415" s="9" t="inlineStr">
         <is>
           <t>CAÑAS ESCRIBANO DANIEL CAMPO D (260.003.549)</t>
@@ -20183,7 +21819,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C416" s="8" t="inlineStr"/>
+      <c r="C416" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D416" s="9" t="inlineStr">
         <is>
           <t>CAÑAS ESCRIBANO DANIEL CAMPO D (260.003.548)</t>
@@ -20231,7 +21871,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C417" s="8" t="inlineStr"/>
+      <c r="C417" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D417" s="9" t="inlineStr">
         <is>
           <t>ESCRIBANO MINGUEZ EUGENIO AREN (260.003.522)</t>
@@ -20279,7 +21923,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C418" s="8" t="inlineStr"/>
+      <c r="C418" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D418" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.003.049)</t>
@@ -20327,7 +21975,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C419" s="8" t="inlineStr"/>
+      <c r="C419" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D419" s="9" t="inlineStr">
         <is>
           <t>GESTION HORTOFRUTIC.LEVANTE SL (260.003.132)</t>
@@ -20375,7 +22027,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C420" s="8" t="inlineStr"/>
+      <c r="C420" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D420" s="9" t="inlineStr">
         <is>
           <t>JUAN GARRE HERNANDEZ LUGAR NUE (260.003.135)</t>
@@ -20423,7 +22079,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C421" s="8" t="inlineStr"/>
+      <c r="C421" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D421" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA PIL (260.003.438)</t>
@@ -20471,7 +22131,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C422" s="8" t="inlineStr"/>
+      <c r="C422" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D422" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA RIN (260.003.482)</t>
@@ -20519,7 +22183,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C423" s="8" t="inlineStr"/>
+      <c r="C423" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D423" s="9" t="inlineStr">
         <is>
           <t>LARA ANGULO JUSTO ARENALES DE (260.003.421)</t>
@@ -20567,7 +22235,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C424" s="8" t="inlineStr"/>
+      <c r="C424" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D424" s="9" t="inlineStr">
         <is>
           <t>LOPEZ DE LA RICA VELA MARIO AL (260.003.505)</t>
@@ -20615,7 +22287,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C425" s="8" t="inlineStr"/>
+      <c r="C425" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D425" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ CAMPO (260.003.317)</t>
@@ -20663,7 +22339,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C426" s="8" t="inlineStr"/>
+      <c r="C426" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D426" s="9" t="inlineStr">
         <is>
           <t>LUCAS TORRES INIESTA J ANTONIO (260.003.426)</t>
@@ -20711,7 +22391,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C427" s="8" t="inlineStr"/>
+      <c r="C427" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D427" s="9" t="inlineStr">
         <is>
           <t>MURPLACA SL EL PERETON 18/202 (260.003.137)</t>
@@ -20759,7 +22443,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C428" s="8" t="inlineStr"/>
+      <c r="C428" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D428" s="9" t="inlineStr">
         <is>
           <t>PRADILLO MANZANERO PATRICIO CA (260.003.547)</t>
@@ -20807,7 +22495,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C429" s="8" t="inlineStr"/>
+      <c r="C429" s="8" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D429" s="9" t="inlineStr">
         <is>
           <t>RAMOS CRUZ ANGEL ALCAZAR DE SA (260.003.516)</t>
@@ -20855,7 +22547,11 @@
           <t>GLV-26-35</t>
         </is>
       </c>
-      <c r="C430" s="5" t="inlineStr"/>
+      <c r="C430" s="5" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
       <c r="D430" s="5" t="inlineStr"/>
       <c r="E430" s="5" t="n">
         <v>3</v>
@@ -20899,7 +22595,11 @@
           <t>GLV-26-35</t>
         </is>
       </c>
-      <c r="C431" s="8" t="inlineStr"/>
+      <c r="C431" s="8" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
       <c r="D431" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.066)</t>
@@ -20947,7 +22647,11 @@
           <t>GLV-26-35</t>
         </is>
       </c>
-      <c r="C432" s="8" t="inlineStr"/>
+      <c r="C432" s="8" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
       <c r="D432" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.003.035)</t>
@@ -20995,7 +22699,11 @@
           <t>GLV-26-35</t>
         </is>
       </c>
-      <c r="C433" s="8" t="inlineStr"/>
+      <c r="C433" s="8" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
       <c r="D433" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA BOR (260.003.036)</t>
@@ -21043,7 +22751,11 @@
           <t>GLV-26-37</t>
         </is>
       </c>
-      <c r="C434" s="5" t="inlineStr"/>
+      <c r="C434" s="5" t="inlineStr">
+        <is>
+          <t>GOYA</t>
+        </is>
+      </c>
       <c r="D434" s="5" t="inlineStr"/>
       <c r="E434" s="5" t="n">
         <v>1</v>
@@ -21087,7 +22799,11 @@
           <t>GLV-26-37</t>
         </is>
       </c>
-      <c r="C435" s="8" t="inlineStr"/>
+      <c r="C435" s="8" t="inlineStr">
+        <is>
+          <t>GOYA</t>
+        </is>
+      </c>
       <c r="D435" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.114)</t>
@@ -21135,7 +22851,11 @@
           <t>GLV-30335</t>
         </is>
       </c>
-      <c r="C436" s="5" t="inlineStr"/>
+      <c r="C436" s="5" t="inlineStr">
+        <is>
+          <t>AR-30335</t>
+        </is>
+      </c>
       <c r="D436" s="5" t="inlineStr"/>
       <c r="E436" s="5" t="n">
         <v>2</v>
@@ -21179,7 +22899,11 @@
           <t>GLV-30335</t>
         </is>
       </c>
-      <c r="C437" s="8" t="inlineStr"/>
+      <c r="C437" s="8" t="inlineStr">
+        <is>
+          <t>AR-30335</t>
+        </is>
+      </c>
       <c r="D437" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.002.947)</t>
@@ -21227,7 +22951,11 @@
           <t>GLV-30335</t>
         </is>
       </c>
-      <c r="C438" s="8" t="inlineStr"/>
+      <c r="C438" s="8" t="inlineStr">
+        <is>
+          <t>AR-30335</t>
+        </is>
+      </c>
       <c r="D438" s="9" t="inlineStr">
         <is>
           <t>EXPLOT AGRICOLAS EL CHERIF S L (260.003.051)</t>
@@ -21275,7 +23003,11 @@
           <t>GLV-BESODO</t>
         </is>
       </c>
-      <c r="C439" s="5" t="inlineStr"/>
+      <c r="C439" s="5" t="inlineStr">
+        <is>
+          <t>BESODO</t>
+        </is>
+      </c>
       <c r="D439" s="5" t="inlineStr"/>
       <c r="E439" s="5" t="n">
         <v>4</v>
@@ -21319,7 +23051,11 @@
           <t>GLV-BESODO</t>
         </is>
       </c>
-      <c r="C440" s="8" t="inlineStr"/>
+      <c r="C440" s="8" t="inlineStr">
+        <is>
+          <t>BESODO</t>
+        </is>
+      </c>
       <c r="D440" s="9" t="inlineStr">
         <is>
           <t>JODAR SANPEDRO ANGEL EL EJIDO (260.003.246)</t>
@@ -21367,7 +23103,11 @@
           <t>GLV-BESODO</t>
         </is>
       </c>
-      <c r="C441" s="8" t="inlineStr"/>
+      <c r="C441" s="8" t="inlineStr">
+        <is>
+          <t>BESODO</t>
+        </is>
+      </c>
       <c r="D441" s="9" t="inlineStr">
         <is>
           <t>MAÑAS GONZALEZ AVELINO LA MOJO (260.003.147)</t>
@@ -21415,7 +23155,11 @@
           <t>GLV-BESODO</t>
         </is>
       </c>
-      <c r="C442" s="8" t="inlineStr"/>
+      <c r="C442" s="8" t="inlineStr">
+        <is>
+          <t>BESODO</t>
+        </is>
+      </c>
       <c r="D442" s="9" t="inlineStr">
         <is>
           <t>MAÑAS GONZALEZ AVELINO LA MOJO (260.003.147) [C2]</t>
@@ -21447,7 +23191,11 @@
           <t>GLV-BESODO</t>
         </is>
       </c>
-      <c r="C443" s="8" t="inlineStr"/>
+      <c r="C443" s="8" t="inlineStr">
+        <is>
+          <t>BESODO</t>
+        </is>
+      </c>
       <c r="D443" s="9" t="inlineStr">
         <is>
           <t>PEREZ GARRIDO JUAN VICAR 18/2 (260.003.202) [C2]</t>
@@ -21479,7 +23227,11 @@
           <t>GLV-BESODO</t>
         </is>
       </c>
-      <c r="C444" s="8" t="inlineStr"/>
+      <c r="C444" s="8" t="inlineStr">
+        <is>
+          <t>BESODO</t>
+        </is>
+      </c>
       <c r="D444" s="9" t="inlineStr">
         <is>
           <t>RUBI SAMPEDRO LUCIA EL EJIDO (260.003.218)</t>
@@ -21527,7 +23279,11 @@
           <t>GLV-CALIMA</t>
         </is>
       </c>
-      <c r="C445" s="5" t="inlineStr"/>
+      <c r="C445" s="5" t="inlineStr">
+        <is>
+          <t>CALIMA</t>
+        </is>
+      </c>
       <c r="D445" s="5" t="inlineStr"/>
       <c r="E445" s="5" t="n">
         <v>1</v>
@@ -21571,7 +23327,11 @@
           <t>GLV-CALIMA</t>
         </is>
       </c>
-      <c r="C446" s="8" t="inlineStr"/>
+      <c r="C446" s="8" t="inlineStr">
+        <is>
+          <t>CALIMA</t>
+        </is>
+      </c>
       <c r="D446" s="9" t="inlineStr">
         <is>
           <t>PARRILLA BONILLA ANTONIO JESUS (260.003.230)</t>
@@ -21619,7 +23379,11 @@
           <t>GLV-CALIMA</t>
         </is>
       </c>
-      <c r="C447" s="8" t="inlineStr"/>
+      <c r="C447" s="8" t="inlineStr">
+        <is>
+          <t>CALIMA</t>
+        </is>
+      </c>
       <c r="D447" s="9" t="inlineStr">
         <is>
           <t>PARRILLA BONILLA ANTONIO JESUS (260.003.230) [C2]</t>
@@ -21651,7 +23415,11 @@
           <t>GLV-TERRAL</t>
         </is>
       </c>
-      <c r="C448" s="5" t="inlineStr"/>
+      <c r="C448" s="5" t="inlineStr">
+        <is>
+          <t>TERRAL</t>
+        </is>
+      </c>
       <c r="D448" s="5" t="inlineStr"/>
       <c r="E448" s="5" t="n">
         <v>1</v>
@@ -21695,7 +23463,11 @@
           <t>GLV-TERRAL</t>
         </is>
       </c>
-      <c r="C449" s="8" t="inlineStr"/>
+      <c r="C449" s="8" t="inlineStr">
+        <is>
+          <t>TERRAL</t>
+        </is>
+      </c>
       <c r="D449" s="9" t="inlineStr">
         <is>
           <t>MARTOS MORENO FRANCISCO EL EJI (260.003.156)</t>
@@ -21743,7 +23515,11 @@
           <t>GLV-TERRAL</t>
         </is>
       </c>
-      <c r="C450" s="8" t="inlineStr"/>
+      <c r="C450" s="8" t="inlineStr">
+        <is>
+          <t>TERRAL</t>
+        </is>
+      </c>
       <c r="D450" s="9" t="inlineStr">
         <is>
           <t>MARTOS MORENO FRANCISCO EL EJI (260.003.156) [C2]</t>
@@ -21775,7 +23551,11 @@
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="C451" s="5" t="inlineStr"/>
+      <c r="C451" s="5" t="inlineStr">
+        <is>
+          <t>VENDAVAL</t>
+        </is>
+      </c>
       <c r="D451" s="5" t="inlineStr"/>
       <c r="E451" s="5" t="n">
         <v>1</v>
@@ -21819,7 +23599,11 @@
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="C452" s="8" t="inlineStr"/>
+      <c r="C452" s="8" t="inlineStr">
+        <is>
+          <t>VENDAVAL</t>
+        </is>
+      </c>
       <c r="D452" s="9" t="inlineStr">
         <is>
           <t>RUBI RUIZ JOSE BERNARDO EL EJI (260.003.224)</t>
@@ -21915,7 +23699,11 @@
           <t>IG-23-04</t>
         </is>
       </c>
-      <c r="C454" s="5" t="inlineStr"/>
+      <c r="C454" s="5" t="inlineStr">
+        <is>
+          <t>AST-MSB-31</t>
+        </is>
+      </c>
       <c r="D454" s="5" t="inlineStr"/>
       <c r="E454" s="5" t="n">
         <v>2</v>
@@ -21959,7 +23747,11 @@
           <t>IG-23-04</t>
         </is>
       </c>
-      <c r="C455" s="8" t="inlineStr"/>
+      <c r="C455" s="8" t="inlineStr">
+        <is>
+          <t>AST-MSB-31</t>
+        </is>
+      </c>
       <c r="D455" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.222)</t>
@@ -22007,7 +23799,11 @@
           <t>IG-23-04</t>
         </is>
       </c>
-      <c r="C456" s="8" t="inlineStr"/>
+      <c r="C456" s="8" t="inlineStr">
+        <is>
+          <t>AST-MSB-31</t>
+        </is>
+      </c>
       <c r="D456" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.141)</t>
@@ -22055,7 +23851,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C457" s="5" t="inlineStr"/>
+      <c r="C457" s="5" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D457" s="5" t="inlineStr"/>
       <c r="E457" s="5" t="n">
         <v>10</v>
@@ -22099,7 +23899,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C458" s="8" t="inlineStr"/>
+      <c r="C458" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D458" s="9" t="inlineStr">
         <is>
           <t>ABAD LOPEZ MARIA CAMPO DE CRIP (260.003.311)</t>
@@ -22147,7 +23951,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C459" s="8" t="inlineStr"/>
+      <c r="C459" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D459" s="9" t="inlineStr">
         <is>
           <t>ABAD LOPEZ MARIA CAMPO DE CRIP (260.003.310)</t>
@@ -22195,7 +24003,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C460" s="8" t="inlineStr"/>
+      <c r="C460" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D460" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE ARENALES (260.003.528)</t>
@@ -22243,7 +24055,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C461" s="8" t="inlineStr"/>
+      <c r="C461" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D461" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE CAMPO DE (260.003.628)</t>
@@ -22291,7 +24107,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C462" s="8" t="inlineStr"/>
+      <c r="C462" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D462" s="9" t="inlineStr">
         <is>
           <t>CAÑAS ESCRIBANO DANIEL CAMPO D (260.003.493)</t>
@@ -22339,7 +24159,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C463" s="8" t="inlineStr"/>
+      <c r="C463" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D463" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.261)</t>
@@ -22387,7 +24211,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C464" s="8" t="inlineStr"/>
+      <c r="C464" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D464" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.021)</t>
@@ -22435,7 +24263,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C465" s="8" t="inlineStr"/>
+      <c r="C465" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D465" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.931)</t>
@@ -22483,7 +24315,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C466" s="8" t="inlineStr"/>
+      <c r="C466" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D466" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ ARENAL (260.003.533)</t>
@@ -22531,7 +24367,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C467" s="8" t="inlineStr"/>
+      <c r="C467" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D467" s="9" t="inlineStr">
         <is>
           <t>PRADILLO MANZANERO PATRICIO CA (260.003.485)</t>
@@ -22579,7 +24419,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C468" s="5" t="inlineStr"/>
+      <c r="C468" s="5" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D468" s="5" t="inlineStr"/>
       <c r="E468" s="5" t="n">
         <v>12</v>
@@ -22623,7 +24467,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C469" s="8" t="inlineStr"/>
+      <c r="C469" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D469" s="9" t="inlineStr">
         <is>
           <t>ABAD LOPEZ MARIA CAMPO DE CRIP (260.003.310)</t>
@@ -22671,7 +24519,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C470" s="8" t="inlineStr"/>
+      <c r="C470" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D470" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE ARENALES (260.003.527)</t>
@@ -22719,7 +24571,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C471" s="8" t="inlineStr"/>
+      <c r="C471" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D471" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE CAMPO DE (260.003.312)</t>
@@ -22767,7 +24623,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C472" s="8" t="inlineStr"/>
+      <c r="C472" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D472" s="9" t="inlineStr">
         <is>
           <t>CAÑAS ESCRIBANO DANIEL CAMPO D (260.003.492)</t>
@@ -22815,7 +24675,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C473" s="8" t="inlineStr"/>
+      <c r="C473" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D473" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.241)</t>
@@ -22863,7 +24727,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C474" s="8" t="inlineStr"/>
+      <c r="C474" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D474" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.072)</t>
@@ -22911,7 +24779,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C475" s="8" t="inlineStr"/>
+      <c r="C475" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D475" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.231)</t>
@@ -22959,7 +24831,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C476" s="8" t="inlineStr"/>
+      <c r="C476" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D476" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.011)</t>
@@ -23007,7 +24883,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C477" s="8" t="inlineStr"/>
+      <c r="C477" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D477" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.041)</t>
@@ -23055,7 +24935,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C478" s="8" t="inlineStr"/>
+      <c r="C478" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D478" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ ARENAL (260.003.532)</t>
@@ -23103,7 +24987,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C479" s="8" t="inlineStr"/>
+      <c r="C479" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D479" s="9" t="inlineStr">
         <is>
           <t>PRADILLO MANZANERO PATRICIO CA (260.003.486)</t>
@@ -23151,7 +25039,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C480" s="8" t="inlineStr"/>
+      <c r="C480" s="8" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D480" s="9" t="inlineStr">
         <is>
           <t>SAT 9861 AGROPEC EL ROSARIO AL (260.003.515)</t>
@@ -23199,7 +25091,11 @@
           <t>IG-26-06</t>
         </is>
       </c>
-      <c r="C481" s="5" t="inlineStr"/>
+      <c r="C481" s="5" t="inlineStr">
+        <is>
+          <t>MAYAN 443</t>
+        </is>
+      </c>
       <c r="D481" s="5" t="inlineStr"/>
       <c r="E481" s="5" t="n">
         <v>2</v>
@@ -23243,7 +25139,11 @@
           <t>IG-26-06</t>
         </is>
       </c>
-      <c r="C482" s="8" t="inlineStr"/>
+      <c r="C482" s="8" t="inlineStr">
+        <is>
+          <t>MAYAN 443</t>
+        </is>
+      </c>
       <c r="D482" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.032)</t>
@@ -23291,7 +25191,11 @@
           <t>IG-26-06</t>
         </is>
       </c>
-      <c r="C483" s="8" t="inlineStr"/>
+      <c r="C483" s="8" t="inlineStr">
+        <is>
+          <t>MAYAN 443</t>
+        </is>
+      </c>
       <c r="D483" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.141)</t>
@@ -23339,7 +25243,11 @@
           <t>IG-30340</t>
         </is>
       </c>
-      <c r="C484" s="5" t="inlineStr"/>
+      <c r="C484" s="5" t="inlineStr">
+        <is>
+          <t>AR-30340</t>
+        </is>
+      </c>
       <c r="D484" s="5" t="inlineStr"/>
       <c r="E484" s="5" t="n">
         <v>1</v>
@@ -23383,7 +25291,11 @@
           <t>IG-30340</t>
         </is>
       </c>
-      <c r="C485" s="8" t="inlineStr"/>
+      <c r="C485" s="8" t="inlineStr">
+        <is>
+          <t>AR-30340</t>
+        </is>
+      </c>
       <c r="D485" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.072)</t>
@@ -23431,7 +25343,11 @@
           <t>IG-30358</t>
         </is>
       </c>
-      <c r="C486" s="5" t="inlineStr"/>
+      <c r="C486" s="5" t="inlineStr">
+        <is>
+          <t>AR-30358</t>
+        </is>
+      </c>
       <c r="D486" s="5" t="inlineStr"/>
       <c r="E486" s="5" t="n">
         <v>1</v>
@@ -23475,7 +25391,11 @@
           <t>IG-30358</t>
         </is>
       </c>
-      <c r="C487" s="8" t="inlineStr"/>
+      <c r="C487" s="8" t="inlineStr">
+        <is>
+          <t>AR-30358</t>
+        </is>
+      </c>
       <c r="D487" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.911)</t>
@@ -23523,7 +25443,11 @@
           <t>IG-795</t>
         </is>
       </c>
-      <c r="C488" s="5" t="inlineStr"/>
+      <c r="C488" s="5" t="inlineStr">
+        <is>
+          <t>EWS-MLN-795</t>
+        </is>
+      </c>
       <c r="D488" s="5" t="inlineStr"/>
       <c r="E488" s="5" t="n">
         <v>1</v>
@@ -23567,7 +25491,11 @@
           <t>IG-795</t>
         </is>
       </c>
-      <c r="C489" s="8" t="inlineStr"/>
+      <c r="C489" s="8" t="inlineStr">
+        <is>
+          <t>EWS-MLN-795</t>
+        </is>
+      </c>
       <c r="D489" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.222)</t>
@@ -23663,7 +25591,11 @@
           <t>OR-22-01</t>
         </is>
       </c>
-      <c r="C491" s="5" t="inlineStr"/>
+      <c r="C491" s="5" t="inlineStr">
+        <is>
+          <t>SV7464MA</t>
+        </is>
+      </c>
       <c r="D491" s="5" t="inlineStr"/>
       <c r="E491" s="5" t="n">
         <v>1</v>
@@ -23707,7 +25639,11 @@
           <t>OR-22-01</t>
         </is>
       </c>
-      <c r="C492" s="8" t="inlineStr"/>
+      <c r="C492" s="8" t="inlineStr">
+        <is>
+          <t>SV7464MA</t>
+        </is>
+      </c>
       <c r="D492" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.393)</t>
@@ -23755,7 +25691,11 @@
           <t>OR-23-04</t>
         </is>
       </c>
-      <c r="C493" s="5" t="inlineStr"/>
+      <c r="C493" s="5" t="inlineStr">
+        <is>
+          <t>ESM2112</t>
+        </is>
+      </c>
       <c r="D493" s="5" t="inlineStr"/>
       <c r="E493" s="5" t="n">
         <v>1</v>
@@ -23799,7 +25739,11 @@
           <t>OR-23-04</t>
         </is>
       </c>
-      <c r="C494" s="8" t="inlineStr"/>
+      <c r="C494" s="8" t="inlineStr">
+        <is>
+          <t>ESM2112</t>
+        </is>
+      </c>
       <c r="D494" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.241)</t>
@@ -23847,7 +25791,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C495" s="5" t="inlineStr"/>
+      <c r="C495" s="5" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D495" s="5" t="inlineStr"/>
       <c r="E495" s="5" t="n">
         <v>10</v>
@@ -23891,7 +25839,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C496" s="8" t="inlineStr"/>
+      <c r="C496" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D496" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.393)</t>
@@ -23939,7 +25891,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C497" s="8" t="inlineStr"/>
+      <c r="C497" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D497" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.371)</t>
@@ -23987,7 +25943,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C498" s="8" t="inlineStr"/>
+      <c r="C498" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D498" s="9" t="inlineStr">
         <is>
           <t>ALBORAJ (2.026.334.381)</t>
@@ -24035,7 +25995,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C499" s="8" t="inlineStr"/>
+      <c r="C499" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D499" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.123)</t>
@@ -24083,7 +26047,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C500" s="8" t="inlineStr"/>
+      <c r="C500" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D500" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.152)</t>
@@ -24131,7 +26099,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C501" s="8" t="inlineStr"/>
+      <c r="C501" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D501" s="9" t="inlineStr">
         <is>
           <t>MULATA (2.026.382.362)</t>
@@ -24179,7 +26151,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C502" s="8" t="inlineStr"/>
+      <c r="C502" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D502" s="9" t="inlineStr">
         <is>
           <t>MULATA (2.026.382.352)</t>
@@ -24227,7 +26203,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C503" s="8" t="inlineStr"/>
+      <c r="C503" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D503" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.271)</t>
@@ -24275,7 +26255,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C504" s="8" t="inlineStr"/>
+      <c r="C504" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D504" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.210)</t>
@@ -24323,7 +26307,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C505" s="8" t="inlineStr"/>
+      <c r="C505" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D505" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.241)</t>
@@ -24419,7 +26407,11 @@
           <t>Z-25-21</t>
         </is>
       </c>
-      <c r="C507" s="5" t="inlineStr"/>
+      <c r="C507" s="5" t="inlineStr">
+        <is>
+          <t>HMC464074</t>
+        </is>
+      </c>
       <c r="D507" s="5" t="inlineStr"/>
       <c r="E507" s="5" t="n">
         <v>2</v>
@@ -24463,7 +26455,11 @@
           <t>Z-25-21</t>
         </is>
       </c>
-      <c r="C508" s="8" t="inlineStr"/>
+      <c r="C508" s="8" t="inlineStr">
+        <is>
+          <t>HMC464074</t>
+        </is>
+      </c>
       <c r="D508" s="9" t="inlineStr">
         <is>
           <t>AGRICOLA ARROYO Y MARIN SL FUE (260.003.445)</t>
@@ -24511,7 +26507,11 @@
           <t>Z-25-21</t>
         </is>
       </c>
-      <c r="C509" s="8" t="inlineStr"/>
+      <c r="C509" s="8" t="inlineStr">
+        <is>
+          <t>HMC464074</t>
+        </is>
+      </c>
       <c r="D509" s="9" t="inlineStr">
         <is>
           <t>AGRICOLA ARROYO Y MARIN SL FUE (260.003.457)</t>
@@ -24559,7 +26559,11 @@
           <t>Z-25-21</t>
         </is>
       </c>
-      <c r="C510" s="8" t="inlineStr"/>
+      <c r="C510" s="8" t="inlineStr">
+        <is>
+          <t>HMC464074</t>
+        </is>
+      </c>
       <c r="D510" s="9" t="inlineStr">
         <is>
           <t>AGRICOLA ARROYO Y MARIN SL FUE (260.003.445) [G]</t>
@@ -24607,7 +26611,11 @@
           <t>Z-25-21</t>
         </is>
       </c>
-      <c r="C511" s="8" t="inlineStr"/>
+      <c r="C511" s="8" t="inlineStr">
+        <is>
+          <t>HMC464074</t>
+        </is>
+      </c>
       <c r="D511" s="9" t="inlineStr">
         <is>
           <t>AGRICOLA ARROYO Y MARIN SL FUE (260.003.457) [G]</t>
@@ -24655,7 +26663,11 @@
           <t>Z-26-02</t>
         </is>
       </c>
-      <c r="C512" s="5" t="inlineStr"/>
+      <c r="C512" s="5" t="inlineStr">
+        <is>
+          <t>DOLSURA (34-138)</t>
+        </is>
+      </c>
       <c r="D512" s="5" t="inlineStr"/>
       <c r="E512" s="5" t="n">
         <v>1</v>
@@ -24699,7 +26711,11 @@
           <t>Z-26-02</t>
         </is>
       </c>
-      <c r="C513" s="8" t="inlineStr"/>
+      <c r="C513" s="8" t="inlineStr">
+        <is>
+          <t>DOLSURA (34-138)</t>
+        </is>
+      </c>
       <c r="D513" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.244)</t>
@@ -24747,7 +26763,11 @@
           <t>Z-26-03</t>
         </is>
       </c>
-      <c r="C514" s="5" t="inlineStr"/>
+      <c r="C514" s="5" t="inlineStr">
+        <is>
+          <t>BRAVURA (34-133)</t>
+        </is>
+      </c>
       <c r="D514" s="5" t="inlineStr"/>
       <c r="E514" s="5" t="n">
         <v>5</v>
@@ -24791,7 +26811,11 @@
           <t>Z-26-03</t>
         </is>
       </c>
-      <c r="C515" s="8" t="inlineStr"/>
+      <c r="C515" s="8" t="inlineStr">
+        <is>
+          <t>BRAVURA (34-133)</t>
+        </is>
+      </c>
       <c r="D515" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.080)</t>
@@ -24839,7 +26863,11 @@
           <t>Z-26-03</t>
         </is>
       </c>
-      <c r="C516" s="8" t="inlineStr"/>
+      <c r="C516" s="8" t="inlineStr">
+        <is>
+          <t>BRAVURA (34-133)</t>
+        </is>
+      </c>
       <c r="D516" s="9" t="inlineStr">
         <is>
           <t>FRUTAS Y VERD. DE LOBOSILLO SA (260.003.627)</t>
@@ -24887,7 +26915,11 @@
           <t>Z-26-03</t>
         </is>
       </c>
-      <c r="C517" s="8" t="inlineStr"/>
+      <c r="C517" s="8" t="inlineStr">
+        <is>
+          <t>BRAVURA (34-133)</t>
+        </is>
+      </c>
       <c r="D517" s="9" t="inlineStr">
         <is>
           <t>FRUTAS Y VERD. DE LOBOSILLO SA (260.003.441)</t>
@@ -24935,7 +26967,11 @@
           <t>Z-26-03</t>
         </is>
       </c>
-      <c r="C518" s="8" t="inlineStr"/>
+      <c r="C518" s="8" t="inlineStr">
+        <is>
+          <t>BRAVURA (34-133)</t>
+        </is>
+      </c>
       <c r="D518" s="9" t="inlineStr">
         <is>
           <t>FRUTAS Y VERD. DE LOBOSILLO SA (260.003.198)</t>
@@ -24983,7 +27019,11 @@
           <t>Z-26-03</t>
         </is>
       </c>
-      <c r="C519" s="8" t="inlineStr"/>
+      <c r="C519" s="8" t="inlineStr">
+        <is>
+          <t>BRAVURA (34-133)</t>
+        </is>
+      </c>
       <c r="D519" s="9" t="inlineStr">
         <is>
           <t>FRUTAS Y VERD. DE LOBOSILLO SA (260.003.323)</t>
@@ -25031,7 +27071,11 @@
           <t>Z-26-03</t>
         </is>
       </c>
-      <c r="C520" s="8" t="inlineStr"/>
+      <c r="C520" s="8" t="inlineStr">
+        <is>
+          <t>BRAVURA (34-133)</t>
+        </is>
+      </c>
       <c r="D520" s="9" t="inlineStr">
         <is>
           <t>FRUTAS Y VERD. DE LOBOSILLO SA (260.003.198) [G]</t>
@@ -25063,7 +27107,11 @@
           <t>Z-26-06</t>
         </is>
       </c>
-      <c r="C521" s="5" t="inlineStr"/>
+      <c r="C521" s="5" t="inlineStr">
+        <is>
+          <t>MINITHOR (34-148)</t>
+        </is>
+      </c>
       <c r="D521" s="5" t="inlineStr"/>
       <c r="E521" s="5" t="n">
         <v>4</v>
@@ -25107,7 +27155,11 @@
           <t>Z-26-06</t>
         </is>
       </c>
-      <c r="C522" s="8" t="inlineStr"/>
+      <c r="C522" s="8" t="inlineStr">
+        <is>
+          <t>MINITHOR (34-148)</t>
+        </is>
+      </c>
       <c r="D522" s="9" t="inlineStr">
         <is>
           <t>EXPLOTACIONES CHINCHILLA SL BA (260.003.430)</t>
@@ -25155,7 +27207,11 @@
           <t>Z-26-06</t>
         </is>
       </c>
-      <c r="C523" s="8" t="inlineStr"/>
+      <c r="C523" s="8" t="inlineStr">
+        <is>
+          <t>MINITHOR (34-148)</t>
+        </is>
+      </c>
       <c r="D523" s="9" t="inlineStr">
         <is>
           <t>EXPLOTACIONES CHINCHILLA SL BA (260.003.429)</t>
@@ -25203,7 +27259,11 @@
           <t>Z-26-06</t>
         </is>
       </c>
-      <c r="C524" s="8" t="inlineStr"/>
+      <c r="C524" s="8" t="inlineStr">
+        <is>
+          <t>MINITHOR (34-148)</t>
+        </is>
+      </c>
       <c r="D524" s="9" t="inlineStr">
         <is>
           <t>MERCO MANCHA SA CINCO CASAS 3 (260.003.645)</t>
@@ -25251,7 +27311,11 @@
           <t>Z-26-06</t>
         </is>
       </c>
-      <c r="C525" s="8" t="inlineStr"/>
+      <c r="C525" s="8" t="inlineStr">
+        <is>
+          <t>MINITHOR (34-148)</t>
+        </is>
+      </c>
       <c r="D525" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.041)</t>
@@ -25299,7 +27363,11 @@
           <t>Z-26-06</t>
         </is>
       </c>
-      <c r="C526" s="8" t="inlineStr"/>
+      <c r="C526" s="8" t="inlineStr">
+        <is>
+          <t>MINITHOR (34-148)</t>
+        </is>
+      </c>
       <c r="D526" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.041) [G]</t>
@@ -25347,7 +27415,11 @@
           <t>Z-26-15</t>
         </is>
       </c>
-      <c r="C527" s="5" t="inlineStr"/>
+      <c r="C527" s="5" t="inlineStr">
+        <is>
+          <t>GRACIANO</t>
+        </is>
+      </c>
       <c r="D527" s="5" t="inlineStr"/>
       <c r="E527" s="5" t="n">
         <v>1</v>
@@ -25391,7 +27463,11 @@
           <t>Z-26-15</t>
         </is>
       </c>
-      <c r="C528" s="8" t="inlineStr"/>
+      <c r="C528" s="8" t="inlineStr">
+        <is>
+          <t>GRACIANO</t>
+        </is>
+      </c>
       <c r="D528" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.731)</t>
@@ -25439,7 +27515,11 @@
           <t>Z-26-15</t>
         </is>
       </c>
-      <c r="C529" s="8" t="inlineStr"/>
+      <c r="C529" s="8" t="inlineStr">
+        <is>
+          <t>GRACIANO</t>
+        </is>
+      </c>
       <c r="D529" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.731) [G]</t>
@@ -25487,7 +27567,11 @@
           <t>Z-26-18</t>
         </is>
       </c>
-      <c r="C530" s="5" t="inlineStr"/>
+      <c r="C530" s="5" t="inlineStr">
+        <is>
+          <t>CORRALES</t>
+        </is>
+      </c>
       <c r="D530" s="5" t="inlineStr"/>
       <c r="E530" s="5" t="n">
         <v>1</v>
@@ -25531,7 +27615,11 @@
           <t>Z-26-18</t>
         </is>
       </c>
-      <c r="C531" s="8" t="inlineStr"/>
+      <c r="C531" s="8" t="inlineStr">
+        <is>
+          <t>CORRALES</t>
+        </is>
+      </c>
       <c r="D531" s="9" t="inlineStr">
         <is>
           <t>EXPLOTACIONES CHINCHILLA SL BA (260.003.431) [G]</t>
@@ -25579,7 +27667,11 @@
           <t>Z-26-27</t>
         </is>
       </c>
-      <c r="C532" s="5" t="inlineStr"/>
+      <c r="C532" s="5" t="inlineStr">
+        <is>
+          <t>CAMACHO</t>
+        </is>
+      </c>
       <c r="D532" s="5" t="inlineStr"/>
       <c r="E532" s="5" t="n">
         <v>1</v>
@@ -25617,7 +27709,11 @@
           <t>Z-26-27</t>
         </is>
       </c>
-      <c r="C533" s="8" t="inlineStr"/>
+      <c r="C533" s="8" t="inlineStr">
+        <is>
+          <t>CAMACHO</t>
+        </is>
+      </c>
       <c r="D533" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.731) [G]</t>
@@ -25659,7 +27755,11 @@
           <t>Z-26-31</t>
         </is>
       </c>
-      <c r="C534" s="5" t="inlineStr"/>
+      <c r="C534" s="5" t="inlineStr">
+        <is>
+          <t>CAMPUZANO</t>
+        </is>
+      </c>
       <c r="D534" s="5" t="inlineStr"/>
       <c r="E534" s="5" t="n">
         <v>1</v>
@@ -25703,7 +27803,11 @@
           <t>Z-26-31</t>
         </is>
       </c>
-      <c r="C535" s="8" t="inlineStr"/>
+      <c r="C535" s="8" t="inlineStr">
+        <is>
+          <t>CAMPUZANO</t>
+        </is>
+      </c>
       <c r="D535" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.262)</t>
@@ -25751,7 +27855,11 @@
           <t>Z-26-31</t>
         </is>
       </c>
-      <c r="C536" s="8" t="inlineStr"/>
+      <c r="C536" s="8" t="inlineStr">
+        <is>
+          <t>CAMPUZANO</t>
+        </is>
+      </c>
       <c r="D536" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.262) [G]</t>
@@ -25799,7 +27907,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C537" s="5" t="inlineStr"/>
+      <c r="C537" s="5" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D537" s="5" t="inlineStr"/>
       <c r="E537" s="5" t="n">
         <v>6</v>
@@ -25843,7 +27955,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C538" s="8" t="inlineStr"/>
+      <c r="C538" s="8" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D538" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.252)</t>
@@ -25891,7 +28007,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C539" s="8" t="inlineStr"/>
+      <c r="C539" s="8" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D539" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.281)</t>
@@ -25939,7 +28059,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C540" s="8" t="inlineStr"/>
+      <c r="C540" s="8" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D540" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.271)</t>
@@ -25987,7 +28111,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C541" s="8" t="inlineStr"/>
+      <c r="C541" s="8" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D541" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.281) [G]</t>
@@ -26035,7 +28163,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C542" s="8" t="inlineStr"/>
+      <c r="C542" s="8" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D542" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.271) [G]</t>
@@ -26083,7 +28215,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C543" s="8" t="inlineStr"/>
+      <c r="C543" s="8" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D543" s="9" t="inlineStr">
         <is>
           <t>EXPLOTACIONES CHINCHILLA SL BA (260.003.429)</t>
@@ -26131,7 +28267,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C544" s="8" t="inlineStr"/>
+      <c r="C544" s="8" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D544" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.710)</t>
@@ -26179,7 +28319,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C545" s="8" t="inlineStr"/>
+      <c r="C545" s="8" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D545" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.740)</t>
@@ -26227,7 +28371,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C546" s="8" t="inlineStr"/>
+      <c r="C546" s="8" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D546" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.710) [G]</t>
@@ -26275,7 +28423,11 @@
           <t>Z-4481</t>
         </is>
       </c>
-      <c r="C547" s="5" t="inlineStr"/>
+      <c r="C547" s="5" t="inlineStr">
+        <is>
+          <t>HMC 4481</t>
+        </is>
+      </c>
       <c r="D547" s="5" t="inlineStr"/>
       <c r="E547" s="5" t="n">
         <v>2</v>
@@ -26319,7 +28471,11 @@
           <t>Z-4481</t>
         </is>
       </c>
-      <c r="C548" s="8" t="inlineStr"/>
+      <c r="C548" s="8" t="inlineStr">
+        <is>
+          <t>HMC 4481</t>
+        </is>
+      </c>
       <c r="D548" s="9" t="inlineStr">
         <is>
           <t>AGROVITORIAS S L LOS GABRIELE (260.003.142)</t>
@@ -26367,7 +28523,11 @@
           <t>Z-4481</t>
         </is>
       </c>
-      <c r="C549" s="8" t="inlineStr"/>
+      <c r="C549" s="8" t="inlineStr">
+        <is>
+          <t>HMC 4481</t>
+        </is>
+      </c>
       <c r="D549" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.021)</t>
@@ -26415,7 +28575,11 @@
           <t>Z-4481</t>
         </is>
       </c>
-      <c r="C550" s="8" t="inlineStr"/>
+      <c r="C550" s="8" t="inlineStr">
+        <is>
+          <t>HMC 4481</t>
+        </is>
+      </c>
       <c r="D550" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.021) [G]</t>
@@ -26511,7 +28675,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C552" s="5" t="inlineStr"/>
+      <c r="C552" s="5" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D552" s="5" t="inlineStr"/>
       <c r="E552" s="5" t="n">
         <v>10</v>
@@ -26555,7 +28723,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C553" s="8" t="inlineStr"/>
+      <c r="C553" s="8" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D553" s="9" t="inlineStr">
         <is>
           <t>CAÑAS ESCRIBANO DANIEL CAMPO D (260.003.491)</t>
@@ -26603,7 +28775,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C554" s="8" t="inlineStr"/>
+      <c r="C554" s="8" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D554" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.072)</t>
@@ -26651,7 +28827,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C555" s="8" t="inlineStr"/>
+      <c r="C555" s="8" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D555" s="9" t="inlineStr">
         <is>
           <t>MARTOS MORENO FRANCISCO EL EJI (260.003.215)</t>
@@ -26699,7 +28879,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C556" s="8" t="inlineStr"/>
+      <c r="C556" s="8" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D556" s="9" t="inlineStr">
         <is>
           <t>PARRILLA BONILLA MANUEL MIGUEL (260.003.272)</t>
@@ -26747,7 +28931,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C557" s="8" t="inlineStr"/>
+      <c r="C557" s="8" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D557" s="9" t="inlineStr">
         <is>
           <t>PRADILLO MANZANERO PATRICIO CA (260.003.487)</t>
@@ -26795,7 +28983,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C558" s="8" t="inlineStr"/>
+      <c r="C558" s="8" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D558" s="9" t="inlineStr">
         <is>
           <t>SAT 9861 AGROPEC EL ROSARIO AL (260.003.514)</t>
@@ -26843,7 +29035,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C559" s="8" t="inlineStr"/>
+      <c r="C559" s="8" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D559" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.073)</t>
@@ -26891,7 +29087,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C560" s="8" t="inlineStr"/>
+      <c r="C560" s="8" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D560" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.142)</t>
@@ -26933,7 +29133,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C561" s="8" t="inlineStr"/>
+      <c r="C561" s="8" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D561" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.102)</t>
@@ -26981,7 +29185,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C562" s="8" t="inlineStr"/>
+      <c r="C562" s="8" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D562" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.051)</t>
@@ -27029,7 +29237,11 @@
           <t>GC-26-03</t>
         </is>
       </c>
-      <c r="C563" s="5" t="inlineStr"/>
+      <c r="C563" s="5" t="inlineStr">
+        <is>
+          <t>SUNBALL</t>
+        </is>
+      </c>
       <c r="D563" s="5" t="inlineStr"/>
       <c r="E563" s="5" t="n">
         <v>1</v>
@@ -27073,7 +29285,11 @@
           <t>GC-26-03</t>
         </is>
       </c>
-      <c r="C564" s="8" t="inlineStr"/>
+      <c r="C564" s="8" t="inlineStr">
+        <is>
+          <t>SUNBALL</t>
+        </is>
+      </c>
       <c r="D564" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.102)</t>
@@ -27121,7 +29337,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C565" s="5" t="inlineStr"/>
+      <c r="C565" s="5" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D565" s="5" t="inlineStr"/>
       <c r="E565" s="5" t="n">
         <v>19</v>
@@ -27165,7 +29385,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C566" s="8" t="inlineStr"/>
+      <c r="C566" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D566" s="9" t="inlineStr">
         <is>
           <t>ALBERCA ORTIZ VICENTE ARENALES (260.003.539)</t>
@@ -27213,7 +29437,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C567" s="8" t="inlineStr"/>
+      <c r="C567" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D567" s="9" t="inlineStr">
         <is>
           <t>CAMPOS DE CASTILLA SL ARENALES (260.003.537)</t>
@@ -27261,7 +29489,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C568" s="8" t="inlineStr"/>
+      <c r="C568" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D568" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.092)</t>
@@ -27309,7 +29541,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C569" s="8" t="inlineStr"/>
+      <c r="C569" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D569" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.081)</t>
@@ -27357,7 +29593,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C570" s="8" t="inlineStr"/>
+      <c r="C570" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D570" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.251)</t>
@@ -27405,7 +29645,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C571" s="8" t="inlineStr"/>
+      <c r="C571" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D571" s="9" t="inlineStr">
         <is>
           <t>EL BOQUERON (2.026.333.242)</t>
@@ -27453,7 +29697,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C572" s="8" t="inlineStr"/>
+      <c r="C572" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D572" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.233)</t>
@@ -27501,7 +29749,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C573" s="8" t="inlineStr"/>
+      <c r="C573" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D573" s="9" t="inlineStr">
         <is>
           <t>LA FORJA ESPARRAGERAL (2.026.326.241)</t>
@@ -27549,7 +29801,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C574" s="8" t="inlineStr"/>
+      <c r="C574" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D574" s="9" t="inlineStr">
         <is>
           <t>LA GUIA (2.026.331.022)</t>
@@ -27587,7 +29843,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C575" s="8" t="inlineStr"/>
+      <c r="C575" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D575" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA RAN (260.003.106)</t>
@@ -27635,7 +29895,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C576" s="8" t="inlineStr"/>
+      <c r="C576" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D576" s="9" t="inlineStr">
         <is>
           <t>LA HUERTA DE SAN ISIDRO SA RIN (260.003.480)</t>
@@ -27683,7 +29947,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C577" s="8" t="inlineStr"/>
+      <c r="C577" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D577" s="9" t="inlineStr">
         <is>
           <t>LOPEZ SANCHEZ MARI CRUZ ARENAL (260.003.538)</t>
@@ -27731,7 +29999,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C578" s="8" t="inlineStr"/>
+      <c r="C578" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D578" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.172)</t>
@@ -27779,7 +30051,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C579" s="8" t="inlineStr"/>
+      <c r="C579" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D579" s="9" t="inlineStr">
         <is>
           <t>MACANEO (2.026.328.190)</t>
@@ -27827,7 +30103,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C580" s="8" t="inlineStr"/>
+      <c r="C580" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D580" s="9" t="inlineStr">
         <is>
           <t>MULATA (2.026.382.331)</t>
@@ -27875,7 +30155,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C581" s="8" t="inlineStr"/>
+      <c r="C581" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D581" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.750)</t>
@@ -27923,7 +30207,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C582" s="8" t="inlineStr"/>
+      <c r="C582" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D582" s="9" t="inlineStr">
         <is>
           <t>SAN ISIDRO (2.026.322.740)</t>
@@ -27971,7 +30259,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C583" s="8" t="inlineStr"/>
+      <c r="C583" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D583" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.102)</t>
@@ -28019,7 +30311,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C584" s="8" t="inlineStr"/>
+      <c r="C584" s="8" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D584" s="9" t="inlineStr">
         <is>
           <t>UBEDAS (2.026.316.112)</t>
@@ -28164,7 +30460,11 @@
           <t>A-25-09</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr"/>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>PEKIN</t>
+        </is>
+      </c>
       <c r="D2" s="8" t="n">
         <v>1</v>
       </c>
@@ -28207,7 +30507,11 @@
           <t>A-26-02</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr"/>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>MAILLOT</t>
+        </is>
+      </c>
       <c r="D3" s="12" t="n">
         <v>4</v>
       </c>
@@ -28250,7 +30554,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
       <c r="D4" s="8" t="n">
         <v>11</v>
       </c>
@@ -28293,7 +30601,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr"/>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n">
         <v>15</v>
       </c>
@@ -28336,7 +30648,11 @@
           <t>A-26-12</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>PIEL DE SOL</t>
+        </is>
+      </c>
       <c r="D6" s="8" t="n">
         <v>3</v>
       </c>
@@ -28379,7 +30695,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr"/>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
       <c r="D7" s="12" t="n">
         <v>9</v>
       </c>
@@ -28422,7 +30742,11 @@
           <t>A-26-14</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>NIVAL (34-379)</t>
+        </is>
+      </c>
       <c r="D8" s="8" t="n">
         <v>6</v>
       </c>
@@ -28465,7 +30789,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
       <c r="D9" s="12" t="n">
         <v>10</v>
       </c>
@@ -28508,7 +30836,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
       <c r="D10" s="8" t="n">
         <v>18</v>
       </c>
@@ -28551,7 +30883,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
       <c r="D11" s="12" t="n">
         <v>9</v>
       </c>
@@ -28594,7 +30930,11 @@
           <t>A-26-25</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>MS12MA058</t>
+        </is>
+      </c>
       <c r="D12" s="8" t="n">
         <v>3</v>
       </c>
@@ -28637,7 +30977,11 @@
           <t>A-26-26</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr"/>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>TEQUILA</t>
+        </is>
+      </c>
       <c r="D13" s="12" t="n">
         <v>4</v>
       </c>
@@ -28680,7 +31024,11 @@
           <t>A-26-27</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>HAWAI</t>
+        </is>
+      </c>
       <c r="D14" s="8" t="n">
         <v>5</v>
       </c>
@@ -28723,7 +31071,11 @@
           <t>A-ATILA</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr"/>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>ATILA</t>
+        </is>
+      </c>
       <c r="D15" s="12" t="n">
         <v>1</v>
       </c>
@@ -28766,7 +31118,11 @@
           <t>A-ROCHESTE</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr"/>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>ROCHESTE</t>
+        </is>
+      </c>
       <c r="D16" s="8" t="n">
         <v>2</v>
       </c>
@@ -28809,7 +31165,11 @@
           <t>A-SUERTE</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr"/>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>SUERTE</t>
+        </is>
+      </c>
       <c r="D17" s="12" t="n">
         <v>1</v>
       </c>
@@ -28852,7 +31212,11 @@
           <t>A-ZENITH</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr"/>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>ZENITH</t>
+        </is>
+      </c>
       <c r="D18" s="8" t="n">
         <v>1</v>
       </c>
@@ -28895,7 +31259,11 @@
           <t>INDURAIN</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr"/>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>INDURAIN</t>
+        </is>
+      </c>
       <c r="D19" s="12" t="n">
         <v>2</v>
       </c>
@@ -28938,7 +31306,11 @@
           <t>MIELON</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr"/>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>MIELON</t>
+        </is>
+      </c>
       <c r="D20" s="8" t="n">
         <v>1</v>
       </c>
@@ -28981,7 +31353,11 @@
           <t>C-19-11</t>
         </is>
       </c>
-      <c r="C21" s="12" t="inlineStr"/>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>N.12788</t>
+        </is>
+      </c>
       <c r="D21" s="12" t="n">
         <v>1</v>
       </c>
@@ -29024,7 +31400,11 @@
           <t>C-24-21</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr"/>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>MAGVERIK</t>
+        </is>
+      </c>
       <c r="D22" s="8" t="n">
         <v>5</v>
       </c>
@@ -29067,7 +31447,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr"/>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
       <c r="D23" s="12" t="n">
         <v>10</v>
       </c>
@@ -29110,7 +31494,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr"/>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
       <c r="D24" s="8" t="n">
         <v>8</v>
       </c>
@@ -29153,7 +31541,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="C25" s="12" t="inlineStr"/>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
       <c r="D25" s="12" t="n">
         <v>33</v>
       </c>
@@ -29196,7 +31588,11 @@
           <t>C-26-26</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr"/>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>URKAN</t>
+        </is>
+      </c>
       <c r="D26" s="8" t="n">
         <v>2</v>
       </c>
@@ -29239,7 +31635,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr"/>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
       <c r="D27" s="12" t="n">
         <v>11</v>
       </c>
@@ -29282,7 +31682,11 @@
           <t>C-26-31</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr"/>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>ORANGELUP</t>
+        </is>
+      </c>
       <c r="D28" s="8" t="n">
         <v>1</v>
       </c>
@@ -29325,7 +31729,11 @@
           <t>C-26-32</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr"/>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>DELPHES</t>
+        </is>
+      </c>
       <c r="D29" s="12" t="n">
         <v>4</v>
       </c>
@@ -29368,7 +31776,11 @@
           <t>SEM-14012</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr"/>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>N.14012</t>
+        </is>
+      </c>
       <c r="D30" s="8" t="n">
         <v>1</v>
       </c>
@@ -29411,7 +31823,11 @@
           <t>SEM-20-03</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr"/>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>TORUM</t>
+        </is>
+      </c>
       <c r="D31" s="12" t="n">
         <v>1</v>
       </c>
@@ -29454,7 +31870,11 @@
           <t>SEM-26-03</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr"/>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>TORUM</t>
+        </is>
+      </c>
       <c r="D32" s="8" t="n">
         <v>2</v>
       </c>
@@ -29497,7 +31917,11 @@
           <t>SEM-26-04</t>
         </is>
       </c>
-      <c r="C33" s="12" t="inlineStr"/>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>SAINZ</t>
+        </is>
+      </c>
       <c r="D33" s="12" t="n">
         <v>3</v>
       </c>
@@ -29540,7 +31964,11 @@
           <t>SEM-26-21</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr"/>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>ARAGORN (N.14511)</t>
+        </is>
+      </c>
       <c r="D34" s="8" t="n">
         <v>6</v>
       </c>
@@ -29583,7 +32011,11 @@
           <t>SEM-26-22</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr"/>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>DELAROSA</t>
+        </is>
+      </c>
       <c r="D35" s="12" t="n">
         <v>5</v>
       </c>
@@ -29626,7 +32058,11 @@
           <t>SEM-26-24</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr"/>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>SEANETO</t>
+        </is>
+      </c>
       <c r="D36" s="8" t="n">
         <v>5</v>
       </c>
@@ -29669,7 +32105,11 @@
           <t>SEM-26-28</t>
         </is>
       </c>
-      <c r="C37" s="12" t="inlineStr"/>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>SVMC0019 (ACAPELLA)</t>
+        </is>
+      </c>
       <c r="D37" s="12" t="n">
         <v>2</v>
       </c>
@@ -29712,7 +32152,11 @@
           <t>SEM-26-30</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr"/>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>BONOBO</t>
+        </is>
+      </c>
       <c r="D38" s="8" t="n">
         <v>4</v>
       </c>
@@ -29755,7 +32199,11 @@
           <t>G-20-02</t>
         </is>
       </c>
-      <c r="C39" s="12" t="inlineStr"/>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>KINDER (G 37526)</t>
+        </is>
+      </c>
       <c r="D39" s="12" t="n">
         <v>1</v>
       </c>
@@ -29798,7 +32246,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr"/>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
       <c r="D40" s="8" t="n">
         <v>24</v>
       </c>
@@ -29841,7 +32293,11 @@
           <t>G-26-04</t>
         </is>
       </c>
-      <c r="C41" s="12" t="inlineStr"/>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>KINETIC</t>
+        </is>
+      </c>
       <c r="D41" s="12" t="n">
         <v>7</v>
       </c>
@@ -29884,7 +32340,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr"/>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
       <c r="D42" s="8" t="n">
         <v>16</v>
       </c>
@@ -29927,7 +32387,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="C43" s="12" t="inlineStr"/>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
       <c r="D43" s="12" t="n">
         <v>28</v>
       </c>
@@ -29970,7 +32434,11 @@
           <t>G-26-14</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr"/>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>KIONNA</t>
+        </is>
+      </c>
       <c r="D44" s="8" t="n">
         <v>6</v>
       </c>
@@ -30013,7 +32481,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C45" s="12" t="inlineStr"/>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D45" s="12" t="n">
         <v>19</v>
       </c>
@@ -30056,7 +32528,11 @@
           <t>G-67054</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr"/>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>N.67054</t>
+        </is>
+      </c>
       <c r="D46" s="8" t="n">
         <v>1</v>
       </c>
@@ -30099,7 +32575,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="C47" s="12" t="inlineStr"/>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
       <c r="D47" s="12" t="n">
         <v>1</v>
       </c>
@@ -30142,7 +32622,11 @@
           <t>GLV-26-02</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr"/>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>SV5133MG</t>
+        </is>
+      </c>
       <c r="D48" s="8" t="n">
         <v>2</v>
       </c>
@@ -30185,7 +32669,11 @@
           <t>GLV-26-04</t>
         </is>
       </c>
-      <c r="C49" s="12" t="inlineStr"/>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>PACHANGA (HMC463936)</t>
+        </is>
+      </c>
       <c r="D49" s="12" t="n">
         <v>1</v>
       </c>
@@ -30228,7 +32716,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr"/>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
       <c r="D50" s="8" t="n">
         <v>8</v>
       </c>
@@ -30271,7 +32763,11 @@
           <t>GLV-26-22</t>
         </is>
       </c>
-      <c r="C51" s="12" t="inlineStr"/>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>ANGLIRU (34-GE0337)</t>
+        </is>
+      </c>
       <c r="D51" s="12" t="n">
         <v>1</v>
       </c>
@@ -30314,7 +32810,11 @@
           <t>GLV-26-27</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr"/>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>GALUNA LITHIUM (34-GL0401)</t>
+        </is>
+      </c>
       <c r="D52" s="8" t="n">
         <v>5</v>
       </c>
@@ -30357,7 +32857,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr"/>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
       <c r="D53" s="12" t="n">
         <v>9</v>
       </c>
@@ -30400,7 +32904,11 @@
           <t>GLV-26-30</t>
         </is>
       </c>
-      <c r="C54" s="8" t="inlineStr"/>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>DURERO</t>
+        </is>
+      </c>
       <c r="D54" s="8" t="n">
         <v>7</v>
       </c>
@@ -30443,7 +32951,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr"/>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
       <c r="D55" s="12" t="n">
         <v>16</v>
       </c>
@@ -30486,7 +32998,11 @@
           <t>GLV-26-35</t>
         </is>
       </c>
-      <c r="C56" s="8" t="inlineStr"/>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
       <c r="D56" s="8" t="n">
         <v>3</v>
       </c>
@@ -30529,7 +33045,11 @@
           <t>GLV-26-37</t>
         </is>
       </c>
-      <c r="C57" s="12" t="inlineStr"/>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>GOYA</t>
+        </is>
+      </c>
       <c r="D57" s="12" t="n">
         <v>1</v>
       </c>
@@ -30572,7 +33092,11 @@
           <t>GLV-30335</t>
         </is>
       </c>
-      <c r="C58" s="8" t="inlineStr"/>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>AR-30335</t>
+        </is>
+      </c>
       <c r="D58" s="8" t="n">
         <v>2</v>
       </c>
@@ -30615,7 +33139,11 @@
           <t>GLV-BESODO</t>
         </is>
       </c>
-      <c r="C59" s="12" t="inlineStr"/>
+      <c r="C59" s="12" t="inlineStr">
+        <is>
+          <t>BESODO</t>
+        </is>
+      </c>
       <c r="D59" s="12" t="n">
         <v>4</v>
       </c>
@@ -30658,7 +33186,11 @@
           <t>GLV-CALIMA</t>
         </is>
       </c>
-      <c r="C60" s="8" t="inlineStr"/>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>CALIMA</t>
+        </is>
+      </c>
       <c r="D60" s="8" t="n">
         <v>1</v>
       </c>
@@ -30701,7 +33233,11 @@
           <t>GLV-TERRAL</t>
         </is>
       </c>
-      <c r="C61" s="12" t="inlineStr"/>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>TERRAL</t>
+        </is>
+      </c>
       <c r="D61" s="12" t="n">
         <v>1</v>
       </c>
@@ -30744,7 +33280,11 @@
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="C62" s="8" t="inlineStr"/>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>VENDAVAL</t>
+        </is>
+      </c>
       <c r="D62" s="8" t="n">
         <v>1</v>
       </c>
@@ -30787,7 +33327,11 @@
           <t>IG-23-04</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr"/>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>AST-MSB-31</t>
+        </is>
+      </c>
       <c r="D63" s="12" t="n">
         <v>2</v>
       </c>
@@ -30830,7 +33374,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr"/>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
       <c r="D64" s="8" t="n">
         <v>10</v>
       </c>
@@ -30873,7 +33421,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr"/>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
       <c r="D65" s="12" t="n">
         <v>12</v>
       </c>
@@ -30916,7 +33468,11 @@
           <t>IG-26-06</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr"/>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>MAYAN 443</t>
+        </is>
+      </c>
       <c r="D66" s="8" t="n">
         <v>2</v>
       </c>
@@ -30959,7 +33515,11 @@
           <t>IG-30340</t>
         </is>
       </c>
-      <c r="C67" s="12" t="inlineStr"/>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>AR-30340</t>
+        </is>
+      </c>
       <c r="D67" s="12" t="n">
         <v>1</v>
       </c>
@@ -31002,7 +33562,11 @@
           <t>IG-30358</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr"/>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>AR-30358</t>
+        </is>
+      </c>
       <c r="D68" s="8" t="n">
         <v>1</v>
       </c>
@@ -31045,7 +33609,11 @@
           <t>IG-795</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr"/>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>EWS-MLN-795</t>
+        </is>
+      </c>
       <c r="D69" s="12" t="n">
         <v>1</v>
       </c>
@@ -31088,7 +33656,11 @@
           <t>OR-22-01</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr"/>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>SV7464MA</t>
+        </is>
+      </c>
       <c r="D70" s="8" t="n">
         <v>1</v>
       </c>
@@ -31131,7 +33703,11 @@
           <t>OR-23-04</t>
         </is>
       </c>
-      <c r="C71" s="12" t="inlineStr"/>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>ESM2112</t>
+        </is>
+      </c>
       <c r="D71" s="12" t="n">
         <v>1</v>
       </c>
@@ -31174,7 +33750,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="C72" s="8" t="inlineStr"/>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
       <c r="D72" s="8" t="n">
         <v>10</v>
       </c>
@@ -31217,7 +33797,11 @@
           <t>Z-25-21</t>
         </is>
       </c>
-      <c r="C73" s="12" t="inlineStr"/>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>HMC464074</t>
+        </is>
+      </c>
       <c r="D73" s="12" t="n">
         <v>2</v>
       </c>
@@ -31260,7 +33844,11 @@
           <t>Z-26-02</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr"/>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>DOLSURA (34-138)</t>
+        </is>
+      </c>
       <c r="D74" s="8" t="n">
         <v>1</v>
       </c>
@@ -31303,7 +33891,11 @@
           <t>Z-26-03</t>
         </is>
       </c>
-      <c r="C75" s="12" t="inlineStr"/>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>BRAVURA (34-133)</t>
+        </is>
+      </c>
       <c r="D75" s="12" t="n">
         <v>5</v>
       </c>
@@ -31346,7 +33938,11 @@
           <t>Z-26-06</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr"/>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>MINITHOR (34-148)</t>
+        </is>
+      </c>
       <c r="D76" s="8" t="n">
         <v>4</v>
       </c>
@@ -31389,7 +33985,11 @@
           <t>Z-26-15</t>
         </is>
       </c>
-      <c r="C77" s="12" t="inlineStr"/>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>GRACIANO</t>
+        </is>
+      </c>
       <c r="D77" s="12" t="n">
         <v>1</v>
       </c>
@@ -31432,7 +34032,11 @@
           <t>Z-26-18</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr"/>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>CORRALES</t>
+        </is>
+      </c>
       <c r="D78" s="8" t="n">
         <v>1</v>
       </c>
@@ -31475,7 +34079,11 @@
           <t>Z-26-27</t>
         </is>
       </c>
-      <c r="C79" s="12" t="inlineStr"/>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>CAMACHO</t>
+        </is>
+      </c>
       <c r="D79" s="12" t="n">
         <v>1</v>
       </c>
@@ -31512,7 +34120,11 @@
           <t>Z-26-31</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr"/>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>CAMPUZANO</t>
+        </is>
+      </c>
       <c r="D80" s="8" t="n">
         <v>1</v>
       </c>
@@ -31555,7 +34167,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="C81" s="12" t="inlineStr"/>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
       <c r="D81" s="12" t="n">
         <v>6</v>
       </c>
@@ -31598,7 +34214,11 @@
           <t>Z-4481</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr"/>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>HMC 4481</t>
+        </is>
+      </c>
       <c r="D82" s="8" t="n">
         <v>2</v>
       </c>
@@ -31641,7 +34261,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="C83" s="12" t="inlineStr"/>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
       <c r="D83" s="12" t="n">
         <v>10</v>
       </c>
@@ -31684,7 +34308,11 @@
           <t>GC-26-03</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr"/>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>SUNBALL</t>
+        </is>
+      </c>
       <c r="D84" s="8" t="n">
         <v>1</v>
       </c>
@@ -31727,7 +34355,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="C85" s="12" t="inlineStr"/>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
       <c r="D85" s="12" t="n">
         <v>19</v>
       </c>
@@ -31796,7 +34428,11 @@
           <t>A-25-09</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr"/>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>PEKIN</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
@@ -31804,7 +34440,11 @@
           <t>A-26-02</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr"/>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>MAILLOT</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -31812,7 +34452,11 @@
           <t>A-26-04</t>
         </is>
       </c>
-      <c r="B4" s="19" t="inlineStr"/>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>ROBLEO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -31820,7 +34464,11 @@
           <t>A-26-11</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr"/>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>AMBARINO (E25M.00702)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -31828,7 +34476,11 @@
           <t>A-26-12</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr"/>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>PIEL DE SOL</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -31836,7 +34488,11 @@
           <t>A-26-13</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr"/>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>YACAL (34-191)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -31844,7 +34500,11 @@
           <t>A-26-14</t>
         </is>
       </c>
-      <c r="B8" s="19" t="inlineStr"/>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>NIVAL (34-379)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -31852,7 +34512,11 @@
           <t>A-26-17</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr"/>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>MANCHESTER</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -31860,7 +34524,11 @@
           <t>A-26-18</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>MIRLO</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -31868,7 +34536,11 @@
           <t>A-26-21</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr"/>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>AMBATAR</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -31876,7 +34548,11 @@
           <t>A-26-25</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr"/>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>MS12MA058</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -31884,7 +34560,11 @@
           <t>A-26-26</t>
         </is>
       </c>
-      <c r="B13" s="19" t="inlineStr"/>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>TEQUILA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -31892,7 +34572,11 @@
           <t>A-26-27</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr"/>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>HAWAI</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -31900,7 +34584,11 @@
           <t>A-ATILA</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr"/>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>ATILA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -31908,7 +34596,11 @@
           <t>A-ROCHESTE</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr"/>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>ROCHESTE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -31916,7 +34608,11 @@
           <t>A-SUERTE</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr"/>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>SUERTE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -31924,7 +34620,11 @@
           <t>A-ZENITH</t>
         </is>
       </c>
-      <c r="B18" s="19" t="inlineStr"/>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>ZENITH</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -31932,7 +34632,11 @@
           <t>C-19-11</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr"/>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>N.12788</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -31940,7 +34644,11 @@
           <t>C-24-21</t>
         </is>
       </c>
-      <c r="B20" s="19" t="inlineStr"/>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>MAGVERIK</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -31948,7 +34656,11 @@
           <t>C-26-03</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr"/>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>ZINASOL (34-506)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -31956,7 +34668,11 @@
           <t>C-26-22</t>
         </is>
       </c>
-      <c r="B22" s="19" t="inlineStr"/>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>CORMORAN</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
@@ -31964,7 +34680,11 @@
           <t>C-26-24</t>
         </is>
       </c>
-      <c r="B23" s="19" t="inlineStr"/>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>PEARL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -31972,7 +34692,11 @@
           <t>C-26-26</t>
         </is>
       </c>
-      <c r="B24" s="19" t="inlineStr"/>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>URKAN</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
@@ -31980,7 +34704,11 @@
           <t>C-26-28</t>
         </is>
       </c>
-      <c r="B25" s="19" t="inlineStr"/>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>SUGARSUN (SVMC1524)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -31988,7 +34716,11 @@
           <t>C-26-31</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr"/>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>ORANGELUP</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
@@ -31996,7 +34728,11 @@
           <t>C-26-32</t>
         </is>
       </c>
-      <c r="B27" s="19" t="inlineStr"/>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>DELPHES</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -32004,7 +34740,11 @@
           <t>G-20-02</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr"/>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>KINDER (G 37526)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
@@ -32012,7 +34752,11 @@
           <t>G-26-03</t>
         </is>
       </c>
-      <c r="B29" s="19" t="inlineStr"/>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>KISSANE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -32020,7 +34764,11 @@
           <t>G-26-04</t>
         </is>
       </c>
-      <c r="B30" s="19" t="inlineStr"/>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>KINETIC</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
@@ -32028,7 +34776,11 @@
           <t>G-26-06</t>
         </is>
       </c>
-      <c r="B31" s="19" t="inlineStr"/>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>KIABI</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -32036,7 +34788,11 @@
           <t>G-26-09</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr"/>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>KIBIC</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
@@ -32044,7 +34800,11 @@
           <t>G-26-14</t>
         </is>
       </c>
-      <c r="B33" s="19" t="inlineStr"/>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>KIONNA</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -32052,7 +34812,11 @@
           <t>G-26-17</t>
         </is>
       </c>
-      <c r="B34" s="19" t="inlineStr"/>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>KIARIS</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
@@ -32060,7 +34824,11 @@
           <t>G-67054</t>
         </is>
       </c>
-      <c r="B35" s="19" t="inlineStr"/>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>N.67054</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
@@ -32068,7 +34836,11 @@
           <t>GC-26-02</t>
         </is>
       </c>
-      <c r="B36" s="19" t="inlineStr"/>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>SUNSILK</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
@@ -32076,7 +34848,11 @@
           <t>GC-26-03</t>
         </is>
       </c>
-      <c r="B37" s="19" t="inlineStr"/>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>SUNBALL</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -32084,7 +34860,11 @@
           <t>GC-26-04</t>
         </is>
       </c>
-      <c r="B38" s="19" t="inlineStr"/>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>SUNBEAT</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
@@ -32092,7 +34872,11 @@
           <t>GLV-26-02</t>
         </is>
       </c>
-      <c r="B39" s="19" t="inlineStr"/>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>SV5133MG</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
@@ -32100,7 +34884,11 @@
           <t>GLV-26-04</t>
         </is>
       </c>
-      <c r="B40" s="19" t="inlineStr"/>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>PACHANGA (HMC463936)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
@@ -32108,7 +34896,11 @@
           <t>GLV-26-11</t>
         </is>
       </c>
-      <c r="B41" s="19" t="inlineStr"/>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>ALBIZU (SVMG7420)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -32116,7 +34908,11 @@
           <t>GLV-26-22</t>
         </is>
       </c>
-      <c r="B42" s="19" t="inlineStr"/>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>ANGLIRU (34-GE0337)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
@@ -32124,7 +34920,11 @@
           <t>GLV-26-27</t>
         </is>
       </c>
-      <c r="B43" s="19" t="inlineStr"/>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>GALUNA LITHIUM (34-GL0401)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
@@ -32132,7 +34932,11 @@
           <t>GLV-26-28</t>
         </is>
       </c>
-      <c r="B44" s="19" t="inlineStr"/>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>GALVES</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
@@ -32140,7 +34944,11 @@
           <t>GLV-26-30</t>
         </is>
       </c>
-      <c r="B45" s="19" t="inlineStr"/>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>DURERO</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -32148,7 +34956,11 @@
           <t>GLV-26-32</t>
         </is>
       </c>
-      <c r="B46" s="19" t="inlineStr"/>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>MAIORAL</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -32156,7 +34968,11 @@
           <t>GLV-26-35</t>
         </is>
       </c>
-      <c r="B47" s="19" t="inlineStr"/>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>BERNAL</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -32164,7 +34980,11 @@
           <t>GLV-26-37</t>
         </is>
       </c>
-      <c r="B48" s="19" t="inlineStr"/>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>GOYA</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
@@ -32172,7 +34992,11 @@
           <t>GLV-30335</t>
         </is>
       </c>
-      <c r="B49" s="19" t="inlineStr"/>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>AR-30335</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -32180,7 +35004,11 @@
           <t>GLV-BESODO</t>
         </is>
       </c>
-      <c r="B50" s="19" t="inlineStr"/>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>BESODO</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
@@ -32188,7 +35016,11 @@
           <t>GLV-CALIMA</t>
         </is>
       </c>
-      <c r="B51" s="19" t="inlineStr"/>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>CALIMA</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -32196,7 +35028,11 @@
           <t>GLV-TERRAL</t>
         </is>
       </c>
-      <c r="B52" s="19" t="inlineStr"/>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>TERRAL</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -32204,7 +35040,11 @@
           <t>IG-23-04</t>
         </is>
       </c>
-      <c r="B53" s="19" t="inlineStr"/>
+      <c r="B53" s="19" t="inlineStr">
+        <is>
+          <t>AST-MSB-31</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -32212,7 +35052,11 @@
           <t>IG-26-01</t>
         </is>
       </c>
-      <c r="B54" s="19" t="inlineStr"/>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>KOHAKU</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
@@ -32220,7 +35064,11 @@
           <t>IG-26-03</t>
         </is>
       </c>
-      <c r="B55" s="19" t="inlineStr"/>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>SILVERWAVE</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -32228,7 +35076,11 @@
           <t>IG-26-06</t>
         </is>
       </c>
-      <c r="B56" s="19" t="inlineStr"/>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>MAYAN 443</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
@@ -32236,7 +35088,11 @@
           <t>IG-30340</t>
         </is>
       </c>
-      <c r="B57" s="19" t="inlineStr"/>
+      <c r="B57" s="19" t="inlineStr">
+        <is>
+          <t>AR-30340</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
@@ -32244,7 +35100,11 @@
           <t>IG-30358</t>
         </is>
       </c>
-      <c r="B58" s="19" t="inlineStr"/>
+      <c r="B58" s="19" t="inlineStr">
+        <is>
+          <t>AR-30358</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -32252,7 +35112,11 @@
           <t>IG-795</t>
         </is>
       </c>
-      <c r="B59" s="19" t="inlineStr"/>
+      <c r="B59" s="19" t="inlineStr">
+        <is>
+          <t>EWS-MLN-795</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
@@ -32260,7 +35124,11 @@
           <t>INDURAIN</t>
         </is>
       </c>
-      <c r="B60" s="19" t="inlineStr"/>
+      <c r="B60" s="19" t="inlineStr">
+        <is>
+          <t>INDURAIN</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
@@ -32268,7 +35136,11 @@
           <t>MIELON</t>
         </is>
       </c>
-      <c r="B61" s="19" t="inlineStr"/>
+      <c r="B61" s="19" t="inlineStr">
+        <is>
+          <t>MIELON</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
@@ -32276,7 +35148,11 @@
           <t>OR-22-01</t>
         </is>
       </c>
-      <c r="B62" s="19" t="inlineStr"/>
+      <c r="B62" s="19" t="inlineStr">
+        <is>
+          <t>SV7464MA</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -32284,7 +35160,11 @@
           <t>OR-23-04</t>
         </is>
       </c>
-      <c r="B63" s="19" t="inlineStr"/>
+      <c r="B63" s="19" t="inlineStr">
+        <is>
+          <t>ESM2112</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
@@ -32292,7 +35172,11 @@
           <t>OR-26-02</t>
         </is>
       </c>
-      <c r="B64" s="19" t="inlineStr"/>
+      <c r="B64" s="19" t="inlineStr">
+        <is>
+          <t>SVMA6558</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
@@ -32300,7 +35184,11 @@
           <t>SEM-14012</t>
         </is>
       </c>
-      <c r="B65" s="19" t="inlineStr"/>
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>N.14012</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
@@ -32308,7 +35196,11 @@
           <t>SEM-20-03</t>
         </is>
       </c>
-      <c r="B66" s="19" t="inlineStr"/>
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>TORUM</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
@@ -32316,7 +35208,11 @@
           <t>SEM-26-03</t>
         </is>
       </c>
-      <c r="B67" s="19" t="inlineStr"/>
+      <c r="B67" s="19" t="inlineStr">
+        <is>
+          <t>TORUM</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
@@ -32324,7 +35220,11 @@
           <t>SEM-26-04</t>
         </is>
       </c>
-      <c r="B68" s="19" t="inlineStr"/>
+      <c r="B68" s="19" t="inlineStr">
+        <is>
+          <t>SAINZ</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
@@ -32332,7 +35232,11 @@
           <t>SEM-26-21</t>
         </is>
       </c>
-      <c r="B69" s="19" t="inlineStr"/>
+      <c r="B69" s="19" t="inlineStr">
+        <is>
+          <t>ARAGORN (N.14511)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
@@ -32340,7 +35244,11 @@
           <t>SEM-26-22</t>
         </is>
       </c>
-      <c r="B70" s="19" t="inlineStr"/>
+      <c r="B70" s="19" t="inlineStr">
+        <is>
+          <t>DELAROSA</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
@@ -32348,7 +35256,11 @@
           <t>SEM-26-24</t>
         </is>
       </c>
-      <c r="B71" s="19" t="inlineStr"/>
+      <c r="B71" s="19" t="inlineStr">
+        <is>
+          <t>SEANETO</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
@@ -32356,7 +35268,11 @@
           <t>SEM-26-28</t>
         </is>
       </c>
-      <c r="B72" s="19" t="inlineStr"/>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>SVMC0019 (ACAPELLA)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
@@ -32364,7 +35280,11 @@
           <t>SEM-26-30</t>
         </is>
       </c>
-      <c r="B73" s="19" t="inlineStr"/>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>BONOBO</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
@@ -32372,7 +35292,11 @@
           <t>VENDAVAL</t>
         </is>
       </c>
-      <c r="B74" s="19" t="inlineStr"/>
+      <c r="B74" s="19" t="inlineStr">
+        <is>
+          <t>VENDAVAL</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
@@ -32380,7 +35304,11 @@
           <t>Z-25-21</t>
         </is>
       </c>
-      <c r="B75" s="19" t="inlineStr"/>
+      <c r="B75" s="19" t="inlineStr">
+        <is>
+          <t>HMC464074</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
@@ -32388,7 +35316,11 @@
           <t>Z-26-02</t>
         </is>
       </c>
-      <c r="B76" s="19" t="inlineStr"/>
+      <c r="B76" s="19" t="inlineStr">
+        <is>
+          <t>DOLSURA (34-138)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
@@ -32396,7 +35328,11 @@
           <t>Z-26-03</t>
         </is>
       </c>
-      <c r="B77" s="19" t="inlineStr"/>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>BRAVURA (34-133)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
@@ -32404,7 +35340,11 @@
           <t>Z-26-06</t>
         </is>
       </c>
-      <c r="B78" s="19" t="inlineStr"/>
+      <c r="B78" s="19" t="inlineStr">
+        <is>
+          <t>MINITHOR (34-148)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
@@ -32412,7 +35352,11 @@
           <t>Z-26-15</t>
         </is>
       </c>
-      <c r="B79" s="19" t="inlineStr"/>
+      <c r="B79" s="19" t="inlineStr">
+        <is>
+          <t>GRACIANO</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
@@ -32420,7 +35364,11 @@
           <t>Z-26-18</t>
         </is>
       </c>
-      <c r="B80" s="19" t="inlineStr"/>
+      <c r="B80" s="19" t="inlineStr">
+        <is>
+          <t>CORRALES</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
@@ -32428,7 +35376,11 @@
           <t>Z-26-27</t>
         </is>
       </c>
-      <c r="B81" s="19" t="inlineStr"/>
+      <c r="B81" s="19" t="inlineStr">
+        <is>
+          <t>CAMACHO</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
@@ -32436,7 +35388,11 @@
           <t>Z-26-31</t>
         </is>
       </c>
-      <c r="B82" s="19" t="inlineStr"/>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>CAMPUZANO</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
@@ -32444,7 +35400,11 @@
           <t>Z-26-32</t>
         </is>
       </c>
-      <c r="B83" s="19" t="inlineStr"/>
+      <c r="B83" s="19" t="inlineStr">
+        <is>
+          <t>MINIJACK</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
@@ -32452,7 +35412,11 @@
           <t>Z-4481</t>
         </is>
       </c>
-      <c r="B84" s="19" t="inlineStr"/>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>HMC 4481</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B84"/>

--- a/Datos de azucar y firmeza por melon en general.xlsx
+++ b/Datos de azucar y firmeza por melon en general.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Muestras azúcar (estim.)</t>
+          <t>Muestras azúcar (deducidas)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -619,7 +619,7 @@
         <v>7407</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>0.8304</v>
+        <v>0.8308</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>3509</v>
@@ -667,7 +667,7 @@
         <v>95</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>0.6943</v>
+        <v>0.6947</v>
       </c>
       <c r="K3" s="5" t="n">
         <v>45</v>
@@ -719,7 +719,7 @@
         <v>95</v>
       </c>
       <c r="J4" s="11" t="n">
-        <v>0.6943</v>
+        <v>0.6947</v>
       </c>
       <c r="K4" s="8" t="n">
         <v>45</v>
@@ -767,7 +767,7 @@
         <v>165</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>0.6906</v>
+        <v>0.6909</v>
       </c>
       <c r="K5" s="5" t="n">
         <v>80</v>
@@ -871,7 +871,7 @@
         <v>35</v>
       </c>
       <c r="J7" s="11" t="n">
-        <v>0.3999</v>
+        <v>0.4</v>
       </c>
       <c r="K7" s="8" t="n">
         <v>15</v>
@@ -975,7 +975,7 @@
         <v>110</v>
       </c>
       <c r="J9" s="11" t="n">
-        <v>0.8087</v>
+        <v>0.8091</v>
       </c>
       <c r="K9" s="8" t="n">
         <v>55</v>
@@ -1023,7 +1023,7 @@
         <v>664</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.8431</v>
+        <v>0.8434</v>
       </c>
       <c r="K10" s="5" t="n">
         <v>319</v>
@@ -1075,7 +1075,7 @@
         <v>15</v>
       </c>
       <c r="J11" s="11" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0667</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>5</v>
@@ -1231,7 +1231,7 @@
         <v>99</v>
       </c>
       <c r="J14" s="11" t="n">
-        <v>0.8989</v>
+        <v>0.899</v>
       </c>
       <c r="K14" s="8" t="n">
         <v>54</v>
@@ -1387,7 +1387,7 @@
         <v>142</v>
       </c>
       <c r="J17" s="11" t="n">
-        <v>0.753</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="K17" s="8" t="n">
         <v>65</v>
@@ -1491,7 +1491,7 @@
         <v>70</v>
       </c>
       <c r="J19" s="11" t="n">
-        <v>0.9425</v>
+        <v>0.9429</v>
       </c>
       <c r="K19" s="8" t="n">
         <v>35</v>
@@ -1543,7 +1543,7 @@
         <v>118</v>
       </c>
       <c r="J20" s="11" t="n">
-        <v>0.9486</v>
+        <v>0.9492</v>
       </c>
       <c r="K20" s="8" t="n">
         <v>60</v>
@@ -1595,7 +1595,7 @@
         <v>70</v>
       </c>
       <c r="J21" s="11" t="n">
-        <v>0.9567</v>
+        <v>0.9571</v>
       </c>
       <c r="K21" s="8" t="n">
         <v>35</v>
@@ -1643,7 +1643,7 @@
         <v>1290</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7488</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>580</v>
@@ -1695,7 +1695,7 @@
         <v>140</v>
       </c>
       <c r="J23" s="11" t="n">
-        <v>0.7138</v>
+        <v>0.7143</v>
       </c>
       <c r="K23" s="8" t="n">
         <v>65</v>
@@ -1851,7 +1851,7 @@
         <v>90</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.7108</v>
+        <v>0.7111</v>
       </c>
       <c r="K26" s="8" t="n">
         <v>40</v>
@@ -1903,7 +1903,7 @@
         <v>150</v>
       </c>
       <c r="J27" s="11" t="n">
-        <v>0.9462</v>
+        <v>0.9467</v>
       </c>
       <c r="K27" s="8" t="n">
         <v>75</v>
@@ -2111,7 +2111,7 @@
         <v>140</v>
       </c>
       <c r="J31" s="11" t="n">
-        <v>0.8995</v>
+        <v>0.9</v>
       </c>
       <c r="K31" s="8" t="n">
         <v>70</v>
@@ -2215,7 +2215,7 @@
         <v>101</v>
       </c>
       <c r="J33" s="11" t="n">
-        <v>0.9207</v>
+        <v>0.9208</v>
       </c>
       <c r="K33" s="8" t="n">
         <v>50</v>
@@ -2319,7 +2319,7 @@
         <v>292</v>
       </c>
       <c r="J35" s="11" t="n">
-        <v>0.6261</v>
+        <v>0.6267</v>
       </c>
       <c r="K35" s="8" t="n">
         <v>115</v>
@@ -2423,7 +2423,7 @@
         <v>157</v>
       </c>
       <c r="J37" s="11" t="n">
-        <v>0.643</v>
+        <v>0.6433</v>
       </c>
       <c r="K37" s="8" t="n">
         <v>70</v>
@@ -2471,7 +2471,7 @@
         <v>401</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9002</v>
       </c>
       <c r="K38" s="5" t="n">
         <v>194</v>
@@ -2523,7 +2523,7 @@
         <v>180</v>
       </c>
       <c r="J39" s="11" t="n">
-        <v>0.9826</v>
+        <v>0.9833</v>
       </c>
       <c r="K39" s="8" t="n">
         <v>90</v>
@@ -2627,7 +2627,7 @@
         <v>211</v>
       </c>
       <c r="J41" s="11" t="n">
-        <v>0.8242</v>
+        <v>0.8246</v>
       </c>
       <c r="K41" s="8" t="n">
         <v>100</v>
@@ -2675,7 +2675,7 @@
         <v>543</v>
       </c>
       <c r="J42" s="7" t="n">
-        <v>0.9371</v>
+        <v>0.9374</v>
       </c>
       <c r="K42" s="5" t="n">
         <v>264</v>
@@ -2727,7 +2727,7 @@
         <v>112</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="K43" s="8" t="n">
         <v>55</v>
@@ -2779,7 +2779,7 @@
         <v>30</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>0.8999</v>
+        <v>0.9</v>
       </c>
       <c r="K44" s="8" t="n">
         <v>15</v>
@@ -2831,7 +2831,7 @@
         <v>60</v>
       </c>
       <c r="J45" s="11" t="n">
-        <v>0.8831</v>
+        <v>0.8833</v>
       </c>
       <c r="K45" s="8" t="n">
         <v>30</v>
@@ -2883,7 +2883,7 @@
         <v>141</v>
       </c>
       <c r="J46" s="11" t="n">
-        <v>0.9142</v>
+        <v>0.9149</v>
       </c>
       <c r="K46" s="8" t="n">
         <v>69</v>
@@ -2987,7 +2987,7 @@
         <v>30</v>
       </c>
       <c r="J48" s="11" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="K48" s="8" t="n">
         <v>15</v>
@@ -3039,7 +3039,7 @@
         <v>30</v>
       </c>
       <c r="J49" s="11" t="n">
-        <v>0.8331</v>
+        <v>0.8333</v>
       </c>
       <c r="K49" s="8" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
         <v>452</v>
       </c>
       <c r="J52" s="7" t="n">
-        <v>0.6788</v>
+        <v>0.6792</v>
       </c>
       <c r="K52" s="5" t="n">
         <v>214</v>
@@ -3295,7 +3295,7 @@
         <v>101</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>0.6039</v>
+        <v>0.604</v>
       </c>
       <c r="K54" s="8" t="n">
         <v>45</v>
@@ -3451,7 +3451,7 @@
         <v>130</v>
       </c>
       <c r="J57" s="11" t="n">
-        <v>0.6993</v>
+        <v>0.7</v>
       </c>
       <c r="K57" s="8" t="n">
         <v>59</v>
@@ -3503,7 +3503,7 @@
         <v>161</v>
       </c>
       <c r="J58" s="11" t="n">
-        <v>0.7201</v>
+        <v>0.7205</v>
       </c>
       <c r="K58" s="8" t="n">
         <v>80</v>
@@ -3551,7 +3551,7 @@
         <v>866</v>
       </c>
       <c r="J59" s="7" t="n">
-        <v>0.8793</v>
+        <v>0.8799</v>
       </c>
       <c r="K59" s="5" t="n">
         <v>400</v>
@@ -3655,7 +3655,7 @@
         <v>30</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>0.7664</v>
+        <v>0.7667</v>
       </c>
       <c r="K61" s="8" t="n">
         <v>15</v>
@@ -3863,7 +3863,7 @@
         <v>137</v>
       </c>
       <c r="J65" s="11" t="n">
-        <v>0.5976</v>
+        <v>0.5985</v>
       </c>
       <c r="K65" s="8" t="n">
         <v>35</v>
@@ -3967,7 +3967,7 @@
         <v>70</v>
       </c>
       <c r="J67" s="11" t="n">
-        <v>0.9424</v>
+        <v>0.9429</v>
       </c>
       <c r="K67" s="8" t="n">
         <v>35</v>
@@ -4019,7 +4019,7 @@
         <v>139</v>
       </c>
       <c r="J68" s="11" t="n">
-        <v>0.9272</v>
+        <v>0.9281</v>
       </c>
       <c r="K68" s="8" t="n">
         <v>65</v>
@@ -4059,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="10" t="n">
-        <v>14.39</v>
+        <v>14.38</v>
       </c>
       <c r="G69" s="8" t="n">
         <v>9</v>
@@ -4071,7 +4071,7 @@
         <v>390</v>
       </c>
       <c r="J69" s="11" t="n">
-        <v>0.9532</v>
+        <v>0.9538</v>
       </c>
       <c r="K69" s="8" t="n">
         <v>195</v>
@@ -4119,7 +4119,7 @@
         <v>1000</v>
       </c>
       <c r="J70" s="7" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="K70" s="5" t="n">
         <v>460</v>
@@ -4223,7 +4223,7 @@
         <v>189</v>
       </c>
       <c r="J72" s="11" t="n">
-        <v>0.9201</v>
+        <v>0.9206</v>
       </c>
       <c r="K72" s="8" t="n">
         <v>95</v>
@@ -4275,7 +4275,7 @@
         <v>30</v>
       </c>
       <c r="J73" s="11" t="n">
-        <v>0.6331</v>
+        <v>0.6333</v>
       </c>
       <c r="K73" s="8" t="n">
         <v>15</v>
@@ -4327,7 +4327,7 @@
         <v>130</v>
       </c>
       <c r="J74" s="11" t="n">
-        <v>0.8223</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="K74" s="8" t="n">
         <v>65</v>
@@ -4639,7 +4639,7 @@
         <v>60</v>
       </c>
       <c r="J80" s="11" t="n">
-        <v>0.9829</v>
+        <v>0.9833</v>
       </c>
       <c r="K80" s="8" t="n">
         <v>25</v>
@@ -4899,7 +4899,7 @@
         <v>71</v>
       </c>
       <c r="J85" s="11" t="n">
-        <v>0.7461</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="K85" s="8" t="n">
         <v>35</v>
@@ -4951,7 +4951,7 @@
         <v>130</v>
       </c>
       <c r="J86" s="11" t="n">
-        <v>0.1842</v>
+        <v>0.1846</v>
       </c>
       <c r="K86" s="8" t="n">
         <v>30</v>
@@ -5091,7 +5091,7 @@
         <v>9</v>
       </c>
       <c r="F89" s="6" t="n">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="G89" s="5" t="n">
         <v>8</v>
@@ -5103,7 +5103,7 @@
         <v>1000</v>
       </c>
       <c r="J89" s="7" t="n">
-        <v>0.9386</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="K89" s="5" t="n">
         <v>509</v>
@@ -5155,7 +5155,7 @@
         <v>109</v>
       </c>
       <c r="J90" s="11" t="n">
-        <v>0.8894</v>
+        <v>0.8899</v>
       </c>
       <c r="K90" s="8" t="n">
         <v>54</v>
@@ -5207,7 +5207,7 @@
         <v>150</v>
       </c>
       <c r="J91" s="11" t="n">
-        <v>0.9796</v>
+        <v>0.98</v>
       </c>
       <c r="K91" s="8" t="n">
         <v>75</v>
@@ -5311,7 +5311,7 @@
         <v>299</v>
       </c>
       <c r="J93" s="11" t="n">
-        <v>0.9425</v>
+        <v>0.9431</v>
       </c>
       <c r="K93" s="8" t="n">
         <v>155</v>
@@ -5363,7 +5363,7 @@
         <v>261</v>
       </c>
       <c r="J94" s="11" t="n">
-        <v>0.9804</v>
+        <v>0.9808</v>
       </c>
       <c r="K94" s="8" t="n">
         <v>130</v>
@@ -5519,7 +5519,7 @@
         <v>21</v>
       </c>
       <c r="J97" s="11" t="n">
-        <v>0.8092</v>
+        <v>0.8095</v>
       </c>
       <c r="K97" s="8" t="n">
         <v>10</v>
@@ -5619,7 +5619,7 @@
         <v>155</v>
       </c>
       <c r="J99" s="7" t="n">
-        <v>0.8127</v>
+        <v>0.8129</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>75</v>
@@ -5659,7 +5659,7 @@
         <v>1</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>13.7</v>
+        <v>13.69</v>
       </c>
       <c r="G100" s="8" t="n">
         <v>9</v>
@@ -5671,7 +5671,7 @@
         <v>95</v>
       </c>
       <c r="J100" s="11" t="n">
-        <v>0.7049</v>
+        <v>0.7053</v>
       </c>
       <c r="K100" s="8" t="n">
         <v>45</v>
@@ -5823,7 +5823,7 @@
         <v>281</v>
       </c>
       <c r="J103" s="7" t="n">
-        <v>0.8929</v>
+        <v>0.8932</v>
       </c>
       <c r="K103" s="5" t="n">
         <v>135</v>
@@ -5875,7 +5875,7 @@
         <v>140</v>
       </c>
       <c r="J104" s="11" t="n">
-        <v>0.9353</v>
+        <v>0.9357</v>
       </c>
       <c r="K104" s="8" t="n">
         <v>65</v>
@@ -5927,7 +5927,7 @@
         <v>71</v>
       </c>
       <c r="J105" s="11" t="n">
-        <v>0.8023</v>
+        <v>0.8028</v>
       </c>
       <c r="K105" s="8" t="n">
         <v>35</v>
@@ -6031,7 +6031,7 @@
         <v>30</v>
       </c>
       <c r="J107" s="11" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="K107" s="8" t="n">
         <v>15</v>
@@ -6079,7 +6079,7 @@
         <v>314</v>
       </c>
       <c r="J108" s="7" t="n">
-        <v>0.834</v>
+        <v>0.8344</v>
       </c>
       <c r="K108" s="5" t="n">
         <v>150</v>
@@ -6131,7 +6131,7 @@
         <v>29</v>
       </c>
       <c r="J109" s="11" t="n">
-        <v>0.5171</v>
+        <v>0.5172</v>
       </c>
       <c r="K109" s="8" t="n">
         <v>10</v>
@@ -6183,7 +6183,7 @@
         <v>120</v>
       </c>
       <c r="J110" s="11" t="n">
-        <v>0.9498</v>
+        <v>0.95</v>
       </c>
       <c r="K110" s="8" t="n">
         <v>60</v>
@@ -6235,7 +6235,7 @@
         <v>145</v>
       </c>
       <c r="J111" s="11" t="n">
-        <v>0.7924</v>
+        <v>0.7931</v>
       </c>
       <c r="K111" s="8" t="n">
         <v>70</v>
@@ -6387,7 +6387,7 @@
         <v>30</v>
       </c>
       <c r="J114" s="7" t="n">
-        <v>0.6663</v>
+        <v>0.6667</v>
       </c>
       <c r="K114" s="5" t="n">
         <v>15</v>
@@ -6439,7 +6439,7 @@
         <v>30</v>
       </c>
       <c r="J115" s="11" t="n">
-        <v>0.6663</v>
+        <v>0.6667</v>
       </c>
       <c r="K115" s="8" t="n">
         <v>15</v>
@@ -6927,7 +6927,7 @@
         <v>81</v>
       </c>
       <c r="J125" s="7" t="n">
-        <v>0.901</v>
+        <v>0.9012</v>
       </c>
       <c r="K125" s="5" t="n">
         <v>34</v>
@@ -6979,7 +6979,7 @@
         <v>60</v>
       </c>
       <c r="J126" s="11" t="n">
-        <v>0.9498</v>
+        <v>0.95</v>
       </c>
       <c r="K126" s="8" t="n">
         <v>29</v>
@@ -7067,7 +7067,7 @@
         <v>21</v>
       </c>
       <c r="J128" s="11" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.7619</v>
       </c>
       <c r="K128" s="8" t="n">
         <v>5</v>
@@ -7275,7 +7275,7 @@
         <v>69</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>13.4</v>
+        <v>13.49</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>5</v>
@@ -7284,10 +7284,10 @@
         <v>19</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>8173</v>
+        <v>10631</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>0.8091</v>
+        <v>0.8151</v>
       </c>
       <c r="K133" s="2" t="n">
         <v>2374</v>
@@ -7435,7 +7435,7 @@
         <v>323</v>
       </c>
       <c r="J136" s="7" t="n">
-        <v>0.7894</v>
+        <v>0.7895</v>
       </c>
       <c r="K136" s="5" t="n">
         <v>80</v>
@@ -7643,7 +7643,7 @@
         <v>63</v>
       </c>
       <c r="J140" s="11" t="n">
-        <v>0.841</v>
+        <v>0.8413</v>
       </c>
       <c r="K140" s="8" t="n">
         <v>15</v>
@@ -7835,7 +7835,7 @@
         <v>10</v>
       </c>
       <c r="F144" s="6" t="n">
-        <v>13.86</v>
+        <v>14.08</v>
       </c>
       <c r="G144" s="5" t="n">
         <v>5</v>
@@ -7844,10 +7844,10 @@
         <v>18</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>1238</v>
+        <v>1855</v>
       </c>
       <c r="J144" s="7" t="n">
-        <v>0.8502</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="K144" s="5" t="n">
         <v>305</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="F145" s="10" t="n">
-        <v>14.73</v>
+        <v>14.72</v>
       </c>
       <c r="G145" s="8" t="n">
         <v>8</v>
@@ -7899,7 +7899,7 @@
         <v>60</v>
       </c>
       <c r="J145" s="11" t="n">
-        <v>0.9498</v>
+        <v>0.95</v>
       </c>
       <c r="K145" s="8" t="n">
         <v>15</v>
@@ -7951,7 +7951,7 @@
         <v>208</v>
       </c>
       <c r="J146" s="11" t="n">
-        <v>0.8314</v>
+        <v>0.8317</v>
       </c>
       <c r="K146" s="8" t="n">
         <v>40</v>
@@ -8003,7 +8003,7 @@
         <v>180</v>
       </c>
       <c r="J147" s="11" t="n">
-        <v>0.9273</v>
+        <v>0.9278</v>
       </c>
       <c r="K147" s="8" t="n">
         <v>45</v>
@@ -8107,7 +8107,7 @@
         <v>60</v>
       </c>
       <c r="J149" s="11" t="n">
-        <v>0.9497</v>
+        <v>0.95</v>
       </c>
       <c r="K149" s="8" t="n">
         <v>10</v>
@@ -8251,7 +8251,7 @@
         <v>1</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>14.52</v>
+        <v>14.51</v>
       </c>
       <c r="G152" s="8" t="n">
         <v>5</v>
@@ -8260,10 +8260,10 @@
         <v>16</v>
       </c>
       <c r="I152" s="8" t="n">
-        <v>100</v>
+        <v>717</v>
       </c>
       <c r="J152" s="11" t="n">
-        <v>0.9492</v>
+        <v>0.9498</v>
       </c>
       <c r="K152" s="8" t="n">
         <v>55</v>
@@ -8315,7 +8315,7 @@
         <v>190</v>
       </c>
       <c r="J153" s="11" t="n">
-        <v>0.8733</v>
+        <v>0.8737</v>
       </c>
       <c r="K153" s="8" t="n">
         <v>45</v>
@@ -8367,7 +8367,7 @@
         <v>130</v>
       </c>
       <c r="J154" s="11" t="n">
-        <v>0.6534</v>
+        <v>0.6538</v>
       </c>
       <c r="K154" s="8" t="n">
         <v>30</v>
@@ -8415,7 +8415,7 @@
         <v>747</v>
       </c>
       <c r="J155" s="7" t="n">
-        <v>0.7749</v>
+        <v>0.7751</v>
       </c>
       <c r="K155" s="5" t="n">
         <v>170</v>
@@ -8519,7 +8519,7 @@
         <v>160</v>
       </c>
       <c r="J157" s="11" t="n">
-        <v>0.7995</v>
+        <v>0.8</v>
       </c>
       <c r="K157" s="8" t="n">
         <v>40</v>
@@ -8571,7 +8571,7 @@
         <v>60</v>
       </c>
       <c r="J158" s="11" t="n">
-        <v>0.883</v>
+        <v>0.8833</v>
       </c>
       <c r="K158" s="8" t="n">
         <v>15</v>
@@ -8623,7 +8623,7 @@
         <v>30</v>
       </c>
       <c r="J159" s="11" t="n">
-        <v>0.5664</v>
+        <v>0.5667</v>
       </c>
       <c r="K159" s="8" t="n">
         <v>5</v>
@@ -8727,7 +8727,7 @@
         <v>199</v>
       </c>
       <c r="J161" s="11" t="n">
-        <v>0.6831</v>
+        <v>0.6834</v>
       </c>
       <c r="K161" s="8" t="n">
         <v>40</v>
@@ -8831,7 +8831,7 @@
         <v>38</v>
       </c>
       <c r="J163" s="11" t="n">
-        <v>0.9735</v>
+        <v>0.9737</v>
       </c>
       <c r="K163" s="8" t="n">
         <v>10</v>
@@ -8867,7 +8867,7 @@
         <v>33</v>
       </c>
       <c r="F164" s="6" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="G164" s="5" t="n">
         <v>5</v>
@@ -8879,7 +8879,7 @@
         <v>4126</v>
       </c>
       <c r="J164" s="7" t="n">
-        <v>0.7825</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="K164" s="5" t="n">
         <v>985</v>
@@ -8931,7 +8931,7 @@
         <v>175</v>
       </c>
       <c r="J165" s="11" t="n">
-        <v>0.874</v>
+        <v>0.8743</v>
       </c>
       <c r="K165" s="8" t="n">
         <v>45</v>
@@ -9035,7 +9035,7 @@
         <v>260</v>
       </c>
       <c r="J167" s="11" t="n">
-        <v>0.7842</v>
+        <v>0.7846</v>
       </c>
       <c r="K167" s="8" t="n">
         <v>55</v>
@@ -9087,7 +9087,7 @@
         <v>81</v>
       </c>
       <c r="J168" s="11" t="n">
-        <v>0.7279</v>
+        <v>0.7284</v>
       </c>
       <c r="K168" s="8" t="n">
         <v>20</v>
@@ -9139,7 +9139,7 @@
         <v>160</v>
       </c>
       <c r="J169" s="11" t="n">
-        <v>0.7936</v>
+        <v>0.7937</v>
       </c>
       <c r="K169" s="8" t="n">
         <v>40</v>
@@ -9243,7 +9243,7 @@
         <v>59</v>
       </c>
       <c r="J171" s="11" t="n">
-        <v>0.7285</v>
+        <v>0.7288</v>
       </c>
       <c r="K171" s="8" t="n">
         <v>15</v>
@@ -9295,7 +9295,7 @@
         <v>280</v>
       </c>
       <c r="J172" s="11" t="n">
-        <v>0.771</v>
+        <v>0.7714</v>
       </c>
       <c r="K172" s="8" t="n">
         <v>65</v>
@@ -9347,7 +9347,7 @@
         <v>160</v>
       </c>
       <c r="J173" s="11" t="n">
-        <v>0.8434</v>
+        <v>0.8438</v>
       </c>
       <c r="K173" s="8" t="n">
         <v>40</v>
@@ -9503,7 +9503,7 @@
         <v>60</v>
       </c>
       <c r="J176" s="11" t="n">
-        <v>0.9163</v>
+        <v>0.9167</v>
       </c>
       <c r="K176" s="8" t="n">
         <v>15</v>
@@ -9555,7 +9555,7 @@
         <v>79</v>
       </c>
       <c r="J177" s="11" t="n">
-        <v>0.9489</v>
+        <v>0.9494</v>
       </c>
       <c r="K177" s="8" t="n">
         <v>15</v>
@@ -9711,7 +9711,7 @@
         <v>60</v>
       </c>
       <c r="J180" s="11" t="n">
-        <v>0.8829</v>
+        <v>0.8833</v>
       </c>
       <c r="K180" s="8" t="n">
         <v>15</v>
@@ -9763,7 +9763,7 @@
         <v>180</v>
       </c>
       <c r="J181" s="11" t="n">
-        <v>0.8107</v>
+        <v>0.8111</v>
       </c>
       <c r="K181" s="8" t="n">
         <v>40</v>
@@ -9919,7 +9919,7 @@
         <v>198</v>
       </c>
       <c r="J184" s="11" t="n">
-        <v>0.7621</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="K184" s="8" t="n">
         <v>50</v>
@@ -9971,7 +9971,7 @@
         <v>99</v>
       </c>
       <c r="J185" s="11" t="n">
-        <v>0.8787</v>
+        <v>0.8788</v>
       </c>
       <c r="K185" s="8" t="n">
         <v>20</v>
@@ -10075,7 +10075,7 @@
         <v>41</v>
       </c>
       <c r="J187" s="11" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.8537</v>
       </c>
       <c r="K187" s="8" t="n">
         <v>10</v>
@@ -10127,7 +10127,7 @@
         <v>59</v>
       </c>
       <c r="J188" s="11" t="n">
-        <v>0.6604</v>
+        <v>0.661</v>
       </c>
       <c r="K188" s="8" t="n">
         <v>15</v>
@@ -10179,7 +10179,7 @@
         <v>278</v>
       </c>
       <c r="J189" s="11" t="n">
-        <v>0.7762</v>
+        <v>0.777</v>
       </c>
       <c r="K189" s="8" t="n">
         <v>70</v>
@@ -10231,7 +10231,7 @@
         <v>293</v>
       </c>
       <c r="J190" s="11" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8669</v>
       </c>
       <c r="K190" s="8" t="n">
         <v>70</v>
@@ -10283,7 +10283,7 @@
         <v>416</v>
       </c>
       <c r="J191" s="11" t="n">
-        <v>0.6343</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="K191" s="8" t="n">
         <v>90</v>
@@ -10335,7 +10335,7 @@
         <v>110</v>
       </c>
       <c r="J192" s="11" t="n">
-        <v>0.5907</v>
+        <v>0.5909</v>
       </c>
       <c r="K192" s="8" t="n">
         <v>20</v>
@@ -10387,7 +10387,7 @@
         <v>139</v>
       </c>
       <c r="J193" s="11" t="n">
-        <v>0.7479</v>
+        <v>0.7482</v>
       </c>
       <c r="K193" s="8" t="n">
         <v>40</v>
@@ -10491,7 +10491,7 @@
         <v>120</v>
       </c>
       <c r="J195" s="11" t="n">
-        <v>0.858</v>
+        <v>0.8583</v>
       </c>
       <c r="K195" s="8" t="n">
         <v>30</v>
@@ -10543,7 +10543,7 @@
         <v>99</v>
       </c>
       <c r="J196" s="11" t="n">
-        <v>0.8787</v>
+        <v>0.8788</v>
       </c>
       <c r="K196" s="8" t="n">
         <v>25</v>
@@ -10595,7 +10595,7 @@
         <v>140</v>
       </c>
       <c r="J197" s="11" t="n">
-        <v>0.8354</v>
+        <v>0.8357</v>
       </c>
       <c r="K197" s="8" t="n">
         <v>35</v>
@@ -10643,7 +10643,7 @@
         <v>219</v>
       </c>
       <c r="J198" s="7" t="n">
-        <v>0.9404</v>
+        <v>0.9406</v>
       </c>
       <c r="K198" s="5" t="n">
         <v>55</v>
@@ -10695,7 +10695,7 @@
         <v>139</v>
       </c>
       <c r="J199" s="11" t="n">
-        <v>0.9564</v>
+        <v>0.9568</v>
       </c>
       <c r="K199" s="8" t="n">
         <v>35</v>
@@ -10783,7 +10783,7 @@
         <v>11</v>
       </c>
       <c r="F201" s="6" t="n">
-        <v>13.9</v>
+        <v>13.65</v>
       </c>
       <c r="G201" s="5" t="n">
         <v>6</v>
@@ -10792,10 +10792,10 @@
         <v>18</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>1200</v>
+        <v>1791</v>
       </c>
       <c r="J201" s="7" t="n">
-        <v>0.8599</v>
+        <v>0.8219</v>
       </c>
       <c r="K201" s="5" t="n">
         <v>435</v>
@@ -10847,7 +10847,7 @@
         <v>119</v>
       </c>
       <c r="J202" s="11" t="n">
-        <v>0.9577</v>
+        <v>0.958</v>
       </c>
       <c r="K202" s="8" t="n">
         <v>30</v>
@@ -10951,7 +10951,7 @@
         <v>19</v>
       </c>
       <c r="J204" s="11" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9474</v>
       </c>
       <c r="K204" s="8" t="n">
         <v>5</v>
@@ -11211,7 +11211,7 @@
         <v>141</v>
       </c>
       <c r="J209" s="11" t="n">
-        <v>0.9144</v>
+        <v>0.9149</v>
       </c>
       <c r="K209" s="8" t="n">
         <v>35</v>
@@ -11260,10 +11260,10 @@
         <v>18</v>
       </c>
       <c r="I210" s="8" t="n">
-        <v>100</v>
+        <v>691</v>
       </c>
       <c r="J210" s="11" t="n">
-        <v>0.7431</v>
+        <v>0.7438</v>
       </c>
       <c r="K210" s="8" t="n">
         <v>160</v>
@@ -11315,7 +11315,7 @@
         <v>381</v>
       </c>
       <c r="J211" s="11" t="n">
-        <v>0.8313</v>
+        <v>0.832</v>
       </c>
       <c r="K211" s="8" t="n">
         <v>95</v>
@@ -11503,7 +11503,7 @@
         <v>4</v>
       </c>
       <c r="F215" s="6" t="n">
-        <v>13.85</v>
+        <v>13.76</v>
       </c>
       <c r="G215" s="5" t="n">
         <v>5</v>
@@ -11512,10 +11512,10 @@
         <v>19</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>200</v>
+        <v>1450</v>
       </c>
       <c r="J215" s="7" t="n">
-        <v>0.8192</v>
+        <v>0.8193</v>
       </c>
       <c r="K215" s="5" t="n">
         <v>314</v>
@@ -11567,7 +11567,7 @@
         <v>60</v>
       </c>
       <c r="J216" s="11" t="n">
-        <v>0.7998</v>
+        <v>0.8</v>
       </c>
       <c r="K216" s="8" t="n">
         <v>10</v>
@@ -11668,10 +11668,10 @@
         <v>19</v>
       </c>
       <c r="I218" s="8" t="n">
-        <v>100</v>
+        <v>1350</v>
       </c>
       <c r="J218" s="11" t="n">
-        <v>0.8185</v>
+        <v>0.8193</v>
       </c>
       <c r="K218" s="8" t="n">
         <v>294</v>
@@ -11771,7 +11771,7 @@
         <v>3382</v>
       </c>
       <c r="J220" s="4" t="n">
-        <v>0.837</v>
+        <v>0.8374</v>
       </c>
       <c r="K220" s="2" t="n">
         <v>833</v>
@@ -11819,7 +11819,7 @@
         <v>60</v>
       </c>
       <c r="J221" s="7" t="n">
-        <v>0.7163</v>
+        <v>0.7167</v>
       </c>
       <c r="K221" s="5" t="n">
         <v>15</v>
@@ -11871,7 +11871,7 @@
         <v>60</v>
       </c>
       <c r="J222" s="11" t="n">
-        <v>0.7163</v>
+        <v>0.7167</v>
       </c>
       <c r="K222" s="8" t="n">
         <v>15</v>
@@ -12171,7 +12171,7 @@
         <v>522</v>
       </c>
       <c r="J228" s="7" t="n">
-        <v>0.9076</v>
+        <v>0.908</v>
       </c>
       <c r="K228" s="5" t="n">
         <v>130</v>
@@ -12275,7 +12275,7 @@
         <v>241</v>
       </c>
       <c r="J230" s="11" t="n">
-        <v>0.9411</v>
+        <v>0.9419</v>
       </c>
       <c r="K230" s="8" t="n">
         <v>60</v>
@@ -12327,7 +12327,7 @@
         <v>201</v>
       </c>
       <c r="J231" s="11" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8607</v>
       </c>
       <c r="K231" s="8" t="n">
         <v>50</v>
@@ -12375,7 +12375,7 @@
         <v>608</v>
       </c>
       <c r="J232" s="7" t="n">
-        <v>0.7742</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="K232" s="5" t="n">
         <v>135</v>
@@ -12427,7 +12427,7 @@
         <v>45</v>
       </c>
       <c r="J233" s="11" t="n">
-        <v>0.533</v>
+        <v>0.5333</v>
       </c>
       <c r="K233" s="8" t="n">
         <v>5</v>
@@ -12583,7 +12583,7 @@
         <v>140</v>
       </c>
       <c r="J236" s="11" t="n">
-        <v>0.4212</v>
+        <v>0.4214</v>
       </c>
       <c r="K236" s="8" t="n">
         <v>25</v>
@@ -12635,7 +12635,7 @@
         <v>209</v>
       </c>
       <c r="J237" s="11" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.9426</v>
       </c>
       <c r="K237" s="8" t="n">
         <v>50</v>
@@ -12687,7 +12687,7 @@
         <v>174</v>
       </c>
       <c r="J238" s="11" t="n">
-        <v>0.8673</v>
+        <v>0.8678</v>
       </c>
       <c r="K238" s="8" t="n">
         <v>45</v>
@@ -12735,7 +12735,7 @@
         <v>703</v>
       </c>
       <c r="J239" s="7" t="n">
-        <v>0.8942</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K239" s="5" t="n">
         <v>160</v>
@@ -12775,7 +12775,7 @@
         <v>1</v>
       </c>
       <c r="F240" s="10" t="n">
-        <v>13.85</v>
+        <v>13.84</v>
       </c>
       <c r="G240" s="8" t="n">
         <v>5</v>
@@ -12787,7 +12787,7 @@
         <v>241</v>
       </c>
       <c r="J240" s="11" t="n">
-        <v>0.8376</v>
+        <v>0.8381999999999999</v>
       </c>
       <c r="K240" s="8" t="n">
         <v>55</v>
@@ -12839,7 +12839,7 @@
         <v>290</v>
       </c>
       <c r="J241" s="11" t="n">
-        <v>0.9510999999999999</v>
+        <v>0.9517</v>
       </c>
       <c r="K241" s="8" t="n">
         <v>70</v>
@@ -12989,7 +12989,7 @@
         <v>132</v>
       </c>
       <c r="J244" s="11" t="n">
-        <v>0.8557</v>
+        <v>0.8561</v>
       </c>
       <c r="K244" s="8" t="n">
         <v>30</v>
@@ -13037,7 +13037,7 @@
         <v>439</v>
       </c>
       <c r="J245" s="7" t="n">
-        <v>0.7539</v>
+        <v>0.754</v>
       </c>
       <c r="K245" s="5" t="n">
         <v>134</v>
@@ -13089,7 +13089,7 @@
         <v>60</v>
       </c>
       <c r="J246" s="11" t="n">
-        <v>0.7166</v>
+        <v>0.7167</v>
       </c>
       <c r="K246" s="8" t="n">
         <v>39</v>
@@ -13141,7 +13141,7 @@
         <v>79</v>
       </c>
       <c r="J247" s="11" t="n">
-        <v>0.7593</v>
+        <v>0.7595</v>
       </c>
       <c r="K247" s="8" t="n">
         <v>20</v>
@@ -13193,7 +13193,7 @@
         <v>160</v>
       </c>
       <c r="J248" s="11" t="n">
-        <v>0.7499</v>
+        <v>0.75</v>
       </c>
       <c r="K248" s="8" t="n">
         <v>40</v>
@@ -13345,7 +13345,7 @@
         <v>460</v>
       </c>
       <c r="J251" s="7" t="n">
-        <v>0.8451</v>
+        <v>0.8457</v>
       </c>
       <c r="K251" s="5" t="n">
         <v>120</v>
@@ -13397,7 +13397,7 @@
         <v>340</v>
       </c>
       <c r="J252" s="11" t="n">
-        <v>0.8406</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="K252" s="8" t="n">
         <v>90</v>
@@ -13449,7 +13449,7 @@
         <v>120</v>
       </c>
       <c r="J253" s="11" t="n">
-        <v>0.858</v>
+        <v>0.8583</v>
       </c>
       <c r="K253" s="8" t="n">
         <v>30</v>
@@ -13497,7 +13497,7 @@
         <v>430</v>
       </c>
       <c r="J254" s="7" t="n">
-        <v>0.8065</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="K254" s="5" t="n">
         <v>99</v>
@@ -13549,7 +13549,7 @@
         <v>330</v>
       </c>
       <c r="J255" s="11" t="n">
-        <v>0.8055</v>
+        <v>0.8061</v>
       </c>
       <c r="K255" s="8" t="n">
         <v>79</v>
@@ -13753,7 +13753,7 @@
         <v>7405</v>
       </c>
       <c r="J259" s="4" t="n">
-        <v>0.9396</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K259" s="2" t="n">
         <v>3694</v>
@@ -13901,7 +13901,7 @@
         <v>1842</v>
       </c>
       <c r="J262" s="7" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9555</v>
       </c>
       <c r="K262" s="5" t="n">
         <v>914</v>
@@ -14045,7 +14045,7 @@
         <v>1</v>
       </c>
       <c r="F265" s="10" t="n">
-        <v>14.63</v>
+        <v>14.62</v>
       </c>
       <c r="G265" s="8" t="n">
         <v>10</v>
@@ -14057,7 +14057,7 @@
         <v>52</v>
       </c>
       <c r="J265" s="11" t="n">
-        <v>0.9804</v>
+        <v>0.9808</v>
       </c>
       <c r="K265" s="8" t="n">
         <v>24</v>
@@ -14109,7 +14109,7 @@
         <v>69</v>
       </c>
       <c r="J266" s="11" t="n">
-        <v>0.9704</v>
+        <v>0.971</v>
       </c>
       <c r="K266" s="8" t="n">
         <v>35</v>
@@ -14161,7 +14161,7 @@
         <v>120</v>
       </c>
       <c r="J267" s="11" t="n">
-        <v>0.983</v>
+        <v>0.9833</v>
       </c>
       <c r="K267" s="8" t="n">
         <v>60</v>
@@ -14213,7 +14213,7 @@
         <v>70</v>
       </c>
       <c r="J268" s="11" t="n">
-        <v>0.8851</v>
+        <v>0.8857</v>
       </c>
       <c r="K268" s="8" t="n">
         <v>35</v>
@@ -14265,7 +14265,7 @@
         <v>369</v>
       </c>
       <c r="J269" s="11" t="n">
-        <v>0.9858</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="K269" s="8" t="n">
         <v>185</v>
@@ -14369,7 +14369,7 @@
         <v>110</v>
       </c>
       <c r="J271" s="11" t="n">
-        <v>0.9902</v>
+        <v>0.9909</v>
       </c>
       <c r="K271" s="8" t="n">
         <v>55</v>
@@ -14421,7 +14421,7 @@
         <v>110</v>
       </c>
       <c r="J272" s="11" t="n">
-        <v>0.9719</v>
+        <v>0.9727</v>
       </c>
       <c r="K272" s="8" t="n">
         <v>55</v>
@@ -14473,7 +14473,7 @@
         <v>90</v>
       </c>
       <c r="J273" s="11" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9333</v>
       </c>
       <c r="K273" s="8" t="n">
         <v>50</v>
@@ -14525,7 +14525,7 @@
         <v>60</v>
       </c>
       <c r="J274" s="11" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="K274" s="8" t="n">
         <v>30</v>
@@ -14577,7 +14577,7 @@
         <v>121</v>
       </c>
       <c r="J275" s="11" t="n">
-        <v>0.8921</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="K275" s="8" t="n">
         <v>60</v>
@@ -14889,7 +14889,7 @@
         <v>119</v>
       </c>
       <c r="J281" s="11" t="n">
-        <v>0.9577</v>
+        <v>0.958</v>
       </c>
       <c r="K281" s="8" t="n">
         <v>55</v>
@@ -14941,7 +14941,7 @@
         <v>70</v>
       </c>
       <c r="J282" s="11" t="n">
-        <v>0.9709</v>
+        <v>0.9714</v>
       </c>
       <c r="K282" s="8" t="n">
         <v>35</v>
@@ -14993,7 +14993,7 @@
         <v>51</v>
       </c>
       <c r="J283" s="11" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="K283" s="8" t="n">
         <v>25</v>
@@ -15045,7 +15045,7 @@
         <v>30</v>
       </c>
       <c r="J284" s="11" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="K284" s="8" t="n">
         <v>15</v>
@@ -15149,7 +15149,7 @@
         <v>61</v>
       </c>
       <c r="J286" s="11" t="n">
-        <v>0.9503</v>
+        <v>0.9508</v>
       </c>
       <c r="K286" s="8" t="n">
         <v>30</v>
@@ -15197,7 +15197,7 @@
         <v>660</v>
       </c>
       <c r="J287" s="7" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8697</v>
       </c>
       <c r="K287" s="5" t="n">
         <v>343</v>
@@ -15249,7 +15249,7 @@
         <v>11</v>
       </c>
       <c r="J288" s="11" t="n">
-        <v>0.909</v>
+        <v>0.9091</v>
       </c>
       <c r="K288" s="8" t="n">
         <v>5</v>
@@ -15353,7 +15353,7 @@
         <v>120</v>
       </c>
       <c r="J290" s="11" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9333</v>
       </c>
       <c r="K290" s="8" t="n">
         <v>65</v>
@@ -15405,7 +15405,7 @@
         <v>70</v>
       </c>
       <c r="J291" s="11" t="n">
-        <v>0.9566</v>
+        <v>0.9571</v>
       </c>
       <c r="K291" s="8" t="n">
         <v>35</v>
@@ -15509,7 +15509,7 @@
         <v>199</v>
       </c>
       <c r="J293" s="11" t="n">
-        <v>0.8137</v>
+        <v>0.8141</v>
       </c>
       <c r="K293" s="8" t="n">
         <v>108</v>
@@ -15609,7 +15609,7 @@
         <v>1409</v>
       </c>
       <c r="J295" s="7" t="n">
-        <v>0.9081</v>
+        <v>0.9084</v>
       </c>
       <c r="K295" s="5" t="n">
         <v>697</v>
@@ -15661,7 +15661,7 @@
         <v>90</v>
       </c>
       <c r="J296" s="11" t="n">
-        <v>0.8774</v>
+        <v>0.8778</v>
       </c>
       <c r="K296" s="8" t="n">
         <v>50</v>
@@ -15713,7 +15713,7 @@
         <v>30</v>
       </c>
       <c r="J297" s="11" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="K297" s="8" t="n">
         <v>20</v>
@@ -15817,7 +15817,7 @@
         <v>19</v>
       </c>
       <c r="J299" s="11" t="n">
-        <v>0.6314</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="K299" s="8" t="n">
         <v>5</v>
@@ -15869,7 +15869,7 @@
         <v>101</v>
       </c>
       <c r="J300" s="11" t="n">
-        <v>0.6435</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="K300" s="8" t="n">
         <v>45</v>
@@ -15973,7 +15973,7 @@
         <v>130</v>
       </c>
       <c r="J302" s="11" t="n">
-        <v>0.8534</v>
+        <v>0.8538</v>
       </c>
       <c r="K302" s="8" t="n">
         <v>65</v>
@@ -16065,7 +16065,7 @@
         <v>1</v>
       </c>
       <c r="F304" s="10" t="n">
-        <v>14.96</v>
+        <v>14.95</v>
       </c>
       <c r="G304" s="8" t="n">
         <v>10</v>
@@ -16077,7 +16077,7 @@
         <v>310</v>
       </c>
       <c r="J304" s="11" t="n">
-        <v>0.9802</v>
+        <v>0.9806</v>
       </c>
       <c r="K304" s="8" t="n">
         <v>150</v>
@@ -16233,7 +16233,7 @@
         <v>110</v>
       </c>
       <c r="J307" s="11" t="n">
-        <v>0.9176</v>
+        <v>0.9182</v>
       </c>
       <c r="K307" s="8" t="n">
         <v>60</v>
@@ -16285,7 +16285,7 @@
         <v>210</v>
       </c>
       <c r="J308" s="11" t="n">
-        <v>0.9757</v>
+        <v>0.9762</v>
       </c>
       <c r="K308" s="8" t="n">
         <v>98</v>
@@ -16337,7 +16337,7 @@
         <v>79</v>
       </c>
       <c r="J309" s="11" t="n">
-        <v>0.9488</v>
+        <v>0.9494</v>
       </c>
       <c r="K309" s="8" t="n">
         <v>40</v>
@@ -16389,7 +16389,7 @@
         <v>110</v>
       </c>
       <c r="J310" s="11" t="n">
-        <v>0.9631999999999999</v>
+        <v>0.9636</v>
       </c>
       <c r="K310" s="8" t="n">
         <v>54</v>
@@ -16489,7 +16489,7 @@
         <v>1475</v>
       </c>
       <c r="J312" s="7" t="n">
-        <v>0.9772</v>
+        <v>0.9776</v>
       </c>
       <c r="K312" s="5" t="n">
         <v>735</v>
@@ -16749,7 +16749,7 @@
         <v>81</v>
       </c>
       <c r="J317" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9506</v>
       </c>
       <c r="K317" s="8" t="n">
         <v>40</v>
@@ -16801,7 +16801,7 @@
         <v>81</v>
       </c>
       <c r="J318" s="11" t="n">
-        <v>0.9502</v>
+        <v>0.9506</v>
       </c>
       <c r="K318" s="8" t="n">
         <v>40</v>
@@ -16853,7 +16853,7 @@
         <v>141</v>
       </c>
       <c r="J319" s="11" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9929</v>
       </c>
       <c r="K319" s="8" t="n">
         <v>70</v>
@@ -16905,7 +16905,7 @@
         <v>499</v>
       </c>
       <c r="J320" s="11" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9719</v>
       </c>
       <c r="K320" s="8" t="n">
         <v>250</v>
@@ -17009,7 +17009,7 @@
         <v>70</v>
       </c>
       <c r="J322" s="11" t="n">
-        <v>0.9566</v>
+        <v>0.9571</v>
       </c>
       <c r="K322" s="8" t="n">
         <v>35</v>
@@ -17113,7 +17113,7 @@
         <v>30</v>
       </c>
       <c r="J324" s="11" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="K324" s="8" t="n">
         <v>15</v>
@@ -17165,7 +17165,7 @@
         <v>18</v>
       </c>
       <c r="J325" s="11" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="K325" s="8" t="n">
         <v>10</v>
@@ -17373,7 +17373,7 @@
         <v>30</v>
       </c>
       <c r="J329" s="11" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="K329" s="8" t="n">
         <v>15</v>
@@ -17477,7 +17477,7 @@
         <v>30</v>
       </c>
       <c r="J331" s="11" t="n">
-        <v>0.9664</v>
+        <v>0.9667</v>
       </c>
       <c r="K331" s="8" t="n">
         <v>10</v>
@@ -17737,7 +17737,7 @@
         <v>60</v>
       </c>
       <c r="J336" s="11" t="n">
-        <v>0.983</v>
+        <v>0.9833</v>
       </c>
       <c r="K336" s="8" t="n">
         <v>30</v>
@@ -17789,7 +17789,7 @@
         <v>30</v>
       </c>
       <c r="J337" s="11" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="K337" s="8" t="n">
         <v>15</v>
@@ -17841,7 +17841,7 @@
         <v>30</v>
       </c>
       <c r="J338" s="11" t="n">
-        <v>0.9664</v>
+        <v>0.9667</v>
       </c>
       <c r="K338" s="8" t="n">
         <v>15</v>
@@ -17945,7 +17945,7 @@
         <v>30</v>
       </c>
       <c r="J340" s="11" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="K340" s="8" t="n">
         <v>15</v>
@@ -17993,7 +17993,7 @@
         <v>411</v>
       </c>
       <c r="J341" s="7" t="n">
-        <v>0.8731</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="K341" s="5" t="n">
         <v>205</v>
@@ -18045,7 +18045,7 @@
         <v>161</v>
       </c>
       <c r="J342" s="11" t="n">
-        <v>0.745</v>
+        <v>0.7453</v>
       </c>
       <c r="K342" s="8" t="n">
         <v>80</v>
@@ -18149,7 +18149,7 @@
         <v>60</v>
       </c>
       <c r="J344" s="11" t="n">
-        <v>0.9663</v>
+        <v>0.9667</v>
       </c>
       <c r="K344" s="8" t="n">
         <v>30</v>
@@ -18201,7 +18201,7 @@
         <v>150</v>
       </c>
       <c r="J345" s="11" t="n">
-        <v>0.9661</v>
+        <v>0.9667</v>
       </c>
       <c r="K345" s="8" t="n">
         <v>75</v>
@@ -18353,7 +18353,7 @@
         <v>1529</v>
       </c>
       <c r="J348" s="7" t="n">
-        <v>0.959</v>
+        <v>0.9595</v>
       </c>
       <c r="K348" s="5" t="n">
         <v>760</v>
@@ -18497,7 +18497,7 @@
         <v>1</v>
       </c>
       <c r="F351" s="10" t="n">
-        <v>14.55</v>
+        <v>14.54</v>
       </c>
       <c r="G351" s="8" t="n">
         <v>7</v>
@@ -18509,7 +18509,7 @@
         <v>182</v>
       </c>
       <c r="J351" s="11" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9176</v>
       </c>
       <c r="K351" s="8" t="n">
         <v>85</v>
@@ -18613,7 +18613,7 @@
         <v>387</v>
       </c>
       <c r="J353" s="11" t="n">
-        <v>0.9606</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="K353" s="8" t="n">
         <v>199</v>
@@ -18665,7 +18665,7 @@
         <v>70</v>
       </c>
       <c r="J354" s="11" t="n">
-        <v>0.9994</v>
+        <v>1</v>
       </c>
       <c r="K354" s="8" t="n">
         <v>35</v>
@@ -18769,7 +18769,7 @@
         <v>59</v>
       </c>
       <c r="J356" s="11" t="n">
-        <v>0.9992</v>
+        <v>1</v>
       </c>
       <c r="K356" s="8" t="n">
         <v>30</v>
@@ -18821,7 +18821,7 @@
         <v>81</v>
       </c>
       <c r="J357" s="11" t="n">
-        <v>0.9377</v>
+        <v>0.9383</v>
       </c>
       <c r="K357" s="8" t="n">
         <v>35</v>
@@ -18873,7 +18873,7 @@
         <v>60</v>
       </c>
       <c r="J358" s="11" t="n">
-        <v>0.9497</v>
+        <v>0.95</v>
       </c>
       <c r="K358" s="8" t="n">
         <v>30</v>
@@ -19029,7 +19029,7 @@
         <v>60</v>
       </c>
       <c r="J361" s="11" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="K361" s="8" t="n">
         <v>30</v>
@@ -19081,7 +19081,7 @@
         <v>30</v>
       </c>
       <c r="J362" s="11" t="n">
-        <v>0.9665</v>
+        <v>0.9667</v>
       </c>
       <c r="K362" s="8" t="n">
         <v>15</v>
@@ -19237,7 +19237,7 @@
         <v>81</v>
       </c>
       <c r="J365" s="11" t="n">
-        <v>0.9131</v>
+        <v>0.9136</v>
       </c>
       <c r="K365" s="8" t="n">
         <v>40</v>
@@ -19289,7 +19289,7 @@
         <v>59</v>
       </c>
       <c r="J366" s="11" t="n">
-        <v>0.9993</v>
+        <v>1</v>
       </c>
       <c r="K366" s="8" t="n">
         <v>30</v>
@@ -19341,7 +19341,7 @@
         <v>70</v>
       </c>
       <c r="J367" s="11" t="n">
-        <v>0.9849</v>
+        <v>0.9857</v>
       </c>
       <c r="K367" s="8" t="n">
         <v>35</v>
@@ -19389,7 +19389,7 @@
         <v>69</v>
       </c>
       <c r="J368" s="7" t="n">
-        <v>0.9994</v>
+        <v>1</v>
       </c>
       <c r="K368" s="5" t="n">
         <v>35</v>
@@ -19441,7 +19441,7 @@
         <v>69</v>
       </c>
       <c r="J369" s="11" t="n">
-        <v>0.9994</v>
+        <v>1</v>
       </c>
       <c r="K369" s="8" t="n">
         <v>35</v>
@@ -19489,7 +19489,7 @@
         <v>4559</v>
       </c>
       <c r="J370" s="4" t="n">
-        <v>0.8364</v>
+        <v>0.8368</v>
       </c>
       <c r="K370" s="2" t="n">
         <v>2268</v>
@@ -19637,7 +19637,7 @@
         <v>240</v>
       </c>
       <c r="J373" s="7" t="n">
-        <v>0.9162</v>
+        <v>0.9167</v>
       </c>
       <c r="K373" s="5" t="n">
         <v>125</v>
@@ -19729,7 +19729,7 @@
         <v>1</v>
       </c>
       <c r="F375" s="10" t="n">
-        <v>14.85</v>
+        <v>14.84</v>
       </c>
       <c r="G375" s="8" t="n">
         <v>9</v>
@@ -19741,7 +19741,7 @@
         <v>190</v>
       </c>
       <c r="J375" s="11" t="n">
-        <v>0.931</v>
+        <v>0.9316</v>
       </c>
       <c r="K375" s="8" t="n">
         <v>100</v>
@@ -19789,7 +19789,7 @@
         <v>89</v>
       </c>
       <c r="J376" s="7" t="n">
-        <v>0.9095</v>
+        <v>0.9101</v>
       </c>
       <c r="K376" s="5" t="n">
         <v>45</v>
@@ -19841,7 +19841,7 @@
         <v>89</v>
       </c>
       <c r="J377" s="11" t="n">
-        <v>0.9095</v>
+        <v>0.9101</v>
       </c>
       <c r="K377" s="8" t="n">
         <v>45</v>
@@ -19889,7 +19889,7 @@
         <v>1314</v>
       </c>
       <c r="J378" s="7" t="n">
-        <v>0.8405</v>
+        <v>0.8409</v>
       </c>
       <c r="K378" s="5" t="n">
         <v>645</v>
@@ -19941,7 +19941,7 @@
         <v>99</v>
       </c>
       <c r="J379" s="11" t="n">
-        <v>0.8686</v>
+        <v>0.8687</v>
       </c>
       <c r="K379" s="8" t="n">
         <v>50</v>
@@ -19993,7 +19993,7 @@
         <v>30</v>
       </c>
       <c r="J380" s="11" t="n">
-        <v>0.7998</v>
+        <v>0.8</v>
       </c>
       <c r="K380" s="8" t="n">
         <v>15</v>
@@ -20045,7 +20045,7 @@
         <v>162</v>
       </c>
       <c r="J381" s="11" t="n">
-        <v>0.839</v>
+        <v>0.8395</v>
       </c>
       <c r="K381" s="8" t="n">
         <v>75</v>
@@ -20097,7 +20097,7 @@
         <v>192</v>
       </c>
       <c r="J382" s="11" t="n">
-        <v>0.8121</v>
+        <v>0.8125</v>
       </c>
       <c r="K382" s="8" t="n">
         <v>90</v>
@@ -20149,7 +20149,7 @@
         <v>270</v>
       </c>
       <c r="J383" s="11" t="n">
-        <v>0.8478</v>
+        <v>0.8481</v>
       </c>
       <c r="K383" s="8" t="n">
         <v>135</v>
@@ -20201,7 +20201,7 @@
         <v>364</v>
       </c>
       <c r="J384" s="11" t="n">
-        <v>0.8921</v>
+        <v>0.8929</v>
       </c>
       <c r="K384" s="8" t="n">
         <v>180</v>
@@ -20253,7 +20253,7 @@
         <v>119</v>
       </c>
       <c r="J385" s="11" t="n">
-        <v>0.8568</v>
+        <v>0.8571</v>
       </c>
       <c r="K385" s="8" t="n">
         <v>65</v>
@@ -20305,7 +20305,7 @@
         <v>78</v>
       </c>
       <c r="J386" s="11" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.6026</v>
       </c>
       <c r="K386" s="8" t="n">
         <v>35</v>
@@ -20453,7 +20453,7 @@
         <v>140</v>
       </c>
       <c r="J389" s="7" t="n">
-        <v>0.8998</v>
+        <v>0.9</v>
       </c>
       <c r="K389" s="5" t="n">
         <v>69</v>
@@ -20713,7 +20713,7 @@
         <v>60</v>
       </c>
       <c r="J394" s="11" t="n">
-        <v>0.9495</v>
+        <v>0.95</v>
       </c>
       <c r="K394" s="8" t="n">
         <v>30</v>
@@ -20761,7 +20761,7 @@
         <v>612</v>
       </c>
       <c r="J395" s="7" t="n">
-        <v>0.8331</v>
+        <v>0.8333</v>
       </c>
       <c r="K395" s="5" t="n">
         <v>305</v>
@@ -20917,7 +20917,7 @@
         <v>152</v>
       </c>
       <c r="J398" s="11" t="n">
-        <v>0.835</v>
+        <v>0.8355</v>
       </c>
       <c r="K398" s="8" t="n">
         <v>80</v>
@@ -21113,7 +21113,7 @@
         <v>1</v>
       </c>
       <c r="F402" s="10" t="n">
-        <v>13.63</v>
+        <v>13.62</v>
       </c>
       <c r="G402" s="8" t="n">
         <v>8</v>
@@ -21125,7 +21125,7 @@
         <v>180</v>
       </c>
       <c r="J402" s="11" t="n">
-        <v>0.8607</v>
+        <v>0.8611</v>
       </c>
       <c r="K402" s="8" t="n">
         <v>90</v>
@@ -21277,7 +21277,7 @@
         <v>240</v>
       </c>
       <c r="J405" s="7" t="n">
-        <v>0.9789</v>
+        <v>0.9792</v>
       </c>
       <c r="K405" s="5" t="n">
         <v>120</v>
@@ -21329,7 +21329,7 @@
         <v>11</v>
       </c>
       <c r="J406" s="11" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="K406" s="8" t="n">
         <v>5</v>
@@ -21485,7 +21485,7 @@
         <v>30</v>
       </c>
       <c r="J409" s="11" t="n">
-        <v>0.9663</v>
+        <v>0.9667</v>
       </c>
       <c r="K409" s="8" t="n">
         <v>15</v>
@@ -21589,7 +21589,7 @@
         <v>59</v>
       </c>
       <c r="J411" s="11" t="n">
-        <v>0.9993</v>
+        <v>1</v>
       </c>
       <c r="K411" s="8" t="n">
         <v>30</v>
@@ -21641,7 +21641,7 @@
         <v>60</v>
       </c>
       <c r="J412" s="11" t="n">
-        <v>0.9831</v>
+        <v>0.9833</v>
       </c>
       <c r="K412" s="8" t="n">
         <v>30</v>
@@ -21689,7 +21689,7 @@
         <v>1163</v>
       </c>
       <c r="J413" s="7" t="n">
-        <v>0.7813</v>
+        <v>0.7816</v>
       </c>
       <c r="K413" s="5" t="n">
         <v>598</v>
@@ -21741,7 +21741,7 @@
         <v>49</v>
       </c>
       <c r="J414" s="11" t="n">
-        <v>0.7548</v>
+        <v>0.7551</v>
       </c>
       <c r="K414" s="8" t="n">
         <v>25</v>
@@ -21793,7 +21793,7 @@
         <v>60</v>
       </c>
       <c r="J415" s="11" t="n">
-        <v>0.6329</v>
+        <v>0.6333</v>
       </c>
       <c r="K415" s="8" t="n">
         <v>25</v>
@@ -21949,7 +21949,7 @@
         <v>139</v>
       </c>
       <c r="J418" s="11" t="n">
-        <v>0.6903</v>
+        <v>0.6906</v>
       </c>
       <c r="K418" s="8" t="n">
         <v>65</v>
@@ -22001,7 +22001,7 @@
         <v>120</v>
       </c>
       <c r="J419" s="11" t="n">
-        <v>0.7329</v>
+        <v>0.7333</v>
       </c>
       <c r="K419" s="8" t="n">
         <v>64</v>
@@ -22053,7 +22053,7 @@
         <v>19</v>
       </c>
       <c r="J420" s="11" t="n">
-        <v>0.8945</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="K420" s="8" t="n">
         <v>10</v>
@@ -22209,7 +22209,7 @@
         <v>120</v>
       </c>
       <c r="J423" s="11" t="n">
-        <v>0.8915999999999999</v>
+        <v>0.8917</v>
       </c>
       <c r="K423" s="8" t="n">
         <v>65</v>
@@ -22313,7 +22313,7 @@
         <v>59</v>
       </c>
       <c r="J425" s="11" t="n">
-        <v>0.6606</v>
+        <v>0.661</v>
       </c>
       <c r="K425" s="8" t="n">
         <v>25</v>
@@ -22365,7 +22365,7 @@
         <v>119</v>
       </c>
       <c r="J426" s="11" t="n">
-        <v>0.8905</v>
+        <v>0.8908</v>
       </c>
       <c r="K426" s="8" t="n">
         <v>60</v>
@@ -22417,7 +22417,7 @@
         <v>30</v>
       </c>
       <c r="J427" s="11" t="n">
-        <v>0.8996</v>
+        <v>0.9</v>
       </c>
       <c r="K427" s="8" t="n">
         <v>20</v>
@@ -22469,7 +22469,7 @@
         <v>91</v>
       </c>
       <c r="J428" s="11" t="n">
-        <v>0.8238</v>
+        <v>0.8242</v>
       </c>
       <c r="K428" s="8" t="n">
         <v>45</v>
@@ -22521,7 +22521,7 @@
         <v>117</v>
       </c>
       <c r="J429" s="11" t="n">
-        <v>0.8371</v>
+        <v>0.8376</v>
       </c>
       <c r="K429" s="8" t="n">
         <v>69</v>
@@ -22569,7 +22569,7 @@
         <v>430</v>
       </c>
       <c r="J430" s="7" t="n">
-        <v>0.8343</v>
+        <v>0.8349</v>
       </c>
       <c r="K430" s="5" t="n">
         <v>201</v>
@@ -22621,7 +22621,7 @@
         <v>190</v>
       </c>
       <c r="J431" s="11" t="n">
-        <v>0.7995</v>
+        <v>0.8</v>
       </c>
       <c r="K431" s="8" t="n">
         <v>90</v>
@@ -22673,7 +22673,7 @@
         <v>230</v>
       </c>
       <c r="J432" s="11" t="n">
-        <v>0.8732</v>
+        <v>0.8739</v>
       </c>
       <c r="K432" s="8" t="n">
         <v>106</v>
@@ -22773,7 +22773,7 @@
         <v>49</v>
       </c>
       <c r="J434" s="7" t="n">
-        <v>0.8976</v>
+        <v>0.898</v>
       </c>
       <c r="K434" s="5" t="n">
         <v>35</v>
@@ -22825,7 +22825,7 @@
         <v>49</v>
       </c>
       <c r="J435" s="11" t="n">
-        <v>0.8976</v>
+        <v>0.898</v>
       </c>
       <c r="K435" s="8" t="n">
         <v>35</v>
@@ -22861,7 +22861,7 @@
         <v>2</v>
       </c>
       <c r="F436" s="6" t="n">
-        <v>12.81</v>
+        <v>12.8</v>
       </c>
       <c r="G436" s="5" t="n">
         <v>8</v>
@@ -22873,7 +22873,7 @@
         <v>100</v>
       </c>
       <c r="J436" s="7" t="n">
-        <v>0.7296</v>
+        <v>0.73</v>
       </c>
       <c r="K436" s="5" t="n">
         <v>50</v>
@@ -22977,7 +22977,7 @@
         <v>90</v>
       </c>
       <c r="J438" s="11" t="n">
-        <v>0.6996</v>
+        <v>0.7</v>
       </c>
       <c r="K438" s="8" t="n">
         <v>45</v>
@@ -23025,7 +23025,7 @@
         <v>51</v>
       </c>
       <c r="J439" s="7" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7647</v>
       </c>
       <c r="K439" s="5" t="n">
         <v>20</v>
@@ -23129,7 +23129,7 @@
         <v>21</v>
       </c>
       <c r="J441" s="11" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.7619</v>
       </c>
       <c r="K441" s="8" t="n">
         <v>5</v>
@@ -23301,7 +23301,7 @@
         <v>30</v>
       </c>
       <c r="J445" s="7" t="n">
-        <v>0.7664</v>
+        <v>0.7667</v>
       </c>
       <c r="K445" s="5" t="n">
         <v>10</v>
@@ -23353,7 +23353,7 @@
         <v>30</v>
       </c>
       <c r="J446" s="11" t="n">
-        <v>0.7664</v>
+        <v>0.7667</v>
       </c>
       <c r="K446" s="8" t="n">
         <v>10</v>
@@ -23437,7 +23437,7 @@
         <v>41</v>
       </c>
       <c r="J448" s="7" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="K448" s="5" t="n">
         <v>15</v>
@@ -23489,7 +23489,7 @@
         <v>41</v>
       </c>
       <c r="J449" s="11" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="K449" s="8" t="n">
         <v>15</v>
@@ -23673,7 +23673,7 @@
         <v>958</v>
       </c>
       <c r="J453" s="4" t="n">
-        <v>0.9516</v>
+        <v>0.952</v>
       </c>
       <c r="K453" s="2" t="n">
         <v>495</v>
@@ -23873,7 +23873,7 @@
         <v>149</v>
       </c>
       <c r="J457" s="7" t="n">
-        <v>0.9796</v>
+        <v>0.9799</v>
       </c>
       <c r="K457" s="5" t="n">
         <v>85</v>
@@ -24185,7 +24185,7 @@
         <v>60</v>
       </c>
       <c r="J463" s="11" t="n">
-        <v>0.9828</v>
+        <v>0.9833</v>
       </c>
       <c r="K463" s="8" t="n">
         <v>35</v>
@@ -24393,7 +24393,7 @@
         <v>9</v>
       </c>
       <c r="J467" s="11" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="K467" s="8" t="n">
         <v>5</v>
@@ -24441,7 +24441,7 @@
         <v>439</v>
       </c>
       <c r="J468" s="7" t="n">
-        <v>0.9678</v>
+        <v>0.9681</v>
       </c>
       <c r="K468" s="5" t="n">
         <v>225</v>
@@ -24493,7 +24493,7 @@
         <v>30</v>
       </c>
       <c r="J469" s="11" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="K469" s="8" t="n">
         <v>15</v>
@@ -24545,7 +24545,7 @@
         <v>9</v>
       </c>
       <c r="J470" s="11" t="n">
-        <v>0.8888</v>
+        <v>0.8889</v>
       </c>
       <c r="K470" s="8" t="n">
         <v>5</v>
@@ -24649,7 +24649,7 @@
         <v>30</v>
       </c>
       <c r="J472" s="11" t="n">
-        <v>0.9332</v>
+        <v>0.9333</v>
       </c>
       <c r="K472" s="8" t="n">
         <v>15</v>
@@ -24701,7 +24701,7 @@
         <v>70</v>
       </c>
       <c r="J473" s="11" t="n">
-        <v>0.9135</v>
+        <v>0.9143</v>
       </c>
       <c r="K473" s="8" t="n">
         <v>35</v>
@@ -24909,7 +24909,7 @@
         <v>90</v>
       </c>
       <c r="J477" s="11" t="n">
-        <v>0.9661</v>
+        <v>0.9667</v>
       </c>
       <c r="K477" s="8" t="n">
         <v>45</v>
@@ -25013,7 +25013,7 @@
         <v>30</v>
       </c>
       <c r="J479" s="11" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="K479" s="8" t="n">
         <v>15</v>
@@ -25065,7 +25065,7 @@
         <v>30</v>
       </c>
       <c r="J480" s="11" t="n">
-        <v>0.9998</v>
+        <v>1</v>
       </c>
       <c r="K480" s="8" t="n">
         <v>15</v>
@@ -25113,7 +25113,7 @@
         <v>160</v>
       </c>
       <c r="J481" s="7" t="n">
-        <v>0.9059</v>
+        <v>0.9062</v>
       </c>
       <c r="K481" s="5" t="n">
         <v>80</v>
@@ -25165,7 +25165,7 @@
         <v>30</v>
       </c>
       <c r="J482" s="11" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="K482" s="8" t="n">
         <v>15</v>
@@ -25217,7 +25217,7 @@
         <v>130</v>
       </c>
       <c r="J483" s="11" t="n">
-        <v>0.8842</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="K483" s="8" t="n">
         <v>65</v>
@@ -25365,7 +25365,7 @@
         <v>30</v>
       </c>
       <c r="J486" s="7" t="n">
-        <v>0.833</v>
+        <v>0.8333</v>
       </c>
       <c r="K486" s="5" t="n">
         <v>15</v>
@@ -25417,7 +25417,7 @@
         <v>30</v>
       </c>
       <c r="J487" s="11" t="n">
-        <v>0.833</v>
+        <v>0.8333</v>
       </c>
       <c r="K487" s="8" t="n">
         <v>15</v>
@@ -25465,7 +25465,7 @@
         <v>110</v>
       </c>
       <c r="J488" s="7" t="n">
-        <v>0.9537</v>
+        <v>0.9545</v>
       </c>
       <c r="K488" s="5" t="n">
         <v>55</v>
@@ -25517,7 +25517,7 @@
         <v>110</v>
       </c>
       <c r="J489" s="11" t="n">
-        <v>0.9537</v>
+        <v>0.9545</v>
       </c>
       <c r="K489" s="8" t="n">
         <v>55</v>
@@ -25565,7 +25565,7 @@
         <v>473</v>
       </c>
       <c r="J490" s="4" t="n">
-        <v>0.9532</v>
+        <v>0.9535</v>
       </c>
       <c r="K490" s="2" t="n">
         <v>245</v>
@@ -25813,7 +25813,7 @@
         <v>443</v>
       </c>
       <c r="J495" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9503</v>
       </c>
       <c r="K495" s="5" t="n">
         <v>230</v>
@@ -25917,7 +25917,7 @@
         <v>59</v>
       </c>
       <c r="J497" s="11" t="n">
-        <v>0.847</v>
+        <v>0.8475</v>
       </c>
       <c r="K497" s="8" t="n">
         <v>30</v>
@@ -26073,7 +26073,7 @@
         <v>60</v>
       </c>
       <c r="J500" s="11" t="n">
-        <v>0.983</v>
+        <v>0.9833</v>
       </c>
       <c r="K500" s="8" t="n">
         <v>30</v>
@@ -26125,7 +26125,7 @@
         <v>15</v>
       </c>
       <c r="J501" s="11" t="n">
-        <v>0.9997</v>
+        <v>1</v>
       </c>
       <c r="K501" s="8" t="n">
         <v>15</v>
@@ -26229,7 +26229,7 @@
         <v>59</v>
       </c>
       <c r="J503" s="11" t="n">
-        <v>0.9994</v>
+        <v>1</v>
       </c>
       <c r="K503" s="8" t="n">
         <v>30</v>
@@ -26333,7 +26333,7 @@
         <v>70</v>
       </c>
       <c r="J505" s="11" t="n">
-        <v>0.9993</v>
+        <v>1</v>
       </c>
       <c r="K505" s="8" t="n">
         <v>35</v>
@@ -26381,7 +26381,7 @@
         <v>1851</v>
       </c>
       <c r="J506" s="4" t="n">
-        <v>0.8333</v>
+        <v>0.8336</v>
       </c>
       <c r="K506" s="2" t="n">
         <v>903</v>
@@ -26585,7 +26585,7 @@
         <v>15</v>
       </c>
       <c r="J510" s="11" t="n">
-        <v>0.3999</v>
+        <v>0.4</v>
       </c>
       <c r="K510" s="8" t="n">
         <v>5</v>
@@ -26685,7 +26685,7 @@
         <v>63</v>
       </c>
       <c r="J512" s="7" t="n">
-        <v>0.9201</v>
+        <v>0.9206</v>
       </c>
       <c r="K512" s="5" t="n">
         <v>30</v>
@@ -26737,7 +26737,7 @@
         <v>63</v>
       </c>
       <c r="J513" s="11" t="n">
-        <v>0.9201</v>
+        <v>0.9206</v>
       </c>
       <c r="K513" s="8" t="n">
         <v>30</v>
@@ -26785,7 +26785,7 @@
         <v>528</v>
       </c>
       <c r="J514" s="7" t="n">
-        <v>0.8576</v>
+        <v>0.858</v>
       </c>
       <c r="K514" s="5" t="n">
         <v>265</v>
@@ -26837,7 +26837,7 @@
         <v>189</v>
       </c>
       <c r="J515" s="11" t="n">
-        <v>0.92</v>
+        <v>0.9206</v>
       </c>
       <c r="K515" s="8" t="n">
         <v>100</v>
@@ -26941,7 +26941,7 @@
         <v>49</v>
       </c>
       <c r="J517" s="11" t="n">
-        <v>0.9589</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="K517" s="8" t="n">
         <v>25</v>
@@ -26993,7 +26993,7 @@
         <v>150</v>
       </c>
       <c r="J518" s="11" t="n">
-        <v>0.7331</v>
+        <v>0.7333</v>
       </c>
       <c r="K518" s="8" t="n">
         <v>75</v>
@@ -27033,7 +27033,7 @@
         <v>1</v>
       </c>
       <c r="F519" s="10" t="n">
-        <v>13.63</v>
+        <v>13.62</v>
       </c>
       <c r="G519" s="8" t="n">
         <v>7</v>
@@ -27045,7 +27045,7 @@
         <v>120</v>
       </c>
       <c r="J519" s="11" t="n">
-        <v>0.8666</v>
+        <v>0.8667</v>
       </c>
       <c r="K519" s="8" t="n">
         <v>55</v>
@@ -27129,7 +27129,7 @@
         <v>346</v>
       </c>
       <c r="J521" s="7" t="n">
-        <v>0.8321</v>
+        <v>0.8324</v>
       </c>
       <c r="K521" s="5" t="n">
         <v>170</v>
@@ -27337,7 +27337,7 @@
         <v>261</v>
       </c>
       <c r="J525" s="11" t="n">
-        <v>0.8004</v>
+        <v>0.8008</v>
       </c>
       <c r="K525" s="8" t="n">
         <v>125</v>
@@ -27437,7 +27437,7 @@
         <v>139</v>
       </c>
       <c r="J527" s="7" t="n">
-        <v>0.8484</v>
+        <v>0.8489</v>
       </c>
       <c r="K527" s="5" t="n">
         <v>70</v>
@@ -27489,7 +27489,7 @@
         <v>70</v>
       </c>
       <c r="J528" s="11" t="n">
-        <v>0.8567</v>
+        <v>0.8571</v>
       </c>
       <c r="K528" s="8" t="n">
         <v>35</v>
@@ -27541,7 +27541,7 @@
         <v>69</v>
       </c>
       <c r="J529" s="11" t="n">
-        <v>0.84</v>
+        <v>0.8406</v>
       </c>
       <c r="K529" s="8" t="n">
         <v>35</v>
@@ -27777,7 +27777,7 @@
         <v>80</v>
       </c>
       <c r="J534" s="7" t="n">
-        <v>0.8373</v>
+        <v>0.8375</v>
       </c>
       <c r="K534" s="5" t="n">
         <v>38</v>
@@ -27829,7 +27829,7 @@
         <v>60</v>
       </c>
       <c r="J535" s="11" t="n">
-        <v>0.8831</v>
+        <v>0.8833</v>
       </c>
       <c r="K535" s="8" t="n">
         <v>28</v>
@@ -27929,7 +27929,7 @@
         <v>410</v>
       </c>
       <c r="J537" s="7" t="n">
-        <v>0.8754</v>
+        <v>0.8756</v>
       </c>
       <c r="K537" s="5" t="n">
         <v>200</v>
@@ -27981,7 +27981,7 @@
         <v>90</v>
       </c>
       <c r="J538" s="11" t="n">
-        <v>0.8331</v>
+        <v>0.8333</v>
       </c>
       <c r="K538" s="8" t="n">
         <v>40</v>
@@ -28033,7 +28033,7 @@
         <v>51</v>
       </c>
       <c r="J539" s="11" t="n">
-        <v>0.8233</v>
+        <v>0.8235</v>
       </c>
       <c r="K539" s="8" t="n">
         <v>25</v>
@@ -28085,7 +28085,7 @@
         <v>49</v>
       </c>
       <c r="J540" s="11" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="K540" s="8" t="n">
         <v>25</v>
@@ -28137,7 +28137,7 @@
         <v>30</v>
       </c>
       <c r="J541" s="11" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="K541" s="8" t="n">
         <v>15</v>
@@ -28241,7 +28241,7 @@
         <v>90</v>
       </c>
       <c r="J543" s="11" t="n">
-        <v>0.9442</v>
+        <v>0.9444</v>
       </c>
       <c r="K543" s="8" t="n">
         <v>45</v>
@@ -28445,7 +28445,7 @@
         <v>180</v>
       </c>
       <c r="J547" s="7" t="n">
-        <v>0.6166</v>
+        <v>0.6167</v>
       </c>
       <c r="K547" s="5" t="n">
         <v>85</v>
@@ -28549,7 +28549,7 @@
         <v>70</v>
       </c>
       <c r="J549" s="11" t="n">
-        <v>0.4713</v>
+        <v>0.4714</v>
       </c>
       <c r="K549" s="8" t="n">
         <v>30</v>
@@ -28637,7 +28637,7 @@
         <v>29</v>
       </c>
       <c r="F551" s="3" t="n">
-        <v>14.1</v>
+        <v>13.94</v>
       </c>
       <c r="G551" s="2" t="n">
         <v>7</v>
@@ -28646,10 +28646,10 @@
         <v>19</v>
       </c>
       <c r="I551" s="2" t="n">
-        <v>3175</v>
+        <v>3683</v>
       </c>
       <c r="J551" s="4" t="n">
-        <v>0.9066</v>
+        <v>0.8914</v>
       </c>
       <c r="K551" s="2" t="n">
         <v>929</v>
@@ -28697,7 +28697,7 @@
         <v>917</v>
       </c>
       <c r="J552" s="7" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9171</v>
       </c>
       <c r="K552" s="5" t="n">
         <v>225</v>
@@ -28749,7 +28749,7 @@
         <v>60</v>
       </c>
       <c r="J553" s="11" t="n">
-        <v>0.983</v>
+        <v>0.9833</v>
       </c>
       <c r="K553" s="8" t="n">
         <v>15</v>
@@ -28905,7 +28905,7 @@
         <v>60</v>
       </c>
       <c r="J556" s="11" t="n">
-        <v>0.9664</v>
+        <v>0.9667</v>
       </c>
       <c r="K556" s="8" t="n">
         <v>15</v>
@@ -29009,7 +29009,7 @@
         <v>260</v>
       </c>
       <c r="J558" s="11" t="n">
-        <v>0.9532</v>
+        <v>0.9538</v>
       </c>
       <c r="K558" s="8" t="n">
         <v>65</v>
@@ -29159,7 +29159,7 @@
         <v>59</v>
       </c>
       <c r="J561" s="11" t="n">
-        <v>0.9488</v>
+        <v>0.9492</v>
       </c>
       <c r="K561" s="8" t="n">
         <v>15</v>
@@ -29211,7 +29211,7 @@
         <v>98</v>
       </c>
       <c r="J562" s="11" t="n">
-        <v>0.8671</v>
+        <v>0.8673</v>
       </c>
       <c r="K562" s="8" t="n">
         <v>25</v>
@@ -29259,7 +29259,7 @@
         <v>79</v>
       </c>
       <c r="J563" s="7" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9747</v>
       </c>
       <c r="K563" s="5" t="n">
         <v>20</v>
@@ -29311,7 +29311,7 @@
         <v>79</v>
       </c>
       <c r="J564" s="11" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9747</v>
       </c>
       <c r="K564" s="8" t="n">
         <v>20</v>
@@ -29347,7 +29347,7 @@
         <v>19</v>
       </c>
       <c r="F565" s="6" t="n">
-        <v>13.91</v>
+        <v>13.73</v>
       </c>
       <c r="G565" s="5" t="n">
         <v>7</v>
@@ -29356,10 +29356,10 @@
         <v>18</v>
       </c>
       <c r="I565" s="5" t="n">
-        <v>2179</v>
+        <v>2687</v>
       </c>
       <c r="J565" s="7" t="n">
-        <v>0.8998</v>
+        <v>0.8802</v>
       </c>
       <c r="K565" s="5" t="n">
         <v>684</v>
@@ -29411,7 +29411,7 @@
         <v>180</v>
       </c>
       <c r="J566" s="11" t="n">
-        <v>0.905</v>
+        <v>0.9056</v>
       </c>
       <c r="K566" s="8" t="n">
         <v>45</v>
@@ -29463,7 +29463,7 @@
         <v>160</v>
       </c>
       <c r="J567" s="11" t="n">
-        <v>0.9247</v>
+        <v>0.925</v>
       </c>
       <c r="K567" s="8" t="n">
         <v>40</v>
@@ -29555,7 +29555,7 @@
         <v>1</v>
       </c>
       <c r="F569" s="10" t="n">
-        <v>13.76</v>
+        <v>13.75</v>
       </c>
       <c r="G569" s="8" t="n">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>179</v>
       </c>
       <c r="J569" s="11" t="n">
-        <v>0.8931</v>
+        <v>0.8939</v>
       </c>
       <c r="K569" s="8" t="n">
         <v>45</v>
@@ -29619,7 +29619,7 @@
         <v>120</v>
       </c>
       <c r="J570" s="11" t="n">
-        <v>0.9331</v>
+        <v>0.9333</v>
       </c>
       <c r="K570" s="8" t="n">
         <v>30</v>
@@ -29671,7 +29671,7 @@
         <v>120</v>
       </c>
       <c r="J571" s="11" t="n">
-        <v>0.8164</v>
+        <v>0.8167</v>
       </c>
       <c r="K571" s="8" t="n">
         <v>30</v>
@@ -29723,7 +29723,7 @@
         <v>141</v>
       </c>
       <c r="J572" s="11" t="n">
-        <v>0.9213</v>
+        <v>0.922</v>
       </c>
       <c r="K572" s="8" t="n">
         <v>35</v>
@@ -29918,10 +29918,10 @@
         <v>18</v>
       </c>
       <c r="I576" s="8" t="n">
-        <v>100</v>
+        <v>608</v>
       </c>
       <c r="J576" s="11" t="n">
-        <v>0.7938</v>
+        <v>0.7944</v>
       </c>
       <c r="K576" s="8" t="n">
         <v>144</v>
@@ -29973,7 +29973,7 @@
         <v>140</v>
       </c>
       <c r="J577" s="11" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.9143</v>
       </c>
       <c r="K577" s="8" t="n">
         <v>30</v>
@@ -30025,7 +30025,7 @@
         <v>99</v>
       </c>
       <c r="J578" s="11" t="n">
-        <v>0.9393</v>
+        <v>0.9394</v>
       </c>
       <c r="K578" s="8" t="n">
         <v>30</v>
@@ -30077,7 +30077,7 @@
         <v>180</v>
       </c>
       <c r="J579" s="11" t="n">
-        <v>0.8552999999999999</v>
+        <v>0.8556</v>
       </c>
       <c r="K579" s="8" t="n">
         <v>45</v>
@@ -30129,7 +30129,7 @@
         <v>120</v>
       </c>
       <c r="J580" s="11" t="n">
-        <v>0.9247</v>
+        <v>0.925</v>
       </c>
       <c r="K580" s="8" t="n">
         <v>30</v>
@@ -30233,7 +30233,7 @@
         <v>220</v>
       </c>
       <c r="J582" s="11" t="n">
-        <v>0.9675</v>
+        <v>0.9681999999999999</v>
       </c>
       <c r="K582" s="8" t="n">
         <v>55</v>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Muestras azúcar (estim.)</t>
+          <t>Muestras azúcar (deducidas)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -30481,7 +30481,7 @@
         <v>95</v>
       </c>
       <c r="I2" s="11" t="n">
-        <v>0.6943</v>
+        <v>0.6947</v>
       </c>
       <c r="J2" s="8" t="n">
         <v>45</v>
@@ -30528,7 +30528,7 @@
         <v>165</v>
       </c>
       <c r="I3" s="14" t="n">
-        <v>0.6906</v>
+        <v>0.6909</v>
       </c>
       <c r="J3" s="12" t="n">
         <v>80</v>
@@ -30575,7 +30575,7 @@
         <v>664</v>
       </c>
       <c r="I4" s="11" t="n">
-        <v>0.8431</v>
+        <v>0.8434</v>
       </c>
       <c r="J4" s="8" t="n">
         <v>319</v>
@@ -30622,7 +30622,7 @@
         <v>1290</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.7488</v>
       </c>
       <c r="J5" s="12" t="n">
         <v>580</v>
@@ -30669,7 +30669,7 @@
         <v>401</v>
       </c>
       <c r="I6" s="11" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.9002</v>
       </c>
       <c r="J6" s="8" t="n">
         <v>194</v>
@@ -30716,7 +30716,7 @@
         <v>543</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>0.9371</v>
+        <v>0.9374</v>
       </c>
       <c r="J7" s="12" t="n">
         <v>264</v>
@@ -30763,7 +30763,7 @@
         <v>452</v>
       </c>
       <c r="I8" s="11" t="n">
-        <v>0.6788</v>
+        <v>0.6792</v>
       </c>
       <c r="J8" s="8" t="n">
         <v>214</v>
@@ -30810,7 +30810,7 @@
         <v>866</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>0.8793</v>
+        <v>0.8799</v>
       </c>
       <c r="J9" s="12" t="n">
         <v>400</v>
@@ -30857,7 +30857,7 @@
         <v>1000</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="J10" s="8" t="n">
         <v>460</v>
@@ -30892,7 +30892,7 @@
         <v>9</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>14.15</v>
+        <v>14.14</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>8</v>
@@ -30904,7 +30904,7 @@
         <v>1000</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>0.9386</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="J11" s="12" t="n">
         <v>509</v>
@@ -30951,7 +30951,7 @@
         <v>155</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>0.8127</v>
+        <v>0.8129</v>
       </c>
       <c r="J12" s="8" t="n">
         <v>75</v>
@@ -30998,7 +30998,7 @@
         <v>281</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>0.8929</v>
+        <v>0.8932</v>
       </c>
       <c r="J13" s="12" t="n">
         <v>135</v>
@@ -31045,7 +31045,7 @@
         <v>314</v>
       </c>
       <c r="I14" s="11" t="n">
-        <v>0.834</v>
+        <v>0.8344</v>
       </c>
       <c r="J14" s="8" t="n">
         <v>150</v>
@@ -31092,7 +31092,7 @@
         <v>30</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>0.6663</v>
+        <v>0.6667</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>15</v>
@@ -31280,7 +31280,7 @@
         <v>81</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>0.901</v>
+        <v>0.9012</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>34</v>
@@ -31421,7 +31421,7 @@
         <v>323</v>
       </c>
       <c r="I22" s="11" t="n">
-        <v>0.7894</v>
+        <v>0.7895</v>
       </c>
       <c r="J22" s="8" t="n">
         <v>80</v>
@@ -31456,7 +31456,7 @@
         <v>10</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>13.86</v>
+        <v>14.08</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>5</v>
@@ -31465,10 +31465,10 @@
         <v>18</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1238</v>
+        <v>1855</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>0.8502</v>
+        <v>0.8836000000000001</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>305</v>
@@ -31515,7 +31515,7 @@
         <v>747</v>
       </c>
       <c r="I24" s="11" t="n">
-        <v>0.7749</v>
+        <v>0.7751</v>
       </c>
       <c r="J24" s="8" t="n">
         <v>170</v>
@@ -31550,7 +31550,7 @@
         <v>33</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>13.11</v>
+        <v>13.1</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>5</v>
@@ -31562,7 +31562,7 @@
         <v>4126</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>0.7825</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>985</v>
@@ -31609,7 +31609,7 @@
         <v>219</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.9404</v>
+        <v>0.9406</v>
       </c>
       <c r="J26" s="8" t="n">
         <v>55</v>
@@ -31644,7 +31644,7 @@
         <v>11</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>13.9</v>
+        <v>13.65</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>6</v>
@@ -31653,10 +31653,10 @@
         <v>18</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>1200</v>
+        <v>1791</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>0.8599</v>
+        <v>0.8219</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>435</v>
@@ -31738,7 +31738,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>13.85</v>
+        <v>13.76</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>5</v>
@@ -31747,10 +31747,10 @@
         <v>19</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>200</v>
+        <v>1450</v>
       </c>
       <c r="I29" s="14" t="n">
-        <v>0.8192</v>
+        <v>0.8193</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>314</v>
@@ -31797,7 +31797,7 @@
         <v>60</v>
       </c>
       <c r="I30" s="11" t="n">
-        <v>0.7163</v>
+        <v>0.7167</v>
       </c>
       <c r="J30" s="8" t="n">
         <v>15</v>
@@ -31938,7 +31938,7 @@
         <v>522</v>
       </c>
       <c r="I33" s="14" t="n">
-        <v>0.9076</v>
+        <v>0.908</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>130</v>
@@ -31985,7 +31985,7 @@
         <v>608</v>
       </c>
       <c r="I34" s="11" t="n">
-        <v>0.7742</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="J34" s="8" t="n">
         <v>135</v>
@@ -32032,7 +32032,7 @@
         <v>703</v>
       </c>
       <c r="I35" s="14" t="n">
-        <v>0.8942</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>160</v>
@@ -32079,7 +32079,7 @@
         <v>439</v>
       </c>
       <c r="I36" s="11" t="n">
-        <v>0.7539</v>
+        <v>0.754</v>
       </c>
       <c r="J36" s="8" t="n">
         <v>134</v>
@@ -32126,7 +32126,7 @@
         <v>460</v>
       </c>
       <c r="I37" s="14" t="n">
-        <v>0.8451</v>
+        <v>0.8457</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>120</v>
@@ -32173,7 +32173,7 @@
         <v>430</v>
       </c>
       <c r="I38" s="11" t="n">
-        <v>0.8065</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="J38" s="8" t="n">
         <v>99</v>
@@ -32267,7 +32267,7 @@
         <v>1842</v>
       </c>
       <c r="I40" s="11" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9555</v>
       </c>
       <c r="J40" s="8" t="n">
         <v>914</v>
@@ -32314,7 +32314,7 @@
         <v>660</v>
       </c>
       <c r="I41" s="14" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.8697</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>343</v>
@@ -32361,7 +32361,7 @@
         <v>1409</v>
       </c>
       <c r="I42" s="11" t="n">
-        <v>0.9081</v>
+        <v>0.9084</v>
       </c>
       <c r="J42" s="8" t="n">
         <v>697</v>
@@ -32408,7 +32408,7 @@
         <v>1475</v>
       </c>
       <c r="I43" s="14" t="n">
-        <v>0.9772</v>
+        <v>0.9776</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>735</v>
@@ -32455,7 +32455,7 @@
         <v>411</v>
       </c>
       <c r="I44" s="11" t="n">
-        <v>0.8731</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="J44" s="8" t="n">
         <v>205</v>
@@ -32502,7 +32502,7 @@
         <v>1529</v>
       </c>
       <c r="I45" s="14" t="n">
-        <v>0.959</v>
+        <v>0.9595</v>
       </c>
       <c r="J45" s="12" t="n">
         <v>760</v>
@@ -32549,7 +32549,7 @@
         <v>69</v>
       </c>
       <c r="I46" s="11" t="n">
-        <v>0.9994</v>
+        <v>1</v>
       </c>
       <c r="J46" s="8" t="n">
         <v>35</v>
@@ -32643,7 +32643,7 @@
         <v>240</v>
       </c>
       <c r="I48" s="11" t="n">
-        <v>0.9162</v>
+        <v>0.9167</v>
       </c>
       <c r="J48" s="8" t="n">
         <v>125</v>
@@ -32690,7 +32690,7 @@
         <v>89</v>
       </c>
       <c r="I49" s="14" t="n">
-        <v>0.9095</v>
+        <v>0.9101</v>
       </c>
       <c r="J49" s="12" t="n">
         <v>45</v>
@@ -32737,7 +32737,7 @@
         <v>1314</v>
       </c>
       <c r="I50" s="11" t="n">
-        <v>0.8405</v>
+        <v>0.8409</v>
       </c>
       <c r="J50" s="8" t="n">
         <v>645</v>
@@ -32831,7 +32831,7 @@
         <v>140</v>
       </c>
       <c r="I52" s="11" t="n">
-        <v>0.8998</v>
+        <v>0.9</v>
       </c>
       <c r="J52" s="8" t="n">
         <v>69</v>
@@ -32878,7 +32878,7 @@
         <v>612</v>
       </c>
       <c r="I53" s="14" t="n">
-        <v>0.8331</v>
+        <v>0.8333</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>305</v>
@@ -32925,7 +32925,7 @@
         <v>240</v>
       </c>
       <c r="I54" s="11" t="n">
-        <v>0.9789</v>
+        <v>0.9792</v>
       </c>
       <c r="J54" s="8" t="n">
         <v>120</v>
@@ -32972,7 +32972,7 @@
         <v>1163</v>
       </c>
       <c r="I55" s="14" t="n">
-        <v>0.7813</v>
+        <v>0.7816</v>
       </c>
       <c r="J55" s="12" t="n">
         <v>598</v>
@@ -33019,7 +33019,7 @@
         <v>430</v>
       </c>
       <c r="I56" s="11" t="n">
-        <v>0.8343</v>
+        <v>0.8349</v>
       </c>
       <c r="J56" s="8" t="n">
         <v>201</v>
@@ -33066,7 +33066,7 @@
         <v>49</v>
       </c>
       <c r="I57" s="14" t="n">
-        <v>0.8976</v>
+        <v>0.898</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>35</v>
@@ -33101,7 +33101,7 @@
         <v>2</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>12.81</v>
+        <v>12.8</v>
       </c>
       <c r="F58" s="8" t="n">
         <v>8</v>
@@ -33113,7 +33113,7 @@
         <v>100</v>
       </c>
       <c r="I58" s="11" t="n">
-        <v>0.7296</v>
+        <v>0.73</v>
       </c>
       <c r="J58" s="8" t="n">
         <v>50</v>
@@ -33160,7 +33160,7 @@
         <v>51</v>
       </c>
       <c r="I59" s="14" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7647</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>20</v>
@@ -33207,7 +33207,7 @@
         <v>30</v>
       </c>
       <c r="I60" s="11" t="n">
-        <v>0.7664</v>
+        <v>0.7667</v>
       </c>
       <c r="J60" s="8" t="n">
         <v>10</v>
@@ -33254,7 +33254,7 @@
         <v>41</v>
       </c>
       <c r="I61" s="14" t="n">
-        <v>0.9996</v>
+        <v>1</v>
       </c>
       <c r="J61" s="12" t="n">
         <v>15</v>
@@ -33395,7 +33395,7 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="n">
-        <v>0.9796</v>
+        <v>0.9799</v>
       </c>
       <c r="J64" s="8" t="n">
         <v>85</v>
@@ -33442,7 +33442,7 @@
         <v>439</v>
       </c>
       <c r="I65" s="14" t="n">
-        <v>0.9678</v>
+        <v>0.9681</v>
       </c>
       <c r="J65" s="12" t="n">
         <v>225</v>
@@ -33489,7 +33489,7 @@
         <v>160</v>
       </c>
       <c r="I66" s="11" t="n">
-        <v>0.9059</v>
+        <v>0.9062</v>
       </c>
       <c r="J66" s="8" t="n">
         <v>80</v>
@@ -33583,7 +33583,7 @@
         <v>30</v>
       </c>
       <c r="I68" s="11" t="n">
-        <v>0.833</v>
+        <v>0.8333</v>
       </c>
       <c r="J68" s="8" t="n">
         <v>15</v>
@@ -33630,7 +33630,7 @@
         <v>110</v>
       </c>
       <c r="I69" s="14" t="n">
-        <v>0.9537</v>
+        <v>0.9545</v>
       </c>
       <c r="J69" s="12" t="n">
         <v>55</v>
@@ -33771,7 +33771,7 @@
         <v>443</v>
       </c>
       <c r="I72" s="11" t="n">
-        <v>0.95</v>
+        <v>0.9503</v>
       </c>
       <c r="J72" s="8" t="n">
         <v>230</v>
@@ -33865,7 +33865,7 @@
         <v>63</v>
       </c>
       <c r="I74" s="11" t="n">
-        <v>0.9201</v>
+        <v>0.9206</v>
       </c>
       <c r="J74" s="8" t="n">
         <v>30</v>
@@ -33912,7 +33912,7 @@
         <v>528</v>
       </c>
       <c r="I75" s="14" t="n">
-        <v>0.8576</v>
+        <v>0.858</v>
       </c>
       <c r="J75" s="12" t="n">
         <v>265</v>
@@ -33959,7 +33959,7 @@
         <v>346</v>
       </c>
       <c r="I76" s="11" t="n">
-        <v>0.8321</v>
+        <v>0.8324</v>
       </c>
       <c r="J76" s="8" t="n">
         <v>170</v>
@@ -34006,7 +34006,7 @@
         <v>139</v>
       </c>
       <c r="I77" s="14" t="n">
-        <v>0.8484</v>
+        <v>0.8489</v>
       </c>
       <c r="J77" s="12" t="n">
         <v>70</v>
@@ -34141,7 +34141,7 @@
         <v>80</v>
       </c>
       <c r="I80" s="11" t="n">
-        <v>0.8373</v>
+        <v>0.8375</v>
       </c>
       <c r="J80" s="8" t="n">
         <v>38</v>
@@ -34188,7 +34188,7 @@
         <v>410</v>
       </c>
       <c r="I81" s="14" t="n">
-        <v>0.8754</v>
+        <v>0.8756</v>
       </c>
       <c r="J81" s="12" t="n">
         <v>200</v>
@@ -34235,7 +34235,7 @@
         <v>180</v>
       </c>
       <c r="I82" s="11" t="n">
-        <v>0.6166</v>
+        <v>0.6167</v>
       </c>
       <c r="J82" s="8" t="n">
         <v>85</v>
@@ -34282,7 +34282,7 @@
         <v>917</v>
       </c>
       <c r="I83" s="14" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.9171</v>
       </c>
       <c r="J83" s="12" t="n">
         <v>225</v>
@@ -34329,7 +34329,7 @@
         <v>79</v>
       </c>
       <c r="I84" s="11" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9747</v>
       </c>
       <c r="J84" s="8" t="n">
         <v>20</v>
@@ -34364,7 +34364,7 @@
         <v>19</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>13.91</v>
+        <v>13.73</v>
       </c>
       <c r="F85" s="12" t="n">
         <v>7</v>
@@ -34373,10 +34373,10 @@
         <v>18</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>2179</v>
+        <v>2687</v>
       </c>
       <c r="I85" s="14" t="n">
-        <v>0.8998</v>
+        <v>0.8802</v>
       </c>
       <c r="J85" s="12" t="n">
         <v>684</v>
